--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G2" t="n">
         <v>1.54</v>
@@ -766,13 +766,13 @@
         <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J2" t="n">
         <v>4.7</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -787,10 +787,10 @@
         <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R2" t="n">
         <v>1.59</v>
@@ -814,7 +814,7 @@
         <v>26</v>
       </c>
       <c r="Y2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z2" t="n">
         <v>80</v>
@@ -874,7 +874,7 @@
         <v>44</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT2" t="n">
         <v>9.199999999999999</v>
@@ -898,7 +898,7 @@
         <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB2" t="n">
         <v>10</v>
@@ -907,20 +907,20 @@
         <v>10.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF2" t="n">
         <v>4.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>4.9</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="I3" t="n">
         <v>1.97</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>3.15</v>
       </c>
       <c r="I4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
@@ -1178,7 +1178,7 @@
         <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="G5" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="H5" t="n">
         <v>2.76</v>
@@ -1354,7 +1354,7 @@
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G7" t="n">
         <v>2.52</v>
       </c>
       <c r="H7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
         <v>4.5</v>
@@ -1742,7 +1742,7 @@
         <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="G8" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="H8" t="n">
-        <v>7.4</v>
+        <v>2.92</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="K8" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G9" t="n">
         <v>2.74</v>
@@ -2127,7 +2127,7 @@
         <v>2.96</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
         <v>4.1</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G10" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="H10" t="n">
         <v>4.6</v>
@@ -2339,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
         <v>1.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -2509,16 +2509,16 @@
         <v>2.12</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J11" t="n">
         <v>2.92</v>
       </c>
       <c r="K11" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
         <v>2.74</v>
@@ -3097,10 +3097,10 @@
         <v>2.64</v>
       </c>
       <c r="J14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K14" t="n">
         <v>3.95</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3112,25 +3112,25 @@
         <v>4.9</v>
       </c>
       <c r="O14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S14" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U14" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3139,16 +3139,16 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB14" t="n">
         <v>14.5</v>
@@ -3187,16 +3187,16 @@
         <v>65</v>
       </c>
       <c r="AN14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO14" t="n">
         <v>18</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AP14" t="n">
         <v>17.5</v>
       </c>
-      <c r="AP14" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AQ14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR14" t="n">
         <v>17.5</v>
@@ -3205,10 +3205,10 @@
         <v>32</v>
       </c>
       <c r="AT14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV14" t="n">
         <v>11</v>
@@ -3223,7 +3223,7 @@
         <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
         <v>21</v>
@@ -3232,7 +3232,7 @@
         <v>24</v>
       </c>
       <c r="BC14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD14" t="n">
         <v>21</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -3285,13 +3285,13 @@
         <v>3.6</v>
       </c>
       <c r="H15" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I15" t="n">
         <v>2.44</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
         <v>4.1</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.79</v>
+        <v>2.36</v>
       </c>
       <c r="G16" t="n">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="H16" t="n">
-        <v>2.08</v>
+        <v>2.84</v>
       </c>
       <c r="I16" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
-        <v>2.58</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3506,7 +3506,7 @@
         <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -3867,10 +3867,10 @@
         <v>2.4</v>
       </c>
       <c r="H18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I18" t="n">
         <v>3.95</v>
-      </c>
-      <c r="I18" t="n">
-        <v>4</v>
       </c>
       <c r="J18" t="n">
         <v>3.05</v>
@@ -3885,22 +3885,22 @@
         <v>1.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P18" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T18" t="n">
         <v>2.16</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y18" t="n">
         <v>10.5</v>
@@ -3933,82 +3933,82 @@
         <v>6.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>65</v>
       </c>
       <c r="AF18" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI18" t="n">
         <v>85</v>
       </c>
       <c r="AJ18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK18" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL18" t="n">
         <v>65</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN18" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AO18" t="n">
         <v>90</v>
       </c>
       <c r="AP18" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR18" t="n">
         <v>23</v>
       </c>
       <c r="AS18" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AT18" t="n">
         <v>7.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV18" t="n">
         <v>15</v>
       </c>
       <c r="AW18" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AX18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BA18" t="n">
         <v>36</v>
       </c>
       <c r="BB18" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC18" t="n">
         <v>27</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>26</v>
       </c>
       <c r="BD18" t="n">
         <v>50</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>2.56</v>
       </c>
       <c r="I19" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
         <v>3.65</v>
@@ -4085,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q19" t="n">
         <v>1.7</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -4455,10 +4455,10 @@
         <v>1.19</v>
       </c>
       <c r="J21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4479,16 +4479,16 @@
         <v>1.38</v>
       </c>
       <c r="R21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S21" t="n">
         <v>1.97</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.98</v>
       </c>
       <c r="T21" t="n">
         <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4500,16 +4500,16 @@
         <v>44</v>
       </c>
       <c r="Y21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB21" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC21" t="n">
         <v>23</v>
@@ -4521,13 +4521,13 @@
         <v>13</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AG21" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AH21" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI21" t="n">
         <v>42</v>
@@ -4542,16 +4542,16 @@
         <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
         <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="AP21" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AQ21" t="n">
         <v>12.5</v>
@@ -4596,17 +4596,17 @@
         <v>75</v>
       </c>
       <c r="BE21" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BF21" t="n">
         <v>110</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
         <v>3.8</v>
       </c>
       <c r="I22" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J22" t="n">
         <v>3.75</v>
@@ -4676,7 +4676,7 @@
         <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T22" t="n">
         <v>1.7</v>
@@ -4691,7 +4691,7 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y22" t="n">
         <v>16.5</v>
@@ -4709,10 +4709,10 @@
         <v>8.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF22" t="n">
         <v>14.5</v>
@@ -4766,7 +4766,7 @@
         <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AX22" t="n">
         <v>12.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
         <v>7.6</v>
       </c>
       <c r="K23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4867,7 +4867,7 @@
         <v>1.33</v>
       </c>
       <c r="R23" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S23" t="n">
         <v>1.8</v>
@@ -4915,7 +4915,7 @@
         <v>12.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
@@ -4939,22 +4939,22 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AQ23" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AR23" t="n">
         <v>42</v>
       </c>
       <c r="AS23" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AT23" t="n">
         <v>15</v>
       </c>
       <c r="AU23" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AV23" t="n">
         <v>40</v>
@@ -4987,14 +4987,14 @@
         <v>36</v>
       </c>
       <c r="BF23" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BG23" t="n">
         <v>40</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -5028,10 +5028,10 @@
         <v>1.74</v>
       </c>
       <c r="G24" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="I24" t="n">
         <v>6.4</v>
@@ -5040,7 +5040,7 @@
         <v>3.05</v>
       </c>
       <c r="K24" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>1.29</v>
       </c>
       <c r="G27" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="H27" t="n">
         <v>7</v>
@@ -5619,7 +5619,7 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="K27" t="n">
         <v>6.4</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH27"/>
+  <dimension ref="A1:BH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,16 +790,16 @@
         <v>2.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R2" t="n">
         <v>1.59</v>
       </c>
       <c r="S2" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="T2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U2" t="n">
         <v>2.1</v>
@@ -811,22 +811,22 @@
         <v>2.84</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Y2" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Z2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AA2" t="n">
         <v>240</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD2" t="n">
         <v>29</v>
@@ -835,31 +835,31 @@
         <v>110</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
         <v>95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK2" t="n">
         <v>18</v>
       </c>
       <c r="AL2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
         <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
         <v>120</v>
@@ -874,7 +874,7 @@
         <v>44</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="AT2" t="n">
         <v>9.199999999999999</v>
@@ -886,7 +886,7 @@
         <v>19.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="AX2" t="n">
         <v>8.800000000000001</v>
@@ -898,7 +898,7 @@
         <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="BB2" t="n">
         <v>10</v>
@@ -907,20 +907,20 @@
         <v>10.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
         <v>1.22</v>
@@ -987,16 +987,16 @@
         <v>1.73</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U3" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
         <v>2.02</v>
@@ -1011,7 +1011,7 @@
         <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
         <v>22</v>
@@ -1029,25 +1029,25 @@
         <v>20</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG3" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
         <v>18.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1056,22 +1056,22 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="AQ3" t="n">
         <v>9</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="AU3" t="n">
         <v>7.8</v>
@@ -1080,41 +1080,41 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.1</v>
+        <v>13.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.2</v>
+        <v>40</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF3" t="n">
         <v>34</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -1345,10 +1345,10 @@
         <v>2.84</v>
       </c>
       <c r="H5" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="I5" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G6" t="n">
         <v>1.41</v>
@@ -1542,13 +1542,13 @@
         <v>8.4</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="J6" t="n">
         <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hobro</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HB Koge</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>2.52</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -1912,31 +1912,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Aarhus Fremad</t>
+          <t>Hobro</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Middelfart</t>
+          <t>HB Koge</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.3</v>
+        <v>1.98</v>
       </c>
       <c r="G8" t="n">
-        <v>1.52</v>
+        <v>2.14</v>
       </c>
       <c r="H8" t="n">
-        <v>2.92</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Aarhus Fremad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Middelfart</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.46</v>
+        <v>1.3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.74</v>
+        <v>1.48</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="I9" t="n">
-        <v>2.96</v>
+        <v>60</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -2300,31 +2300,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FC Copenhagen</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.66</v>
+        <v>2.46</v>
       </c>
       <c r="G10" t="n">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>2.96</v>
       </c>
       <c r="J10" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>FC Copenhagen</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="G11" t="n">
-        <v>2.12</v>
+        <v>1.71</v>
       </c>
       <c r="H11" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="I11" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="J11" t="n">
-        <v>2.92</v>
+        <v>4.3</v>
       </c>
       <c r="K11" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.46</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.22</v>
+        <v>1.5</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Red Bull Salzburg</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="I12" t="n">
         <v>6.6</v>
       </c>
       <c r="J12" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.08</v>
+        <v>1.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.56</v>
+        <v>2.22</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rapid Vienna</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>1.83</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>1.07</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,66 +3071,66 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>1.07</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3139,123 +3139,123 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Oliveirense</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Benfica B</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>1.07</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,36 +3459,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Rapid Vienna</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.36</v>
+        <v>1.73</v>
       </c>
       <c r="G16" t="n">
-        <v>2.52</v>
+        <v>1.83</v>
       </c>
       <c r="H16" t="n">
-        <v>2.84</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,36 +3653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Red Bull Salzburg</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.4</v>
+        <v>1.66</v>
       </c>
       <c r="G17" t="n">
-        <v>7</v>
+        <v>1.76</v>
       </c>
       <c r="H17" t="n">
-        <v>1.82</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>2.12</v>
+        <v>6.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.54</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,66 +3847,66 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Oliveirense</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Benfica B</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="H18" t="n">
-        <v>3.9</v>
+        <v>2.18</v>
       </c>
       <c r="I18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K18" t="n">
         <v>3.95</v>
       </c>
-      <c r="J18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.1</v>
-      </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3915,123 +3915,123 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,66 +4041,66 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G19" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="H19" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="J19" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4109,123 +4109,123 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,36 +4235,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Brondby</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,66 +4429,66 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>4.4</v>
       </c>
       <c r="G21" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>1.18</v>
+        <v>1.82</v>
       </c>
       <c r="I21" t="n">
-        <v>1.19</v>
+        <v>2.12</v>
       </c>
       <c r="J21" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="K21" t="n">
-        <v>9.6</v>
+        <v>4.5</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.45</v>
+        <v>1.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="R21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4497,123 +4497,123 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,66 +4623,66 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="G22" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="H22" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I22" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="K22" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="N22" t="n">
-        <v>4.6</v>
+        <v>2.76</v>
       </c>
       <c r="O22" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="P22" t="n">
-        <v>2.22</v>
+        <v>1.57</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.79</v>
+        <v>2.66</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="S22" t="n">
-        <v>2.98</v>
+        <v>5.4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="U22" t="n">
-        <v>2.36</v>
+        <v>1.82</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4691,123 +4691,123 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>17.5</v>
+        <v>8.6</v>
       </c>
       <c r="Y22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z22" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI22" t="n">
+      <c r="BA22" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE22" t="n">
         <v>46</v>
       </c>
-      <c r="AJ22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO22" t="n">
+      <c r="BF22" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG22" t="n">
         <v>36</v>
       </c>
-      <c r="AP22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>23</v>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,66 +4817,66 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.26</v>
+        <v>2.7</v>
       </c>
       <c r="G23" t="n">
-        <v>1.27</v>
+        <v>2.88</v>
       </c>
       <c r="H23" t="n">
-        <v>12</v>
+        <v>2.54</v>
       </c>
       <c r="I23" t="n">
-        <v>13.5</v>
+        <v>2.74</v>
       </c>
       <c r="J23" t="n">
-        <v>7.6</v>
+        <v>3.65</v>
       </c>
       <c r="K23" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3.75</v>
+        <v>2.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="R23" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4885,123 +4885,123 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,36 +5011,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>2.22</v>
+        <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="K24" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>20</v>
       </c>
       <c r="G25" t="n">
+        <v>21</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="J25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>210</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>1000</v>
       </c>
-      <c r="H25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="AK25" t="n">
+        <v>340</v>
+      </c>
+      <c r="AL25" t="n">
         <v>1000</v>
       </c>
-      <c r="J25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="AM25" t="n">
         <v>1000</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0</v>
-      </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,66 +5399,66 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Barcelona (Ecu)</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="J26" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="K26" t="n">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P26" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5467,310 +5467,1086 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H27" t="n">
+        <v>12</v>
+      </c>
+      <c r="I27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>8</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>470</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>990</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-20 06:19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>17:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-20 06:19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Real Potosi</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-20 06:19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-20 06:19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>20:20:00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Ind Medellin</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Boyaca Chico</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F31" t="n">
         <v>1.29</v>
       </c>
-      <c r="G27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="H27" t="n">
-        <v>7</v>
-      </c>
-      <c r="I27" t="n">
+      <c r="G31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I31" t="n">
         <v>18</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J31" t="n">
         <v>4.7</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K31" t="n">
         <v>6.4</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q31" t="n">
         <v>1.64</v>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH27" t="inlineStr">
-        <is>
-          <t>2026-04-20 04:08:36</t>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
@@ -760,7 +760,7 @@
         <v>1.47</v>
       </c>
       <c r="G2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H2" t="n">
         <v>7</v>
@@ -796,19 +796,19 @@
         <v>1.59</v>
       </c>
       <c r="S2" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="T2" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V2" t="n">
         <v>1.14</v>
       </c>
       <c r="W2" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="X2" t="n">
         <v>30</v>
@@ -817,7 +817,7 @@
         <v>36</v>
       </c>
       <c r="Z2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA2" t="n">
         <v>240</v>
@@ -829,10 +829,10 @@
         <v>14.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AE2" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF2" t="n">
         <v>12.5</v>
@@ -868,16 +868,16 @@
         <v>20</v>
       </c>
       <c r="AQ2" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
-        <v>44</v>
+        <v>4.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU2" t="n">
         <v>10</v>
@@ -898,7 +898,7 @@
         <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB2" t="n">
         <v>10</v>
@@ -910,17 +910,17 @@
         <v>4</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF2" t="n">
         <v>5.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="I3" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -975,79 +975,79 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
         <v>2.72</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="U3" t="n">
         <v>2.2</v>
       </c>
       <c r="V3" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="W3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X3" t="n">
         <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AB3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG3" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1056,65 +1056,65 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP3" t="n">
         <v>16</v>
       </c>
       <c r="AQ3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV3" t="n">
         <v>9</v>
       </c>
-      <c r="AR3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV3" t="n">
+      <c r="AW3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AW3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>38</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>34</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
         <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v>2.7</v>
       </c>
       <c r="I10" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="J10" t="n">
         <v>3.65</v>
@@ -2339,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
         <v>1.67</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="G19" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="H19" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="I19" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
         <v>3.9</v>
@@ -4115,7 +4115,7 @@
         <v>15</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA19" t="n">
         <v>44</v>
@@ -4166,7 +4166,7 @@
         <v>17</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR19" t="n">
         <v>17</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -4452,10 +4452,10 @@
         <v>1.82</v>
       </c>
       <c r="I21" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
         <v>4.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G22" t="n">
         <v>2.34</v>
       </c>
-      <c r="G22" t="n">
-        <v>2.36</v>
-      </c>
       <c r="H22" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I22" t="n">
         <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K22" t="n">
         <v>3.15</v>
@@ -4661,7 +4661,7 @@
         <v>1.13</v>
       </c>
       <c r="N22" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="O22" t="n">
         <v>1.54</v>
@@ -4670,7 +4670,7 @@
         <v>1.57</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R22" t="n">
         <v>1.2</v>
@@ -4748,7 +4748,7 @@
         <v>7.8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR22" t="n">
         <v>23</v>
@@ -4775,7 +4775,7 @@
         <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA22" t="n">
         <v>38</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>2.88</v>
       </c>
       <c r="H23" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I23" t="n">
         <v>2.74</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -5225,16 +5225,16 @@
         <v>21</v>
       </c>
       <c r="H25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I25" t="n">
         <v>1.18</v>
       </c>
-      <c r="I25" t="n">
-        <v>1.19</v>
-      </c>
       <c r="J25" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,7 +5249,7 @@
         <v>1.12</v>
       </c>
       <c r="P25" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q25" t="n">
         <v>1.38</v>
@@ -5264,7 +5264,7 @@
         <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5273,7 +5273,7 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Y25" t="n">
         <v>13.5</v>
@@ -5282,7 +5282,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AA25" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB25" t="n">
         <v>75</v>
@@ -5291,7 +5291,7 @@
         <v>23</v>
       </c>
       <c r="AD25" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -5300,7 +5300,7 @@
         <v>210</v>
       </c>
       <c r="AG25" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AH25" t="n">
         <v>42</v>
@@ -5336,13 +5336,13 @@
         <v>8.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT25" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AU25" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AV25" t="n">
         <v>12</v>
@@ -5360,7 +5360,7 @@
         <v>34</v>
       </c>
       <c r="BA25" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB25" t="n">
         <v>150</v>
@@ -5378,11 +5378,11 @@
         <v>120</v>
       </c>
       <c r="BG25" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
         <v>4.6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P26" t="n">
         <v>2.2</v>
@@ -5452,7 +5452,7 @@
         <v>1.49</v>
       </c>
       <c r="S26" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
         <v>1.7</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y26" t="n">
         <v>16.5</v>
@@ -5485,7 +5485,7 @@
         <v>8.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE26" t="n">
         <v>40</v>
@@ -5497,7 +5497,7 @@
         <v>10.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI26" t="n">
         <v>46</v>
@@ -5527,10 +5527,10 @@
         <v>14.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AS26" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AT26" t="n">
         <v>10.5</v>
@@ -5542,7 +5542,7 @@
         <v>14</v>
       </c>
       <c r="AW26" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AX26" t="n">
         <v>12.5</v>
@@ -5563,7 +5563,7 @@
         <v>18.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BE26" t="n">
         <v>34</v>
@@ -5572,11 +5572,11 @@
         <v>11</v>
       </c>
       <c r="BG26" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -5616,13 +5616,13 @@
         <v>12</v>
       </c>
       <c r="I27" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="J27" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="K27" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5646,7 +5646,7 @@
         <v>2.12</v>
       </c>
       <c r="S27" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="T27" t="n">
         <v>1.75</v>
@@ -5676,7 +5676,7 @@
         <v>16.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AD27" t="n">
         <v>48</v>
@@ -5691,7 +5691,7 @@
         <v>12.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
@@ -5715,10 +5715,10 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ27" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AR27" t="n">
         <v>42</v>
@@ -5730,10 +5730,10 @@
         <v>14.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AV27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW27" t="n">
         <v>44</v>
@@ -5748,7 +5748,7 @@
         <v>24</v>
       </c>
       <c r="BA27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB27" t="n">
         <v>10.5</v>
@@ -5760,17 +5760,17 @@
         <v>23</v>
       </c>
       <c r="BE27" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF27" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BG27" t="n">
         <v>40</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="G30" t="n">
         <v>1.9</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -6389,13 +6389,13 @@
         <v>1.36</v>
       </c>
       <c r="H31" t="n">
-        <v>1.09</v>
+        <v>12.5</v>
       </c>
       <c r="I31" t="n">
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="K31" t="n">
         <v>6.4</v>
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH31"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G2" t="n">
         <v>1.53</v>
@@ -817,22 +817,22 @@
         <v>36</v>
       </c>
       <c r="Z2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AA2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB2" t="n">
         <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD2" t="n">
         <v>34</v>
       </c>
       <c r="AE2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF2" t="n">
         <v>12.5</v>
@@ -862,7 +862,7 @@
         <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP2" t="n">
         <v>20</v>
@@ -871,10 +871,10 @@
         <v>4</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT2" t="n">
         <v>9</v>
@@ -886,7 +886,7 @@
         <v>19.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX2" t="n">
         <v>8.800000000000001</v>
@@ -898,7 +898,7 @@
         <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB2" t="n">
         <v>10</v>
@@ -910,17 +910,17 @@
         <v>4</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF2" t="n">
         <v>5.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="H3" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -990,19 +990,19 @@
         <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T3" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V3" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="W3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
         <v>21</v>
@@ -1029,10 +1029,10 @@
         <v>21</v>
       </c>
       <c r="AF3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AG3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH3" t="n">
         <v>18</v>
@@ -1059,7 +1059,7 @@
         <v>13.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ3" t="n">
         <v>9.199999999999999</v>
@@ -1092,29 +1092,29 @@
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD3" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -1160,19 +1160,19 @@
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
         <v>1.96</v>
@@ -1181,134 +1181,134 @@
         <v>1.9</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="G5" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H5" t="n">
         <v>2.8</v>
       </c>
       <c r="I5" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
@@ -1357,152 +1357,152 @@
         <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -1539,171 +1539,171 @@
         <v>1.41</v>
       </c>
       <c r="H6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I6" t="n">
         <v>11.5</v>
       </c>
       <c r="J6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K6" t="n">
         <v>6.6</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P6" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q6" t="n">
         <v>1.46</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nomme Utd</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="G7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM7" t="n">
         <v>1000</v>
       </c>
-      <c r="H7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="AN7" t="n">
         <v>1000</v>
       </c>
-      <c r="J7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="AO7" t="n">
         <v>1000</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hobro</t>
+          <t>Athlitiki Enosi Larissa</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HB Koge</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="G8" t="n">
-        <v>2.14</v>
+        <v>3.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>2.44</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>2.54</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,33 +2101,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aarhus Fremad</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Middelfart</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1.48</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,31 +2300,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FC Copenhagen</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.66</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>1.71</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="G12" t="n">
         <v>2.12</v>
       </c>
       <c r="H12" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
         <v>6.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,31 +2882,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>Hobro</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>HB Koge</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.98</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,31 +3076,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trans Narva</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,28 +3270,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>Aarhus Fremad</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>Middelfart</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>1.45</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,36 +3459,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Rapid Vienna</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="G16" t="n">
-        <v>1.83</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3.85</v>
+        <v>1.91</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.97</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,37 +3653,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Red Bull Salzburg</t>
+          <t>FC Copenhagen</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1.66</v>
       </c>
       <c r="G17" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="H17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K17" t="n">
         <v>5</v>
       </c>
-      <c r="I17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,36 +3847,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Oliveirense</t>
+          <t>Rapid Vienna</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Benfica B</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.15</v>
+        <v>1.73</v>
       </c>
       <c r="G18" t="n">
-        <v>3.6</v>
+        <v>1.83</v>
       </c>
       <c r="H18" t="n">
-        <v>2.18</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>2.44</v>
+        <v>6.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,66 +4041,66 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Red Bull Salzburg</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.76</v>
+        <v>1.66</v>
       </c>
       <c r="G19" t="n">
-        <v>2.78</v>
+        <v>1.76</v>
       </c>
       <c r="H19" t="n">
-        <v>2.58</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="R19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4109,123 +4109,123 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,36 +4235,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="G20" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H20" t="n">
-        <v>2.84</v>
+        <v>3.65</v>
       </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.36</v>
+        <v>1.61</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.63</v>
+        <v>2.28</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,36 +4429,36 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Oliveirense</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Benfica B</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="H21" t="n">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.54</v>
+        <v>2.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -4623,66 +4623,66 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="G22" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="H22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K22" t="n">
         <v>3.95</v>
       </c>
-      <c r="I22" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.15</v>
-      </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>2.74</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="P22" t="n">
-        <v>1.57</v>
+        <v>2.26</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.64</v>
+        <v>1.78</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>5.4</v>
+        <v>2.84</v>
       </c>
       <c r="T22" t="n">
-        <v>2.16</v>
+        <v>1.64</v>
       </c>
       <c r="U22" t="n">
-        <v>1.82</v>
+        <v>2.46</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4691,123 +4691,123 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>8.6</v>
+        <v>19.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="Z22" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AA22" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AB22" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AC22" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="AF22" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AG22" t="n">
         <v>12.5</v>
       </c>
       <c r="AH22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS22" t="n">
         <v>23</v>
       </c>
-      <c r="AI22" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>36</v>
-      </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AV22" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE22" t="n">
         <v>55</v>
       </c>
-      <c r="AX22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>46</v>
-      </c>
       <c r="BF22" t="n">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,36 +4817,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Brondby</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="G23" t="n">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="H23" t="n">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="I23" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,36 +5011,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>20</v>
+        <v>2.32</v>
       </c>
       <c r="G25" t="n">
-        <v>21</v>
+        <v>2.34</v>
       </c>
       <c r="H25" t="n">
-        <v>1.17</v>
+        <v>3.95</v>
       </c>
       <c r="I25" t="n">
-        <v>1.18</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="K25" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
+      <c r="AR25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE25" t="n">
         <v>46</v>
       </c>
-      <c r="Y25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>75</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>210</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>75</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>340</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>90</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>34</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>150</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>110</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>75</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>90</v>
-      </c>
       <c r="BF25" t="n">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="BG25" t="n">
-        <v>2.74</v>
+        <v>80</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,66 +5399,66 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.08</v>
+        <v>2.7</v>
       </c>
       <c r="G26" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="H26" t="n">
-        <v>3.85</v>
+        <v>2.56</v>
       </c>
       <c r="I26" t="n">
-        <v>3.95</v>
+        <v>2.74</v>
       </c>
       <c r="J26" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K26" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5467,123 +5467,123 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,66 +5593,66 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="G27" t="n">
-        <v>1.27</v>
+        <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="I27" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="K27" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>3.75</v>
+        <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="R27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -5661,123 +5661,123 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,66 +5787,66 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.75</v>
+        <v>21</v>
       </c>
       <c r="G28" t="n">
-        <v>2.22</v>
+        <v>23</v>
       </c>
       <c r="H28" t="n">
-        <v>3.65</v>
+        <v>1.17</v>
       </c>
       <c r="I28" t="n">
-        <v>6.4</v>
+        <v>1.18</v>
       </c>
       <c r="J28" t="n">
-        <v>3.05</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P28" t="n">
-        <v>1.58</v>
+        <v>3.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.1</v>
+        <v>1.37</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5855,123 +5855,123 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,66 +5981,66 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>2.12</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="J29" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6049,123 +6049,123 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,66 +6175,66 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Barcelona (Ecu)</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="G30" t="n">
-        <v>1.9</v>
+        <v>1.27</v>
       </c>
       <c r="H30" t="n">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
       <c r="I30" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="J30" t="n">
-        <v>2.8</v>
+        <v>7.8</v>
       </c>
       <c r="K30" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>3.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -6243,310 +6243,892 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>17:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-20 10:44:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Real Potosi</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-20 10:44:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-04-20 10:44:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>20:20:00</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Ind Medellin</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Boyaca Chico</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="F34" t="n">
         <v>1.29</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G34" t="n">
         <v>1.36</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H34" t="n">
         <v>12.5</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I34" t="n">
         <v>18</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J34" t="n">
         <v>5.3</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K34" t="n">
         <v>6.4</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q31" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>2026-04-20 08:31:25</t>
+      <c r="Q34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH34"/>
+  <dimension ref="A1:BH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="G2" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="H2" t="n">
         <v>7</v>
@@ -769,7 +769,7 @@
         <v>7.8</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K2" t="n">
         <v>5.3</v>
@@ -808,13 +808,13 @@
         <v>1.14</v>
       </c>
       <c r="W2" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="X2" t="n">
         <v>30</v>
       </c>
       <c r="Y2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z2" t="n">
         <v>65</v>
@@ -829,7 +829,7 @@
         <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AE2" t="n">
         <v>110</v>
@@ -868,13 +868,13 @@
         <v>20</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT2" t="n">
         <v>9</v>
@@ -886,7 +886,7 @@
         <v>19.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX2" t="n">
         <v>8.800000000000001</v>
@@ -898,7 +898,7 @@
         <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB2" t="n">
         <v>10</v>
@@ -907,20 +907,20 @@
         <v>10.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF2" t="n">
         <v>5.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="I3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J3" t="n">
         <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -981,7 +981,7 @@
         <v>1.23</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
         <v>1.75</v>
@@ -993,16 +993,16 @@
         <v>2.76</v>
       </c>
       <c r="T3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X3" t="n">
         <v>21</v>
@@ -1053,7 +1053,7 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO3" t="n">
         <v>13.5</v>
@@ -1083,7 +1083,7 @@
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY3" t="n">
         <v>14</v>
@@ -1092,10 +1092,10 @@
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC3" t="n">
         <v>6.6</v>
@@ -1104,17 +1104,17 @@
         <v>6.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF3" t="n">
         <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -1166,13 +1166,13 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.96</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
         <v>1.96</v>
@@ -1187,10 +1187,10 @@
         <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="U4" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="V4" t="n">
         <v>1.4</v>
@@ -1199,116 +1199,116 @@
         <v>1.68</v>
       </c>
       <c r="X4" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AD4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH4" t="n">
         <v>20</v>
       </c>
-      <c r="AE4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>24</v>
-      </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AK4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AL4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.28</v>
+        <v>3.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.26</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.4</v>
+        <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.2</v>
+        <v>3.55</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.08</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.28</v>
+        <v>3.85</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.44</v>
+        <v>4.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.22</v>
+        <v>3.65</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.32</v>
+        <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.48</v>
+        <v>4.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.44</v>
+        <v>4.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.44</v>
+        <v>4.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.56</v>
+        <v>4.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.56</v>
+        <v>14.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.56</v>
+        <v>4.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
@@ -1360,149 +1360,149 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.02</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="T5" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Y5" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Z5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK5" t="n">
         <v>28</v>
       </c>
-      <c r="AA5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AL5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>11</v>
       </c>
-      <c r="AD5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AR5" t="n">
-        <v>2.38</v>
+        <v>7.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.5</v>
+        <v>9.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.24</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.1</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.46</v>
+        <v>8.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.36</v>
+        <v>15.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.26</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.34</v>
+        <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.48</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.48</v>
+        <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.44</v>
+        <v>8.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.48</v>
+        <v>32</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.54</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.6</v>
+        <v>19</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -1536,16 +1536,16 @@
         <v>1.34</v>
       </c>
       <c r="G6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H6" t="n">
         <v>8.6</v>
       </c>
       <c r="I6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K6" t="n">
         <v>6.6</v>
@@ -1557,55 +1557,55 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.8</v>
+        <v>5.7</v>
       </c>
       <c r="O6" t="n">
         <v>1.13</v>
       </c>
       <c r="P6" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S6" t="n">
-        <v>1.46</v>
+        <v>2.06</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
         <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W6" t="n">
         <v>3.4</v>
       </c>
       <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD6" t="n">
         <v>42</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>44</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1614,10 +1614,10 @@
         <v>13.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1629,55 +1629,55 @@
         <v>18.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.9</v>
+        <v>3.15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="AT6" t="n">
         <v>9.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.8</v>
+        <v>10.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.74</v>
+        <v>2.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.75</v>
+        <v>2.58</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.88</v>
+        <v>2.9</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.77</v>
+        <v>2.68</v>
       </c>
       <c r="BC6" t="n">
         <v>10</v>
@@ -1686,17 +1686,17 @@
         <v>21</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="H7" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J7" t="n">
         <v>2.84</v>
@@ -1745,16 +1745,16 @@
         <v>3.25</v>
       </c>
       <c r="L7" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>1.5</v>
+        <v>2.52</v>
       </c>
       <c r="O7" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="P7" t="n">
         <v>1.5</v>
@@ -1763,134 +1763,134 @@
         <v>2.62</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S7" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="T7" t="n">
         <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY7" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>2.54</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>2.68</v>
+        <v>19.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.84</v>
+        <v>7.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.82</v>
+        <v>7.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.84</v>
+        <v>7.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.94</v>
+        <v>8</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.94</v>
+        <v>40</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.94</v>
+        <v>7.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -1921,177 +1921,177 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="H8" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.54</v>
+        <v>3.05</v>
       </c>
       <c r="K8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S8" t="n">
         <v>4.2</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Al-Masry</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nomme Utd</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.32</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M9" t="n">
         <v>1.01</v>
       </c>
-      <c r="K9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trans Narva</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>1.86</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M10" t="n">
         <v>1.01</v>
       </c>
-      <c r="K10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,17 +2489,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>FK Novi Pazar</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2521,159 +2521,159 @@
         <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="Q11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T11" t="n">
         <v>1.01</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Partizan Belgrade</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.8</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.12</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>1.46</v>
+        <v>1.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.22</v>
+        <v>1.24</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hobro</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HB Koge</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>2.14</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.97</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,31 +3076,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,28 +3270,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Aarhus Fremad</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Middelfart</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>1.45</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.24</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>2.12</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>6.6</v>
       </c>
       <c r="J16" t="n">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,31 +3658,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FC Copenhagen</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="G17" t="n">
-        <v>1.71</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>5.4</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3</v>
+        <v>1.92</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,36 +3847,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Rapid Vienna</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.73</v>
+        <v>2.46</v>
       </c>
       <c r="G18" t="n">
-        <v>1.83</v>
+        <v>2.7</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="I18" t="n">
-        <v>6.2</v>
+        <v>2.96</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,36 +4041,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Red Bull Salzburg</t>
+          <t>Aarhus Fremad</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Middelfart</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="G19" t="n">
-        <v>1.76</v>
+        <v>1.45</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="I19" t="n">
-        <v>6.4</v>
+        <v>60</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="K19" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Greek Super League</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,36 +4235,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Hobro</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>HB Koge</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.22</v>
+        <v>1.98</v>
       </c>
       <c r="G20" t="n">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="H20" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,36 +4429,36 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Oliveirense</t>
+          <t>FC Copenhagen</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica B</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.15</v>
+        <v>1.66</v>
       </c>
       <c r="G21" t="n">
-        <v>3.6</v>
+        <v>1.71</v>
       </c>
       <c r="H21" t="n">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
-        <v>2.44</v>
+        <v>5.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.04</v>
+        <v>2.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,66 +4623,66 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Red Bull Salzburg</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.78</v>
+        <v>1.66</v>
       </c>
       <c r="G22" t="n">
-        <v>2.8</v>
+        <v>1.76</v>
       </c>
       <c r="H22" t="n">
-        <v>2.56</v>
+        <v>5</v>
       </c>
       <c r="I22" t="n">
-        <v>2.58</v>
+        <v>6.4</v>
       </c>
       <c r="J22" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K22" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4691,123 +4691,123 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,36 +4817,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Rapid Vienna</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.36</v>
+        <v>1.73</v>
       </c>
       <c r="G23" t="n">
-        <v>2.52</v>
+        <v>1.83</v>
       </c>
       <c r="H23" t="n">
-        <v>2.84</v>
+        <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="K23" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.36</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,36 +5011,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Cukaricki</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="K24" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.54</v>
+        <v>1.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,66 +5205,66 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="G25" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="H25" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J25" t="n">
         <v>3.1</v>
       </c>
       <c r="K25" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5273,123 +5273,123 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,36 +5399,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Oliveirense</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Benfica B</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="G26" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="H26" t="n">
-        <v>2.56</v>
+        <v>2.18</v>
       </c>
       <c r="I26" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="J26" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,14 +5576,14 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,17 +5593,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Zeleznicar Pancevo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Crvena Zvezda</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5622,7 +5622,7 @@
         <v>1.01</v>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5637,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q27" t="n">
         <v>1.01</v>
@@ -5770,14 +5770,14 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,66 +5787,66 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>21</v>
+        <v>2.68</v>
       </c>
       <c r="G28" t="n">
-        <v>23</v>
+        <v>2.7</v>
       </c>
       <c r="H28" t="n">
-        <v>1.17</v>
+        <v>2.66</v>
       </c>
       <c r="I28" t="n">
-        <v>1.18</v>
+        <v>2.68</v>
       </c>
       <c r="J28" t="n">
-        <v>9.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="K28" t="n">
-        <v>10.5</v>
+        <v>3.95</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>8.6</v>
+        <v>4.7</v>
       </c>
       <c r="O28" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="P28" t="n">
-        <v>3.55</v>
+        <v>2.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.37</v>
+        <v>1.79</v>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>1.95</v>
+        <v>2.84</v>
       </c>
       <c r="T28" t="n">
-        <v>2.14</v>
+        <v>1.64</v>
       </c>
       <c r="U28" t="n">
-        <v>1.84</v>
+        <v>2.46</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5855,123 +5855,123 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>44</v>
+        <v>19.5</v>
       </c>
       <c r="Y28" t="n">
         <v>14</v>
       </c>
       <c r="Z28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC28" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AA28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM28" t="n">
         <v>70</v>
       </c>
-      <c r="AC28" t="n">
-        <v>23</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>250</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>75</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>370</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>2.78</v>
+        <v>18.5</v>
       </c>
       <c r="AP28" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="AQ28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT28" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS28" t="n">
+      <c r="AU28" t="n">
         <v>8</v>
       </c>
-      <c r="AT28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>20</v>
-      </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AX28" t="n">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="AY28" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="AZ28" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="BA28" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BB28" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="BC28" t="n">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="BD28" t="n">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="BE28" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="BF28" t="n">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.72</v>
+        <v>16</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,66 +5981,66 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="G29" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="H29" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I29" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="K29" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>2.78</v>
       </c>
       <c r="O29" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.79</v>
+        <v>2.64</v>
       </c>
       <c r="R29" t="n">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="T29" t="n">
-        <v>1.7</v>
+        <v>2.18</v>
       </c>
       <c r="U29" t="n">
-        <v>2.36</v>
+        <v>1.83</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6049,123 +6049,123 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD29" t="n">
         <v>17</v>
       </c>
-      <c r="Y29" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>16</v>
-      </c>
       <c r="AE29" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AF29" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG29" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH29" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AI29" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE29" t="n">
         <v>46</v>
       </c>
-      <c r="AJ29" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO29" t="n">
+      <c r="BF29" t="n">
+        <v>27</v>
+      </c>
+      <c r="BG29" t="n">
         <v>36</v>
       </c>
-      <c r="AP29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>30</v>
-      </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Smouha</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.26</v>
+        <v>3.2</v>
       </c>
       <c r="G30" t="n">
-        <v>1.27</v>
+        <v>3.85</v>
       </c>
       <c r="H30" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="I30" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR30" t="n">
         <v>13</v>
       </c>
-      <c r="J30" t="n">
+      <c r="AS30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT30" t="n">
         <v>7.8</v>
       </c>
-      <c r="K30" t="n">
-        <v>8</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N30" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="P30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>55</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>65</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>470</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AK30" t="n">
+      <c r="AU30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY30" t="n">
         <v>13.5</v>
       </c>
-      <c r="AL30" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>38</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>50</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>95</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>17</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>38</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ30" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BA30" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="BB30" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="BC30" t="n">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="BD30" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="BE30" t="n">
-        <v>36</v>
+        <v>5.2</v>
       </c>
       <c r="BF30" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="BG30" t="n">
-        <v>40</v>
+        <v>4.9</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,36 +6369,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Brondby</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.75</v>
+        <v>2.36</v>
       </c>
       <c r="G31" t="n">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="H31" t="n">
-        <v>3.65</v>
+        <v>2.84</v>
       </c>
       <c r="I31" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="J31" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="K31" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.06</v>
+        <v>1.63</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -6546,14 +6546,14 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,36 +6563,36 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="G32" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="H32" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6607,10 +6607,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -6740,14 +6740,14 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,36 +6757,36 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Barcelona (Ecu)</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.58</v>
+        <v>2.68</v>
       </c>
       <c r="G33" t="n">
-        <v>1.88</v>
+        <v>2.88</v>
       </c>
       <c r="H33" t="n">
-        <v>4.9</v>
+        <v>2.56</v>
       </c>
       <c r="I33" t="n">
-        <v>8.4</v>
+        <v>2.74</v>
       </c>
       <c r="J33" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K33" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -6801,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.64</v>
+        <v>2.26</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6934,201 +6934,1559 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Always Ready</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:58:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Man City</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>22</v>
+      </c>
+      <c r="G35" t="n">
+        <v>23</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J35" t="n">
+        <v>10</v>
+      </c>
+      <c r="K35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N35" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>80</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>240</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>85</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>360</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>36</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>55</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>110</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>50</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>36</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>150</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>110</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>95</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>110</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:58:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:58:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H37" t="n">
+        <v>12</v>
+      </c>
+      <c r="I37" t="n">
+        <v>13</v>
+      </c>
+      <c r="J37" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K37" t="n">
+        <v>8</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N37" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>450</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>990</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>38</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:58:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>17:30:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:58:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Real Potosi</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:58:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I40" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K40" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:58:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>20:20:00</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Ind Medellin</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Boyaca Chico</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="G34" t="n">
+      <c r="F41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G41" t="n">
         <v>1.36</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H41" t="n">
         <v>12.5</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I41" t="n">
         <v>18</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J41" t="n">
         <v>5.3</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K41" t="n">
         <v>6.4</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="Q41" t="n">
         <v>1.72</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2026-04-20 10:44:51</t>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
@@ -766,7 +766,7 @@
         <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
         <v>4.8</v>
@@ -796,7 +796,7 @@
         <v>1.6</v>
       </c>
       <c r="S2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
         <v>1.79</v>
@@ -898,7 +898,7 @@
         <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
         <v>11.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O3" t="n">
         <v>1.26</v>
@@ -984,7 +984,7 @@
         <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R3" t="n">
         <v>1.42</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
         <v>1.73</v>
       </c>
       <c r="U4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
         <v>1.4</v>
@@ -1274,7 +1274,7 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX4" t="n">
         <v>12</v>
@@ -1283,10 +1283,10 @@
         <v>3.7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB4" t="n">
         <v>4.5</v>
@@ -1295,7 +1295,7 @@
         <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE4" t="n">
         <v>4.8</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
         <v>3.95</v>
       </c>
       <c r="O5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
@@ -1441,7 +1441,7 @@
         <v>80</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO5" t="n">
         <v>32</v>
@@ -1453,10 +1453,10 @@
         <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
         <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
@@ -1480,19 +1480,19 @@
         <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BD5" t="n">
         <v>32</v>
       </c>
       <c r="BE5" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF5" t="n">
         <v>7.6</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -1557,10 +1557,10 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P6" t="n">
         <v>2.8</v>
@@ -1653,7 +1653,7 @@
         <v>3.15</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.4</v>
+        <v>2.64</v>
       </c>
       <c r="AU6" t="n">
         <v>10.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I7" t="n">
         <v>3.15</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -1951,10 +1951,10 @@
         <v>1.48</v>
       </c>
       <c r="P8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="R8" t="n">
         <v>1.21</v>
@@ -1984,7 +1984,7 @@
         <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB8" t="n">
         <v>11</v>
@@ -1996,7 +1996,7 @@
         <v>16</v>
       </c>
       <c r="AE8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF8" t="n">
         <v>23</v>
@@ -2062,29 +2062,29 @@
         <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB8" t="n">
         <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF8" t="n">
         <v>4</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G9" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
-        <v>2.92</v>
+        <v>1.09</v>
       </c>
       <c r="K9" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>1.47</v>
@@ -2157,16 +2157,16 @@
         <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
         <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X9" t="n">
         <v>9.800000000000001</v>
@@ -2232,7 +2232,7 @@
         <v>21</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AT9" t="n">
         <v>5.9</v>
@@ -2256,7 +2256,7 @@
         <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BB9" t="n">
         <v>4.7</v>
@@ -2271,14 +2271,14 @@
         <v>4.3</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.1</v>
+        <v>23</v>
       </c>
       <c r="BG9" t="n">
         <v>4.3</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
         <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="P11" t="n">
         <v>1.08</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G12" t="n">
         <v>2.8</v>
       </c>
       <c r="H12" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
@@ -2712,16 +2712,16 @@
         <v>2.4</v>
       </c>
       <c r="K12" t="n">
-        <v>7.4</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="O12" t="n">
         <v>1.25</v>
@@ -2730,13 +2730,13 @@
         <v>1.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R12" t="n">
         <v>1.08</v>
       </c>
       <c r="S12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -3106,13 +3106,13 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P14" t="n">
         <v>2.04</v>
@@ -3121,134 +3121,134 @@
         <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="T14" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="U14" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="V14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W14" t="n">
         <v>1.59</v>
       </c>
       <c r="X14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z14" t="n">
         <v>23</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC14" t="n">
         <v>19</v>
       </c>
-      <c r="Z14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="BD14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG14" t="n">
         <v>18.5</v>
       </c>
-      <c r="AE14" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -4058,16 +4058,16 @@
         <v>1.66</v>
       </c>
       <c r="G19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
         <v>5.4</v>
       </c>
       <c r="J19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K19" t="n">
         <v>5</v>
@@ -4079,10 +4079,10 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P19" t="n">
         <v>2.7</v>
@@ -4091,134 +4091,134 @@
         <v>1.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="U19" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="V19" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X19" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="Y19" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="Z19" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB19" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AC19" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AI19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM19" t="n">
         <v>65</v>
       </c>
-      <c r="AJ19" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>85</v>
-      </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.04</v>
+        <v>8.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>2.04</v>
+        <v>8.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.08</v>
+        <v>9.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.16</v>
+        <v>11</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.94</v>
+        <v>12</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.89</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV19" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.94</v>
+        <v>12</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.89</v>
+        <v>9.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.98</v>
+        <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>29</v>
+        <v>9.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.99</v>
+        <v>16</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.97</v>
+        <v>13.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>17.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE19" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.16</v>
+        <v>5.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H20" t="n">
         <v>2.7</v>
       </c>
       <c r="I20" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J20" t="n">
         <v>3.65</v>
@@ -4273,13 +4273,13 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O20" t="n">
         <v>1.21</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
         <v>1.67</v>
@@ -4291,10 +4291,10 @@
         <v>2.46</v>
       </c>
       <c r="T20" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="U20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V20" t="n">
         <v>1.51</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -4479,10 +4479,10 @@
         <v>1.89</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -4551,7 +4551,7 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="AQ21" t="n">
         <v>9.199999999999999</v>
@@ -4560,7 +4560,7 @@
         <v>17.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="AT21" t="n">
         <v>6.2</v>
@@ -4572,7 +4572,7 @@
         <v>10</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="AX21" t="n">
         <v>8.199999999999999</v>
@@ -4584,7 +4584,7 @@
         <v>11</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="BB21" t="n">
         <v>15</v>
@@ -4593,20 +4593,20 @@
         <v>13</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="G22" t="n">
         <v>2.12</v>
@@ -4652,7 +4652,7 @@
         <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>5.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4661,13 +4661,13 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O22" t="n">
         <v>1.44</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q22" t="n">
         <v>2.2</v>
@@ -4685,7 +4685,7 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W22" t="n">
         <v>1.89</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="G23" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="I23" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="J23" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="K23" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4873,16 +4873,16 @@
         <v>2.58</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W23" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="X23" t="n">
         <v>32</v>
@@ -4933,68 +4933,68 @@
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.88</v>
+        <v>2.24</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.89</v>
+        <v>2.26</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.06</v>
+        <v>2.52</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.96</v>
+        <v>2.36</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.02</v>
+        <v>2.46</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>2.12</v>
+        <v>5.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5067,7 @@
         <v>2.84</v>
       </c>
       <c r="T24" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U24" t="n">
         <v>1.87</v>
@@ -5127,68 +5127,68 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="AQ24" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.32</v>
+        <v>2.74</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="AV24" t="n">
         <v>14.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="AX24" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="AY24" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="BF24" t="n">
-        <v>2.42</v>
+        <v>7.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>2.42</v>
+        <v>2.86</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="G25" t="n">
         <v>2.42</v>
       </c>
       <c r="H25" t="n">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="I25" t="n">
         <v>4.5</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
         <v>3.35</v>
       </c>
       <c r="H26" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I26" t="n">
         <v>2.5</v>
@@ -5443,7 +5443,7 @@
         <v>1.29</v>
       </c>
       <c r="P26" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q26" t="n">
         <v>1.9</v>
@@ -5503,7 +5503,7 @@
         <v>50</v>
       </c>
       <c r="AJ26" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK26" t="n">
         <v>48</v>
@@ -5512,7 +5512,7 @@
         <v>60</v>
       </c>
       <c r="AM26" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
         <v>1000</v>
@@ -5521,46 +5521,46 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="AQ26" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AR26" t="n">
         <v>11.5</v>
       </c>
       <c r="AS26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BB26" t="n">
         <v>2.66</v>
       </c>
-      <c r="AT26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX26" t="n">
+      <c r="BC26" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>24</v>
       </c>
       <c r="BD26" t="n">
         <v>30</v>
@@ -5569,14 +5569,14 @@
         <v>2.76</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="BG26" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -5631,16 +5631,16 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="O27" t="n">
         <v>1.16</v>
       </c>
       <c r="P27" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R27" t="n">
         <v>1.58</v>
@@ -5652,7 +5652,7 @@
         <v>2.14</v>
       </c>
       <c r="U27" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="V27" t="n">
         <v>1.05</v>
@@ -5709,68 +5709,68 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.85</v>
+        <v>2.94</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.89</v>
+        <v>3.05</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.94</v>
+        <v>3.15</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.94</v>
+        <v>3.15</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.69</v>
+        <v>2.58</v>
       </c>
       <c r="AU27" t="n">
         <v>12.5</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.94</v>
+        <v>3.15</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.64</v>
+        <v>2.46</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.75</v>
+        <v>2.72</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.88</v>
+        <v>3.05</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.94</v>
+        <v>3.15</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.67</v>
+        <v>2.52</v>
       </c>
       <c r="BC27" t="n">
         <v>10</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.89</v>
+        <v>3.05</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.94</v>
+        <v>3.15</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.94</v>
+        <v>3.1</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.94</v>
+        <v>3.15</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -5825,13 +5825,13 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="O28" t="n">
         <v>1.24</v>
       </c>
       <c r="P28" t="n">
-        <v>1.42</v>
+        <v>2.12</v>
       </c>
       <c r="Q28" t="n">
         <v>1.24</v>
@@ -5879,13 +5879,13 @@
         <v>30</v>
       </c>
       <c r="AF28" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI28" t="n">
         <v>48</v>
@@ -5909,62 +5909,62 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AR28" t="n">
         <v>2.14</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="AS28" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV28" t="n">
         <v>2.06</v>
       </c>
-      <c r="AR28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AW28" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AX28" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BB28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BC28" t="n">
         <v>2.28</v>
       </c>
-      <c r="BC28" t="n">
-        <v>2.26</v>
-      </c>
       <c r="BD28" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BF28" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="G29" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H29" t="n">
         <v>1.09</v>
@@ -6025,7 +6025,7 @@
         <v>1.2</v>
       </c>
       <c r="P29" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q29" t="n">
         <v>1.64</v>
@@ -6037,7 +6037,7 @@
         <v>2.58</v>
       </c>
       <c r="T29" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U29" t="n">
         <v>2.34</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -6198,10 +6198,10 @@
         <v>16.5</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="K30" t="n">
         <v>9.4</v>
@@ -6219,7 +6219,7 @@
         <v>1.11</v>
       </c>
       <c r="P30" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q30" t="n">
         <v>1.35</v>
@@ -6228,7 +6228,7 @@
         <v>2.06</v>
       </c>
       <c r="S30" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="T30" t="n">
         <v>1.92</v>
@@ -6237,13 +6237,13 @@
         <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W30" t="n">
         <v>6</v>
       </c>
       <c r="X30" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
         <v>90</v>
@@ -6255,7 +6255,7 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC30" t="n">
         <v>21</v>
@@ -6285,40 +6285,40 @@
         <v>13</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT30" t="n">
         <v>13</v>
       </c>
       <c r="AU30" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AV30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX30" t="n">
         <v>9.199999999999999</v>
@@ -6327,10 +6327,10 @@
         <v>11</v>
       </c>
       <c r="AZ30" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BA30" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB30" t="n">
         <v>9.199999999999999</v>
@@ -6342,17 +6342,17 @@
         <v>24</v>
       </c>
       <c r="BE30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF30" t="n">
         <v>2.88</v>
       </c>
       <c r="BG30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.13</v>
+        <v>9.4</v>
       </c>
       <c r="G31" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H31" t="n">
         <v>1.19</v>
@@ -6395,158 +6395,158 @@
         <v>1.25</v>
       </c>
       <c r="J31" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="K31" t="n">
         <v>9</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M31" t="n">
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="O31" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P31" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="R31" t="n">
-        <v>1.08</v>
+        <v>1.75</v>
       </c>
       <c r="S31" t="n">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X31" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB31" t="n">
         <v>4.6</v>
       </c>
-      <c r="W31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BC31" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -6577,170 +6577,170 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="H32" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="I32" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="J32" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K32" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O32" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="P32" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q32" t="n">
         <v>1.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S32" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V32" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="W32" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X32" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z32" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF32" t="n">
         <v>22</v>
       </c>
-      <c r="AA32" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -6795,16 +6795,16 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="O33" t="n">
         <v>1.43</v>
       </c>
       <c r="P33" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R33" t="n">
         <v>1.18</v>
@@ -6813,10 +6813,10 @@
         <v>3.85</v>
       </c>
       <c r="T33" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="U33" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="V33" t="n">
         <v>1.32</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -6968,13 +6968,13 @@
         <v>2.68</v>
       </c>
       <c r="G34" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H34" t="n">
         <v>2.66</v>
       </c>
       <c r="I34" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J34" t="n">
         <v>3.9</v>
@@ -6998,10 +6998,10 @@
         <v>2.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R34" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S34" t="n">
         <v>2.84</v>
@@ -7013,19 +7013,19 @@
         <v>2.44</v>
       </c>
       <c r="V34" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W34" t="n">
         <v>1.58</v>
       </c>
       <c r="X34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y34" t="n">
         <v>14</v>
       </c>
       <c r="Z34" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA34" t="n">
         <v>40</v>
@@ -7040,7 +7040,7 @@
         <v>12</v>
       </c>
       <c r="AE34" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF34" t="n">
         <v>19.5</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
         <v>1.81</v>
       </c>
       <c r="G35" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H35" t="n">
         <v>3.7</v>
@@ -7195,7 +7195,7 @@
         <v>1.48</v>
       </c>
       <c r="R35" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S35" t="n">
         <v>2.18</v>
@@ -7210,7 +7210,7 @@
         <v>1.22</v>
       </c>
       <c r="W35" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7267,52 +7267,52 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF35" t="n">
         <v>1.01</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -7356,19 +7356,19 @@
         <v>1.64</v>
       </c>
       <c r="G36" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H36" t="n">
-        <v>1.98</v>
+        <v>3.35</v>
       </c>
       <c r="I36" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
         <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -7377,7 +7377,7 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="O36" t="n">
         <v>1.12</v>
@@ -7389,7 +7389,7 @@
         <v>1.38</v>
       </c>
       <c r="R36" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S36" t="n">
         <v>1.94</v>
@@ -7401,10 +7401,10 @@
         <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W36" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7461,52 +7461,52 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF36" t="n">
         <v>1.01</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -7547,16 +7547,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G37" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I37" t="n">
         <v>3.95</v>
-      </c>
-      <c r="I37" t="n">
-        <v>4</v>
       </c>
       <c r="J37" t="n">
         <v>3.1</v>
@@ -7565,16 +7565,16 @@
         <v>3.15</v>
       </c>
       <c r="L37" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
         <v>1.13</v>
       </c>
       <c r="N37" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O37" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P37" t="n">
         <v>1.58</v>
@@ -7586,7 +7586,7 @@
         <v>1.21</v>
       </c>
       <c r="S37" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T37" t="n">
         <v>2.16</v>
@@ -7598,10 +7598,10 @@
         <v>1.33</v>
       </c>
       <c r="W37" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X37" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y37" t="n">
         <v>10.5</v>
@@ -7613,13 +7613,13 @@
         <v>85</v>
       </c>
       <c r="AB37" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC37" t="n">
         <v>7</v>
       </c>
       <c r="AD37" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE37" t="n">
         <v>65</v>
@@ -7637,7 +7637,7 @@
         <v>85</v>
       </c>
       <c r="AJ37" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK37" t="n">
         <v>32</v>
@@ -7652,7 +7652,7 @@
         <v>32</v>
       </c>
       <c r="AO37" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
         <v>8.199999999999999</v>
@@ -7673,7 +7673,7 @@
         <v>6.6</v>
       </c>
       <c r="AV37" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW37" t="n">
         <v>55</v>
@@ -7688,13 +7688,13 @@
         <v>21</v>
       </c>
       <c r="BA37" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BB37" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC37" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD37" t="n">
         <v>50</v>
@@ -7706,11 +7706,11 @@
         <v>27</v>
       </c>
       <c r="BG37" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>3.2</v>
       </c>
       <c r="G38" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H38" t="n">
         <v>2.5</v>
@@ -7759,16 +7759,16 @@
         <v>3.2</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P38" t="n">
         <v>1.12</v>
@@ -7777,10 +7777,10 @@
         <v>2.52</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T38" t="n">
         <v>2.14</v>
@@ -7789,13 +7789,13 @@
         <v>1.7</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X38" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y38" t="n">
         <v>8.6</v>
@@ -7852,13 +7852,13 @@
         <v>6.6</v>
       </c>
       <c r="AQ38" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AR38" t="n">
         <v>13</v>
       </c>
       <c r="AS38" t="n">
-        <v>4.9</v>
+        <v>34</v>
       </c>
       <c r="AT38" t="n">
         <v>7.8</v>
@@ -7870,7 +7870,7 @@
         <v>11.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AX38" t="n">
         <v>18.5</v>
@@ -7882,7 +7882,7 @@
         <v>20</v>
       </c>
       <c r="BA38" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BB38" t="n">
         <v>5.1</v>
@@ -7891,20 +7891,20 @@
         <v>5</v>
       </c>
       <c r="BD38" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE38" t="n">
         <v>5.2</v>
       </c>
-      <c r="BE38" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BF38" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BG38" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -7953,152 +7953,152 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R39" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -8135,164 +8135,164 @@
         <v>2.64</v>
       </c>
       <c r="H40" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I40" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J40" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K40" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P40" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q40" t="n">
         <v>1.6</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG40" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
         <v>2.84</v>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J41" t="n">
         <v>3.8</v>
@@ -8341,16 +8341,16 @@
         <v>4.4</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P41" t="n">
         <v>2.36</v>
@@ -8359,134 +8359,134 @@
         <v>1.63</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BG41" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="G42" t="n">
         <v>7</v>
@@ -8526,7 +8526,7 @@
         <v>1.82</v>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="J42" t="n">
         <v>3.3</v>
@@ -8535,16 +8535,16 @@
         <v>950</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P42" t="n">
         <v>1.54</v>
@@ -8553,134 +8553,134 @@
         <v>2.02</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -8726,155 +8726,155 @@
         <v>3.65</v>
       </c>
       <c r="K43" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P43" t="n">
         <v>2.24</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BG43" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
         <v>1.04</v>
       </c>
       <c r="G44" t="n">
-        <v>1000</v>
+        <v>1.22</v>
       </c>
       <c r="H44" t="n">
         <v>1.04</v>
@@ -8923,152 +8923,152 @@
         <v>1000</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="P44" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -9099,10 +9099,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G45" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H45" t="n">
         <v>1.16</v>
@@ -9117,13 +9117,13 @@
         <v>10.5</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M45" t="n">
         <v>1.02</v>
       </c>
       <c r="N45" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="O45" t="n">
         <v>1.12</v>
@@ -9135,22 +9135,22 @@
         <v>1.38</v>
       </c>
       <c r="R45" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S45" t="n">
         <v>1.96</v>
       </c>
       <c r="T45" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U45" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X45" t="n">
         <v>44</v>
@@ -9168,7 +9168,7 @@
         <v>75</v>
       </c>
       <c r="AC45" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AD45" t="n">
         <v>13</v>
@@ -9183,7 +9183,7 @@
         <v>80</v>
       </c>
       <c r="AH45" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AI45" t="n">
         <v>44</v>
@@ -9195,7 +9195,7 @@
         <v>360</v>
       </c>
       <c r="AL45" t="n">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AM45" t="n">
         <v>1000</v>
@@ -9234,7 +9234,7 @@
         <v>110</v>
       </c>
       <c r="AY45" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AZ45" t="n">
         <v>36</v>
@@ -9249,20 +9249,20 @@
         <v>110</v>
       </c>
       <c r="BD45" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BE45" t="n">
         <v>90</v>
       </c>
       <c r="BF45" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BG45" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G46" t="n">
         <v>2.12</v>
@@ -9311,7 +9311,7 @@
         <v>3.8</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M46" t="n">
         <v>1.06</v>
@@ -9341,13 +9341,13 @@
         <v>2.36</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="X46" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y46" t="n">
         <v>16.5</v>
@@ -9362,22 +9362,22 @@
         <v>11.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD46" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE46" t="n">
         <v>40</v>
       </c>
       <c r="AF46" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG46" t="n">
         <v>10.5</v>
       </c>
       <c r="AH46" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI46" t="n">
         <v>46</v>
@@ -9386,7 +9386,7 @@
         <v>25</v>
       </c>
       <c r="AK46" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL46" t="n">
         <v>32</v>
@@ -9398,46 +9398,46 @@
         <v>13</v>
       </c>
       <c r="AO46" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP46" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ46" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AS46" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AT46" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU46" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV46" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AX46" t="n">
         <v>13</v>
       </c>
       <c r="AY46" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ46" t="n">
         <v>14.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="BB46" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC46" t="n">
         <v>18.5</v>
@@ -9446,17 +9446,17 @@
         <v>29</v>
       </c>
       <c r="BE46" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BF46" t="n">
         <v>12</v>
       </c>
       <c r="BG46" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
         <v>1.27</v>
       </c>
       <c r="H47" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I47" t="n">
         <v>13</v>
@@ -9505,13 +9505,13 @@
         <v>8</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M47" t="n">
         <v>1.02</v>
       </c>
       <c r="N47" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O47" t="n">
         <v>1.11</v>
@@ -9526,7 +9526,7 @@
         <v>2.12</v>
       </c>
       <c r="S47" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="T47" t="n">
         <v>1.75</v>
@@ -9535,13 +9535,13 @@
         <v>2.26</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="X47" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Y47" t="n">
         <v>65</v>
@@ -9553,46 +9553,46 @@
         <v>450</v>
       </c>
       <c r="AB47" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC47" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AD47" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AE47" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF47" t="n">
         <v>11.5</v>
       </c>
       <c r="AG47" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK47" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH47" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AL47" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AM47" t="n">
-        <v>990</v>
+        <v>100</v>
       </c>
       <c r="AN47" t="n">
         <v>3</v>
       </c>
       <c r="AO47" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP47" t="n">
         <v>38</v>
@@ -9604,10 +9604,10 @@
         <v>42</v>
       </c>
       <c r="AS47" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AT47" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU47" t="n">
         <v>17</v>
@@ -9616,7 +9616,7 @@
         <v>38</v>
       </c>
       <c r="AW47" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX47" t="n">
         <v>10.5</v>
@@ -9625,10 +9625,10 @@
         <v>11</v>
       </c>
       <c r="AZ47" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA47" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB47" t="n">
         <v>10.5</v>
@@ -9637,20 +9637,20 @@
         <v>12</v>
       </c>
       <c r="BD47" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BE47" t="n">
         <v>36</v>
       </c>
       <c r="BF47" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="BG47" t="n">
         <v>40</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="G48" t="n">
         <v>2.6</v>
@@ -9696,7 +9696,7 @@
         <v>3.05</v>
       </c>
       <c r="K48" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -10081,7 +10081,7 @@
         <v>8.4</v>
       </c>
       <c r="J50" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K50" t="n">
         <v>5.1</v>
@@ -10102,7 +10102,7 @@
         <v>1.64</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
@@ -766,7 +766,7 @@
         <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J2" t="n">
         <v>4.8</v>
@@ -805,7 +805,7 @@
         <v>2.14</v>
       </c>
       <c r="V2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W2" t="n">
         <v>2.98</v>
@@ -859,7 +859,7 @@
         <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AO2" t="n">
         <v>110</v>
@@ -871,10 +871,10 @@
         <v>4.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT2" t="n">
         <v>9</v>
@@ -886,7 +886,7 @@
         <v>19.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX2" t="n">
         <v>8.800000000000001</v>
@@ -898,7 +898,7 @@
         <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB2" t="n">
         <v>11.5</v>
@@ -910,17 +910,17 @@
         <v>4.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>3.8</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>2.12</v>
@@ -978,7 +978,7 @@
         <v>3.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
         <v>2.12</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G4" t="n">
         <v>2.46</v>
       </c>
       <c r="H4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I4" t="n">
         <v>3.5</v>
@@ -1160,7 +1160,7 @@
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1196,7 +1196,7 @@
         <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="X4" t="n">
         <v>17.5</v>
@@ -1253,7 +1253,7 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AQ4" t="n">
         <v>10</v>
@@ -1262,53 +1262,53 @@
         <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="AU4" t="n">
         <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX4" t="n">
         <v>12</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB4" t="n">
         <v>4.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>19</v>
+        <v>4.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE4" t="n">
         <v>4.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>14</v>
+        <v>4.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
         <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS5" t="n">
         <v>8.6</v>
@@ -1489,20 +1489,20 @@
         <v>7.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG5" t="n">
         <v>19</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -1566,19 +1566,19 @@
         <v>2.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S6" t="n">
         <v>2.06</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="V6" t="n">
         <v>1.1</v>
@@ -1644,16 +1644,16 @@
         <v>3.15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AU6" t="n">
         <v>10.5</v>
@@ -1662,31 +1662,31 @@
         <v>3</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AX6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AY6" t="n">
         <v>2.6</v>
       </c>
-      <c r="AY6" t="n">
-        <v>2.58</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BC6" t="n">
-        <v>10</v>
+        <v>2.78</v>
       </c>
       <c r="BD6" t="n">
         <v>21</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BF6" t="n">
         <v>3.15</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I7" t="n">
         <v>3.15</v>
@@ -1742,7 +1742,7 @@
         <v>2.86</v>
       </c>
       <c r="K7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1772,7 +1772,7 @@
         <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V7" t="n">
         <v>1.47</v>
@@ -1832,7 +1832,7 @@
         <v>60</v>
       </c>
       <c r="AO7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP7" t="n">
         <v>7.2</v>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX7" t="n">
         <v>15</v>
@@ -1877,10 +1877,10 @@
         <v>7.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF7" t="n">
         <v>40</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="G8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.05</v>
       </c>
       <c r="K8" t="n">
         <v>3.35</v>
@@ -1945,7 +1945,7 @@
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
         <v>1.48</v>
@@ -1954,10 +1954,10 @@
         <v>1.61</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="R8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
         <v>4.7</v>
@@ -1969,10 +1969,10 @@
         <v>1.86</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
         <v>12</v>
@@ -1999,22 +1999,22 @@
         <v>48</v>
       </c>
       <c r="AF8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
         <v>75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL8" t="n">
         <v>75</v>
@@ -2023,7 +2023,7 @@
         <v>180</v>
       </c>
       <c r="AN8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO8" t="n">
         <v>55</v>
@@ -2038,7 +2038,7 @@
         <v>13</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT8" t="n">
         <v>7.8</v>
@@ -2050,7 +2050,7 @@
         <v>11</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AX8" t="n">
         <v>13.5</v>
@@ -2062,29 +2062,29 @@
         <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G10" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="H10" t="n">
         <v>4.6</v>
@@ -2345,7 +2345,7 @@
         <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
         <v>2.74</v>
@@ -2354,13 +2354,13 @@
         <v>1.61</v>
       </c>
       <c r="U10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
         <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X10" t="n">
         <v>28</v>
@@ -2369,13 +2369,13 @@
         <v>29</v>
       </c>
       <c r="Z10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC10" t="n">
         <v>13.5</v>
@@ -2387,7 +2387,7 @@
         <v>85</v>
       </c>
       <c r="AF10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG10" t="n">
         <v>15</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AQ10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>2.4</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD10" t="n">
         <v>2.5</v>
       </c>
-      <c r="AS10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2.46</v>
-      </c>
       <c r="BE10" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BF10" t="n">
         <v>6.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="G11" t="n">
         <v>2.44</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -2700,10 +2700,10 @@
         <v>2.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
@@ -2724,19 +2724,19 @@
         <v>1.01</v>
       </c>
       <c r="O12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P12" t="n">
         <v>1.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R12" t="n">
         <v>1.08</v>
       </c>
       <c r="S12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2748,7 +2748,7 @@
         <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G14" t="n">
         <v>2.68</v>
@@ -3097,7 +3097,7 @@
         <v>3.25</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
         <v>3.8</v>
@@ -3115,13 +3115,13 @@
         <v>1.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
         <v>2.92</v>
@@ -3139,46 +3139,46 @@
         <v>1.59</v>
       </c>
       <c r="X14" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="Z14" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AA14" t="n">
         <v>60</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AF14" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ14" t="n">
         <v>38</v>
       </c>
       <c r="AK14" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL14" t="n">
         <v>44</v>
@@ -3187,58 +3187,58 @@
         <v>90</v>
       </c>
       <c r="AN14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AR14" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="AT14" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AU14" t="n">
         <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="AX14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="BC14" t="n">
         <v>19</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.6</v>
+        <v>3.95</v>
       </c>
       <c r="BE14" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="BF14" t="n">
         <v>13.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -3864,10 +3864,10 @@
         <v>1.3</v>
       </c>
       <c r="G18" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="H18" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="I18" t="n">
         <v>60</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I19" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J19" t="n">
         <v>4.4</v>
@@ -4088,13 +4088,13 @@
         <v>2.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R19" t="n">
         <v>1.69</v>
       </c>
       <c r="S19" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="T19" t="n">
         <v>1.58</v>
@@ -4106,13 +4106,13 @@
         <v>1.23</v>
       </c>
       <c r="W19" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X19" t="n">
         <v>29</v>
       </c>
       <c r="Y19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z19" t="n">
         <v>44</v>
@@ -4127,7 +4127,7 @@
         <v>11.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE19" t="n">
         <v>55</v>
@@ -4163,16 +4163,16 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ19" t="n">
         <v>8.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT19" t="n">
         <v>12</v>
@@ -4181,7 +4181,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV19" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW19" t="n">
         <v>10</v>
@@ -4196,7 +4196,7 @@
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB19" t="n">
         <v>16</v>
@@ -4205,20 +4205,20 @@
         <v>13.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF19" t="n">
         <v>5.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
         <v>1.67</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
         <v>2.46</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G21" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H21" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I21" t="n">
         <v>4.7</v>
@@ -4485,7 +4485,7 @@
         <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U21" t="n">
         <v>1.99</v>
@@ -4494,7 +4494,7 @@
         <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="G22" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="H22" t="n">
         <v>4.1</v>
       </c>
       <c r="I22" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="K22" t="n">
-        <v>5.7</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4688,7 +4688,7 @@
         <v>1.19</v>
       </c>
       <c r="W22" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>1.89</v>
       </c>
       <c r="H23" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="I23" t="n">
         <v>7.4</v>
@@ -4846,7 +4846,7 @@
         <v>3.75</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4867,10 +4867,10 @@
         <v>1.56</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S23" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="T23" t="n">
         <v>1.59</v>
@@ -4939,7 +4939,7 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.4</v>
+        <v>13</v>
       </c>
       <c r="AQ23" t="n">
         <v>2.4</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="G24" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="I24" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K24" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
         <v>1.33</v>
@@ -5049,13 +5049,13 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="O24" t="n">
         <v>1.27</v>
       </c>
       <c r="P24" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="Q24" t="n">
         <v>1.82</v>
@@ -5073,13 +5073,13 @@
         <v>1.87</v>
       </c>
       <c r="V24" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="W24" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="X24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y24" t="n">
         <v>26</v>
@@ -5136,59 +5136,59 @@
         <v>2.56</v>
       </c>
       <c r="AQ24" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AV24" t="n">
         <v>14.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AX24" t="n">
         <v>2.44</v>
       </c>
       <c r="AY24" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AZ24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BB24" t="n">
         <v>2.62</v>
       </c>
-      <c r="BA24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>2.6</v>
-      </c>
       <c r="BC24" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BF24" t="n">
         <v>7.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G25" t="n">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="H25" t="n">
         <v>2.58</v>
@@ -5231,7 +5231,7 @@
         <v>4.5</v>
       </c>
       <c r="J25" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="K25" t="n">
         <v>950</v>
@@ -5243,22 +5243,22 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.92</v>
+        <v>1.08</v>
       </c>
       <c r="O25" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P25" t="n">
-        <v>1.92</v>
+        <v>1.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.86</v>
+        <v>1.31</v>
       </c>
       <c r="R25" t="n">
         <v>1.08</v>
       </c>
       <c r="S25" t="n">
-        <v>1.86</v>
+        <v>1.31</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -5270,7 +5270,7 @@
         <v>1.28</v>
       </c>
       <c r="W25" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -5413,19 +5413,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
         <v>3.35</v>
       </c>
       <c r="H26" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I26" t="n">
         <v>2.5</v>
       </c>
       <c r="J26" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K26" t="n">
         <v>3.75</v>
@@ -5434,7 +5434,7 @@
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N26" t="n">
         <v>2.02</v>
@@ -5533,7 +5533,7 @@
         <v>2.6</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AU26" t="n">
         <v>2.18</v>
@@ -5551,7 +5551,7 @@
         <v>2.4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BA26" t="n">
         <v>2.62</v>
@@ -5560,7 +5560,7 @@
         <v>2.66</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BD26" t="n">
         <v>30</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
         <v>2.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R27" t="n">
         <v>1.58</v>
@@ -5715,7 +5715,7 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="AQ27" t="n">
         <v>3.05</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -5825,13 +5825,13 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>2.12</v>
+        <v>1.43</v>
       </c>
       <c r="O28" t="n">
         <v>1.24</v>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>1.42</v>
       </c>
       <c r="Q28" t="n">
         <v>1.24</v>
@@ -5840,13 +5840,13 @@
         <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
         <v>1.79</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -5998,19 +5998,19 @@
         <v>2.84</v>
       </c>
       <c r="G29" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H29" t="n">
-        <v>1.09</v>
+        <v>2.32</v>
       </c>
       <c r="I29" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="J29" t="n">
         <v>1.09</v>
       </c>
       <c r="K29" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -6022,7 +6022,7 @@
         <v>1.02</v>
       </c>
       <c r="O29" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P29" t="n">
         <v>1.46</v>
@@ -6043,10 +6043,10 @@
         <v>2.34</v>
       </c>
       <c r="V29" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>1.19</v>
       </c>
       <c r="G30" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="H30" t="n">
         <v>16.5</v>
@@ -6219,7 +6219,7 @@
         <v>1.11</v>
       </c>
       <c r="P30" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q30" t="n">
         <v>1.35</v>
@@ -6240,7 +6240,7 @@
         <v>1.06</v>
       </c>
       <c r="W30" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6258,10 +6258,10 @@
         <v>16.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
@@ -6282,7 +6282,7 @@
         <v>10.5</v>
       </c>
       <c r="AK30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AL30" t="n">
         <v>36</v>
@@ -6297,7 +6297,7 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ30" t="n">
         <v>13</v>
@@ -6306,7 +6306,7 @@
         <v>13.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT30" t="n">
         <v>13</v>
@@ -6315,10 +6315,10 @@
         <v>19</v>
       </c>
       <c r="AV30" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX30" t="n">
         <v>9.199999999999999</v>
@@ -6336,7 +6336,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BC30" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD30" t="n">
         <v>24</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>9.4</v>
+        <v>1.49</v>
       </c>
       <c r="G31" t="n">
         <v>20</v>
@@ -6542,11 +6542,11 @@
         <v>4.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
         <v>1.27</v>
       </c>
       <c r="P32" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q32" t="n">
         <v>1.8</v>
@@ -6616,10 +6616,10 @@
         <v>1.39</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T32" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="U32" t="n">
         <v>2.2</v>
@@ -6628,7 +6628,7 @@
         <v>1.63</v>
       </c>
       <c r="W32" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X32" t="n">
         <v>18.5</v>
@@ -6721,7 +6721,7 @@
         <v>6.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="BC32" t="n">
         <v>6.8</v>
@@ -6730,7 +6730,7 @@
         <v>30</v>
       </c>
       <c r="BE32" t="n">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="BF32" t="n">
         <v>22</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
         <v>3.1</v>
       </c>
       <c r="K33" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -6795,16 +6795,16 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="O33" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="P33" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R33" t="n">
         <v>1.18</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -6965,13 +6965,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G34" t="n">
         <v>2.72</v>
       </c>
       <c r="H34" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I34" t="n">
         <v>2.68</v>
@@ -6983,28 +6983,28 @@
         <v>3.95</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M34" t="n">
         <v>1.05</v>
       </c>
       <c r="N34" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O34" t="n">
         <v>1.25</v>
       </c>
       <c r="P34" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R34" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S34" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="T34" t="n">
         <v>1.65</v>
@@ -7073,7 +7073,7 @@
         <v>19</v>
       </c>
       <c r="AP34" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ34" t="n">
         <v>12.5</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -7159,13 +7159,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="G35" t="n">
         <v>2.14</v>
       </c>
       <c r="H35" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I35" t="n">
         <v>5.6</v>
@@ -7174,7 +7174,7 @@
         <v>3.5</v>
       </c>
       <c r="K35" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
         <v>6</v>
       </c>
       <c r="J36" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K36" t="n">
         <v>11.5</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
         <v>3.9</v>
       </c>
       <c r="I37" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
         <v>3.1</v>
@@ -7565,7 +7565,7 @@
         <v>3.15</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M37" t="n">
         <v>1.13</v>
@@ -7580,13 +7580,13 @@
         <v>1.58</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="R37" t="n">
         <v>1.21</v>
       </c>
       <c r="S37" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T37" t="n">
         <v>2.16</v>
@@ -7613,13 +7613,13 @@
         <v>85</v>
       </c>
       <c r="AB37" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC37" t="n">
         <v>7</v>
       </c>
       <c r="AD37" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE37" t="n">
         <v>65</v>
@@ -7652,7 +7652,7 @@
         <v>32</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP37" t="n">
         <v>8.199999999999999</v>
@@ -7664,7 +7664,7 @@
         <v>23</v>
       </c>
       <c r="AS37" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AT37" t="n">
         <v>7</v>
@@ -7688,7 +7688,7 @@
         <v>21</v>
       </c>
       <c r="BA37" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BB37" t="n">
         <v>29</v>
@@ -7703,14 +7703,14 @@
         <v>46</v>
       </c>
       <c r="BF37" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG37" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -7741,28 +7741,28 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="G38" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="H38" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="I38" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
-        <v>2.76</v>
+        <v>2.26</v>
       </c>
       <c r="K38" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N38" t="n">
         <v>1.12</v>
@@ -7783,16 +7783,16 @@
         <v>5</v>
       </c>
       <c r="T38" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U38" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W38" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="X38" t="n">
         <v>8.800000000000001</v>
@@ -7858,7 +7858,7 @@
         <v>13</v>
       </c>
       <c r="AS38" t="n">
-        <v>34</v>
+        <v>4.9</v>
       </c>
       <c r="AT38" t="n">
         <v>7.8</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
         <v>1.53</v>
       </c>
       <c r="U40" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V40" t="n">
         <v>1.52</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -8431,22 +8431,22 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AQ41" t="n">
         <v>2.04</v>
       </c>
       <c r="AR41" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AT41" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AV41" t="n">
         <v>2</v>
@@ -8458,35 +8458,35 @@
         <v>2.06</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AZ41" t="n">
         <v>2.02</v>
       </c>
       <c r="BA41" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BB41" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BD41" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BE41" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BF41" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BG41" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="G42" t="n">
         <v>7</v>
@@ -8532,7 +8532,7 @@
         <v>3.3</v>
       </c>
       <c r="K42" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -8711,13 +8711,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G43" t="n">
         <v>2.86</v>
       </c>
       <c r="H43" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I43" t="n">
         <v>2.74</v>
@@ -8726,7 +8726,7 @@
         <v>3.65</v>
       </c>
       <c r="K43" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
@@ -8735,10 +8735,10 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>4.3</v>
+        <v>2.24</v>
       </c>
       <c r="O43" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P43" t="n">
         <v>2.24</v>
@@ -8756,7 +8756,7 @@
         <v>1.5</v>
       </c>
       <c r="U43" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V43" t="n">
         <v>1.57</v>
@@ -8795,7 +8795,7 @@
         <v>15.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI43" t="n">
         <v>40</v>
@@ -8819,62 +8819,62 @@
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>2.52</v>
+        <v>12.5</v>
       </c>
       <c r="AQ43" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.52</v>
+        <v>13.5</v>
       </c>
       <c r="AS43" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AT43" t="n">
-        <v>9.800000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="AU43" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AV43" t="n">
-        <v>2.36</v>
+        <v>9</v>
       </c>
       <c r="AW43" t="n">
         <v>18.5</v>
       </c>
       <c r="AX43" t="n">
-        <v>14.5</v>
+        <v>2.56</v>
       </c>
       <c r="AY43" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AZ43" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BA43" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BB43" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BC43" t="n">
         <v>19.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="BE43" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BF43" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BG43" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -8923,7 +8923,7 @@
         <v>1000</v>
       </c>
       <c r="L44" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="M44" t="n">
         <v>1.01</v>
@@ -8956,7 +8956,7 @@
         <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -9013,52 +9013,52 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF44" t="n">
         <v>1.01</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G45" t="n">
         <v>23</v>
@@ -9132,7 +9132,7 @@
         <v>3.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R45" t="n">
         <v>2</v>
@@ -9147,7 +9147,7 @@
         <v>1.82</v>
       </c>
       <c r="V45" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="W45" t="n">
         <v>1.04</v>
@@ -9165,10 +9165,10 @@
         <v>8.6</v>
       </c>
       <c r="AB45" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD45" t="n">
         <v>13</v>
@@ -9180,13 +9180,13 @@
         <v>1000</v>
       </c>
       <c r="AG45" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AH45" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AI45" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ45" t="n">
         <v>1000</v>
@@ -9204,7 +9204,7 @@
         <v>1000</v>
       </c>
       <c r="AO45" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AP45" t="n">
         <v>38</v>
@@ -9234,7 +9234,7 @@
         <v>110</v>
       </c>
       <c r="AY45" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AZ45" t="n">
         <v>36</v>
@@ -9252,17 +9252,17 @@
         <v>85</v>
       </c>
       <c r="BE45" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BF45" t="n">
         <v>120</v>
       </c>
       <c r="BG45" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G46" t="n">
         <v>2.12</v>
@@ -9320,7 +9320,7 @@
         <v>4.6</v>
       </c>
       <c r="O46" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P46" t="n">
         <v>2.2</v>
@@ -9398,7 +9398,7 @@
         <v>13</v>
       </c>
       <c r="AO46" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP46" t="n">
         <v>15.5</v>
@@ -9428,10 +9428,10 @@
         <v>13</v>
       </c>
       <c r="AY46" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ46" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA46" t="n">
         <v>42</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
         <v>1.27</v>
       </c>
       <c r="H47" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="I47" t="n">
         <v>13</v>
@@ -9505,25 +9505,25 @@
         <v>8</v>
       </c>
       <c r="L47" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="M47" t="n">
         <v>1.02</v>
       </c>
       <c r="N47" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="O47" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P47" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q47" t="n">
         <v>1.33</v>
       </c>
       <c r="R47" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S47" t="n">
         <v>1.83</v>
@@ -9538,7 +9538,7 @@
         <v>1.08</v>
       </c>
       <c r="W47" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="X47" t="n">
         <v>48</v>
@@ -9553,7 +9553,7 @@
         <v>450</v>
       </c>
       <c r="AB47" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC47" t="n">
         <v>19</v>
@@ -9568,25 +9568,25 @@
         <v>11.5</v>
       </c>
       <c r="AG47" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH47" t="n">
         <v>28</v>
       </c>
       <c r="AI47" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ47" t="n">
         <v>11.5</v>
       </c>
       <c r="AK47" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AL47" t="n">
         <v>25</v>
       </c>
       <c r="AM47" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN47" t="n">
         <v>3</v>
@@ -9595,7 +9595,7 @@
         <v>110</v>
       </c>
       <c r="AP47" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AQ47" t="n">
         <v>50</v>
@@ -9625,7 +9625,7 @@
         <v>11</v>
       </c>
       <c r="AZ47" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA47" t="n">
         <v>38</v>
@@ -9643,14 +9643,14 @@
         <v>36</v>
       </c>
       <c r="BF47" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="BG47" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -9681,170 +9681,170 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="G48" t="n">
-        <v>2.6</v>
+        <v>970</v>
       </c>
       <c r="H48" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="I48" t="n">
-        <v>5.3</v>
+        <v>970</v>
       </c>
       <c r="J48" t="n">
-        <v>3.05</v>
+        <v>1.09</v>
       </c>
       <c r="K48" t="n">
-        <v>5.4</v>
+        <v>950</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P48" t="n">
         <v>1.6</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G49" t="n">
         <v>1.83</v>
@@ -9893,152 +9893,152 @@
         <v>1000</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P49" t="n">
         <v>1.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -10102,7 +10102,7 @@
         <v>1.64</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
         <v>1.29</v>
       </c>
       <c r="G51" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="H51" t="n">
         <v>12.5</v>
@@ -10275,7 +10275,7 @@
         <v>17.5</v>
       </c>
       <c r="J51" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="K51" t="n">
         <v>6.4</v>
@@ -10296,7 +10296,7 @@
         <v>1.92</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH51"/>
+  <dimension ref="A1:BH57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -957,13 +957,13 @@
         <v>4.2</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I3" t="n">
         <v>2.12</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
@@ -972,31 +972,31 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U3" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V3" t="n">
         <v>1.89</v>
@@ -1014,13 +1014,13 @@
         <v>14</v>
       </c>
       <c r="AA3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB3" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
         <v>11</v>
@@ -1029,7 +1029,7 @@
         <v>21</v>
       </c>
       <c r="AF3" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AG3" t="n">
         <v>18.5</v>
@@ -1050,10 +1050,10 @@
         <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO3" t="n">
         <v>13.5</v>
@@ -1077,13 +1077,13 @@
         <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW3" t="n">
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AY3" t="n">
         <v>14</v>
@@ -1092,29 +1092,29 @@
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.4</v>
+        <v>26</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG3" t="n">
         <v>10.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G4" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I4" t="n">
         <v>3.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,16 +1169,16 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R4" t="n">
         <v>1.37</v>
@@ -1196,7 +1196,7 @@
         <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="X4" t="n">
         <v>17.5</v>
@@ -1259,7 +1259,7 @@
         <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>18</v>
+        <v>4.3</v>
       </c>
       <c r="AS4" t="n">
         <v>4.8</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G5" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
@@ -1375,7 +1375,7 @@
         <v>1.87</v>
       </c>
       <c r="R5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
         <v>3.15</v>
@@ -1384,13 +1384,13 @@
         <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X5" t="n">
         <v>16</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H6" t="n">
         <v>8.800000000000001</v>
@@ -1545,7 +1545,7 @@
         <v>10.5</v>
       </c>
       <c r="J6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K6" t="n">
         <v>6.6</v>
@@ -1554,7 +1554,7 @@
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N6" t="n">
         <v>6.2</v>
@@ -1563,16 +1563,16 @@
         <v>1.15</v>
       </c>
       <c r="P6" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q6" t="n">
         <v>1.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="S6" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="T6" t="n">
         <v>1.78</v>
@@ -1584,119 +1584,119 @@
         <v>1.1</v>
       </c>
       <c r="W6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y6" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AB6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC6" t="n">
         <v>15</v>
       </c>
-      <c r="AC6" t="n">
-        <v>17</v>
-      </c>
       <c r="AD6" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF6" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="AL6" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.15</v>
+        <v>7.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.05</v>
+        <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.2</v>
+        <v>9.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.68</v>
+        <v>10.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>3</v>
+        <v>7.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.62</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
-        <v>2.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.92</v>
+        <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.72</v>
+        <v>10</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.78</v>
+        <v>12</v>
       </c>
       <c r="BD6" t="n">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.15</v>
+        <v>9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H7" t="n">
         <v>2.86</v>
       </c>
-      <c r="G7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.82</v>
-      </c>
       <c r="I7" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
         <v>2.86</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1754,7 +1754,7 @@
         <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P7" t="n">
         <v>1.5</v>
@@ -1775,10 +1775,10 @@
         <v>1.75</v>
       </c>
       <c r="V7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.47</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.46</v>
       </c>
       <c r="X7" t="n">
         <v>8.800000000000001</v>
@@ -1814,7 +1814,7 @@
         <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="n">
         <v>65</v>
@@ -1874,7 +1874,7 @@
         <v>7.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD7" t="n">
         <v>8</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G8" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H8" t="n">
         <v>2.86</v>
       </c>
       <c r="I8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
         <v>3.1</v>
@@ -1966,13 +1966,13 @@
         <v>1.96</v>
       </c>
       <c r="U8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V8" t="n">
         <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X8" t="n">
         <v>12</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="G10" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H10" t="n">
         <v>4.6</v>
@@ -2345,10 +2345,10 @@
         <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="T10" t="n">
         <v>1.61</v>
@@ -2360,7 +2360,7 @@
         <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X10" t="n">
         <v>28</v>
@@ -2375,7 +2375,7 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC10" t="n">
         <v>13.5</v>
@@ -2387,7 +2387,7 @@
         <v>85</v>
       </c>
       <c r="AF10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG10" t="n">
         <v>15</v>
@@ -2411,7 +2411,7 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
@@ -2420,16 +2420,16 @@
         <v>2.42</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AR10" t="n">
         <v>2.52</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AU10" t="n">
         <v>2.22</v>
@@ -2438,41 +2438,41 @@
         <v>2.42</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AX10" t="n">
         <v>2.3</v>
       </c>
       <c r="AY10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AZ10" t="n">
         <v>2.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BC10" t="n">
         <v>2.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BF10" t="n">
         <v>6.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>3.25</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
         <v>3.8</v>
@@ -3115,10 +3115,10 @@
         <v>1.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
         <v>1.42</v>
@@ -3127,10 +3127,10 @@
         <v>2.92</v>
       </c>
       <c r="T14" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U14" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V14" t="n">
         <v>1.45</v>
@@ -3154,7 +3154,7 @@
         <v>15</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD14" t="n">
         <v>16.5</v>
@@ -3202,19 +3202,19 @@
         <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
         <v>11.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AX14" t="n">
         <v>13</v>
@@ -3226,19 +3226,19 @@
         <v>11</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BC14" t="n">
         <v>19</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF14" t="n">
         <v>13.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -4079,19 +4079,19 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O19" t="n">
         <v>1.17</v>
       </c>
       <c r="P19" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="Q19" t="n">
         <v>1.51</v>
       </c>
       <c r="R19" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="S19" t="n">
         <v>2.26</v>
@@ -4100,7 +4100,7 @@
         <v>1.58</v>
       </c>
       <c r="U19" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V19" t="n">
         <v>1.23</v>
@@ -4157,22 +4157,22 @@
         <v>65</v>
       </c>
       <c r="AN19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT19" t="n">
         <v>12</v>
@@ -4181,10 +4181,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV19" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX19" t="n">
         <v>12</v>
@@ -4196,7 +4196,7 @@
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB19" t="n">
         <v>16</v>
@@ -4205,20 +4205,20 @@
         <v>13.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF19" t="n">
         <v>5.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>2.72</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I20" t="n">
         <v>2.94</v>
@@ -4273,7 +4273,7 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>2.28</v>
+        <v>1.03</v>
       </c>
       <c r="O20" t="n">
         <v>1.21</v>
@@ -4285,7 +4285,7 @@
         <v>1.67</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
         <v>2.46</v>
@@ -4309,7 +4309,7 @@
         <v>20</v>
       </c>
       <c r="Z20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA20" t="n">
         <v>55</v>
@@ -4381,19 +4381,19 @@
         <v>2.32</v>
       </c>
       <c r="AX20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AY20" t="n">
         <v>2.16</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BB20" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BC20" t="n">
         <v>2.3</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>1.99</v>
       </c>
       <c r="G21" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H21" t="n">
         <v>3.75</v>
@@ -4485,7 +4485,7 @@
         <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
         <v>1.99</v>
@@ -4494,7 +4494,7 @@
         <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4533,7 +4533,7 @@
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK21" t="n">
         <v>30</v>
@@ -4551,7 +4551,7 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AQ21" t="n">
         <v>9.199999999999999</v>
@@ -4560,7 +4560,7 @@
         <v>17.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AT21" t="n">
         <v>6.2</v>
@@ -4572,7 +4572,7 @@
         <v>10</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AX21" t="n">
         <v>8.199999999999999</v>
@@ -4584,7 +4584,7 @@
         <v>11</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BB21" t="n">
         <v>15</v>
@@ -4593,20 +4593,20 @@
         <v>13</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
         <v>90</v>
       </c>
       <c r="AF23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG23" t="n">
         <v>15</v>
@@ -4942,7 +4942,7 @@
         <v>13</v>
       </c>
       <c r="AQ23" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AR23" t="n">
         <v>2.5</v>
@@ -4957,10 +4957,10 @@
         <v>2.22</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AX23" t="n">
         <v>2.26</v>
@@ -4972,13 +4972,13 @@
         <v>2.38</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BB23" t="n">
         <v>2.36</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BD23" t="n">
         <v>2.46</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -5028,16 +5028,16 @@
         <v>1.57</v>
       </c>
       <c r="G24" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="H24" t="n">
         <v>4.3</v>
       </c>
       <c r="I24" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J24" t="n">
-        <v>3.9</v>
+        <v>2.82</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
@@ -5049,7 +5049,7 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O24" t="n">
         <v>1.27</v>
@@ -5076,7 +5076,7 @@
         <v>1.16</v>
       </c>
       <c r="W24" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X24" t="n">
         <v>21</v>
@@ -5103,10 +5103,10 @@
         <v>95</v>
       </c>
       <c r="AF24" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG24" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH24" t="n">
         <v>28</v>
@@ -5115,10 +5115,10 @@
         <v>95</v>
       </c>
       <c r="AJ24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL24" t="n">
         <v>48</v>
@@ -5127,68 +5127,68 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="AQ24" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AV24" t="n">
         <v>14.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="AX24" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="AY24" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="BB24" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BF24" t="n">
         <v>7.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G25" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
         <v>2.58</v>
@@ -5231,7 +5231,7 @@
         <v>4.5</v>
       </c>
       <c r="J25" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="K25" t="n">
         <v>950</v>
@@ -5243,7 +5243,7 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="O25" t="n">
         <v>1.31</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
         <v>3.45</v>
       </c>
       <c r="K26" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -5763,14 +5763,14 @@
         <v>3.15</v>
       </c>
       <c r="BF27" t="n">
-        <v>3.1</v>
+        <v>1.94</v>
       </c>
       <c r="BG27" t="n">
         <v>3.15</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -5825,13 +5825,13 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="O28" t="n">
         <v>1.24</v>
       </c>
       <c r="P28" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q28" t="n">
         <v>1.24</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
         <v>1.46</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.64</v>
+        <v>1.23</v>
       </c>
       <c r="R29" t="n">
         <v>1.45</v>
@@ -6158,14 +6158,14 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>French Ligue 1</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6180,186 +6180,186 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Zeleznicar Pancevo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Crvena Zvezda</t>
         </is>
       </c>
       <c r="F30" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G30" t="n">
+        <v>20</v>
+      </c>
+      <c r="H30" t="n">
         <v>1.19</v>
       </c>
-      <c r="G30" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="H30" t="n">
-        <v>16.5</v>
-      </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>1.25</v>
       </c>
       <c r="J30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K30" t="n">
         <v>9</v>
       </c>
-      <c r="K30" t="n">
-        <v>9.4</v>
-      </c>
       <c r="L30" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M30" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>8.800000000000001</v>
+        <v>3.45</v>
       </c>
       <c r="O30" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="P30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X30" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW30" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W30" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>75</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>19</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>13</v>
-      </c>
       <c r="AX30" t="n">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="AZ30" t="n">
-        <v>25</v>
+        <v>4.2</v>
       </c>
       <c r="BA30" t="n">
-        <v>13.5</v>
+        <v>4.2</v>
       </c>
       <c r="BB30" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="BC30" t="n">
-        <v>11.5</v>
+        <v>4.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>24</v>
+        <v>4.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6374,186 +6374,186 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Zeleznicar Pancevo</t>
+          <t>Oliveirense</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Crvena Zvezda</t>
+          <t>Benfica B</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.49</v>
+        <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>20</v>
+        <v>3.35</v>
       </c>
       <c r="H31" t="n">
-        <v>1.19</v>
+        <v>2.32</v>
       </c>
       <c r="I31" t="n">
-        <v>1.25</v>
+        <v>2.6</v>
       </c>
       <c r="J31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF31" t="n">
         <v>6.6</v>
       </c>
-      <c r="K31" t="n">
-        <v>9</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X31" t="n">
-        <v>42</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>75</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>23</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>75</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BG31" t="n">
-        <v>3</v>
+        <v>13.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6568,186 +6568,186 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Oliveirense</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Benfica B</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>2.22</v>
       </c>
       <c r="G32" t="n">
-        <v>3.35</v>
+        <v>2.48</v>
       </c>
       <c r="H32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q32" t="n">
         <v>2.32</v>
       </c>
-      <c r="I32" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N32" t="n">
-        <v>4</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X32" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>19</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>12</v>
-      </c>
       <c r="AQ32" t="n">
-        <v>10</v>
+        <v>2.08</v>
       </c>
       <c r="AR32" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AS32" t="n">
-        <v>6.6</v>
+        <v>2.38</v>
       </c>
       <c r="AT32" t="n">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="AU32" t="n">
-        <v>7</v>
+        <v>1.94</v>
       </c>
       <c r="AV32" t="n">
         <v>10</v>
       </c>
       <c r="AW32" t="n">
-        <v>21</v>
+        <v>2.32</v>
       </c>
       <c r="AX32" t="n">
-        <v>19</v>
+        <v>9.4</v>
       </c>
       <c r="AY32" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="AZ32" t="n">
-        <v>13.5</v>
+        <v>2.2</v>
       </c>
       <c r="BA32" t="n">
-        <v>6.6</v>
+        <v>2.38</v>
       </c>
       <c r="BB32" t="n">
-        <v>38</v>
+        <v>2.26</v>
       </c>
       <c r="BC32" t="n">
-        <v>6.8</v>
+        <v>2.26</v>
       </c>
       <c r="BD32" t="n">
-        <v>30</v>
+        <v>2.38</v>
       </c>
       <c r="BE32" t="n">
-        <v>55</v>
+        <v>2.38</v>
       </c>
       <c r="BF32" t="n">
-        <v>22</v>
+        <v>2.38</v>
       </c>
       <c r="BG32" t="n">
-        <v>13.5</v>
+        <v>2.38</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Greek Super League</t>
+          <t>French Ligue 1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6762,179 +6762,179 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Paris St-G</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.22</v>
+        <v>1.2</v>
       </c>
       <c r="G33" t="n">
-        <v>2.48</v>
+        <v>1.21</v>
       </c>
       <c r="H33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>18</v>
+      </c>
+      <c r="J33" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N33" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P33" t="n">
         <v>3.65</v>
       </c>
-      <c r="I33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.63</v>
-      </c>
       <c r="Q33" t="n">
-        <v>2.32</v>
+        <v>1.35</v>
       </c>
       <c r="R33" t="n">
-        <v>1.18</v>
+        <v>2.06</v>
       </c>
       <c r="S33" t="n">
-        <v>3.85</v>
+        <v>1.86</v>
       </c>
       <c r="T33" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U33" t="n">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="V33" t="n">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="W33" t="n">
-        <v>1.67</v>
+        <v>5.7</v>
       </c>
       <c r="X33" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="Z33" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>19</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC33" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD33" t="n">
+      <c r="BD33" t="n">
         <v>24</v>
       </c>
-      <c r="AE33" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>2.38</v>
-      </c>
       <c r="BE33" t="n">
-        <v>2.38</v>
+        <v>13</v>
       </c>
       <c r="BF33" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="BG33" t="n">
-        <v>2.38</v>
+        <v>13</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G35" t="n">
         <v>2.14</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -7592,7 +7592,7 @@
         <v>2.16</v>
       </c>
       <c r="U37" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V37" t="n">
         <v>1.33</v>
@@ -7664,7 +7664,7 @@
         <v>23</v>
       </c>
       <c r="AS37" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AT37" t="n">
         <v>7</v>
@@ -7688,7 +7688,7 @@
         <v>21</v>
       </c>
       <c r="BA37" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BB37" t="n">
         <v>29</v>
@@ -7710,14 +7710,14 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7732,32 +7732,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Smouha</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Brondby</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.92</v>
+        <v>2.36</v>
       </c>
       <c r="G38" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K38" t="n">
         <v>4.4</v>
       </c>
-      <c r="H38" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="I38" t="n">
-        <v>3</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="K38" t="n">
-        <v>3.95</v>
-      </c>
       <c r="L38" t="n">
         <v>1.01</v>
       </c>
@@ -7765,153 +7765,153 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.12</v>
+        <v>5.1</v>
       </c>
       <c r="O38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R38" t="n">
         <v>1.56</v>
       </c>
-      <c r="P38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.12</v>
-      </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>2.56</v>
       </c>
       <c r="T38" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U38" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="V38" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W38" t="n">
-        <v>1.29</v>
+        <v>1.65</v>
       </c>
       <c r="X38" t="n">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="Y38" t="n">
-        <v>8.6</v>
+        <v>17</v>
       </c>
       <c r="Z38" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA38" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB38" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU38" t="n">
         <v>8</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>6</v>
       </c>
       <c r="AV38" t="n">
         <v>11.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AX38" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG38" t="n">
         <v>13.5</v>
       </c>
-      <c r="AZ38" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7926,186 +7926,186 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KA Akureyri</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N39" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="O39" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="P39" t="n">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.15</v>
+        <v>1.6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="S39" t="n">
-        <v>1.15</v>
+        <v>2.5</v>
       </c>
       <c r="T39" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U39" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y39" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z39" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA39" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB39" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC39" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD39" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF39" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG39" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH39" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI39" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK39" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL39" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM39" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN39" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO39" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8120,186 +8120,186 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SC Telstar</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.46</v>
+        <v>3.75</v>
       </c>
       <c r="G40" t="n">
-        <v>2.64</v>
+        <v>7</v>
       </c>
       <c r="H40" t="n">
-        <v>2.68</v>
+        <v>1.82</v>
       </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="J40" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="K40" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
       </c>
       <c r="M40" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>5.1</v>
+        <v>1.54</v>
       </c>
       <c r="O40" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="P40" t="n">
-        <v>2.38</v>
+        <v>1.54</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="R40" t="n">
-        <v>1.56</v>
+        <v>1.19</v>
       </c>
       <c r="S40" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="T40" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="U40" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="V40" t="n">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="W40" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="X40" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y40" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z40" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA40" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC40" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD40" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE40" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG40" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH40" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI40" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK40" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL40" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM40" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AO40" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ40" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR40" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS40" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT40" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU40" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV40" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW40" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AX40" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY40" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ40" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA40" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB40" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC40" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD40" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE40" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BF40" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG40" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8314,186 +8314,186 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Smouha</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.36</v>
+        <v>2.92</v>
       </c>
       <c r="G41" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Q41" t="n">
         <v>2.52</v>
       </c>
-      <c r="H41" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="I41" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K41" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N41" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1.63</v>
-      </c>
       <c r="R41" t="n">
-        <v>1.56</v>
+        <v>1.12</v>
       </c>
       <c r="S41" t="n">
-        <v>2.56</v>
+        <v>5</v>
       </c>
       <c r="T41" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="U41" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V41" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W41" t="n">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="X41" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS41" t="n">
         <v>34</v>
       </c>
-      <c r="Y41" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC41" t="n">
+      <c r="AT41" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY41" t="n">
         <v>13.5</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AZ41" t="n">
         <v>20</v>
       </c>
-      <c r="AE41" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BA41" t="n">
-        <v>2.14</v>
+        <v>5</v>
       </c>
       <c r="BB41" t="n">
-        <v>2.14</v>
+        <v>5.1</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="BD41" t="n">
-        <v>2.14</v>
+        <v>5.1</v>
       </c>
       <c r="BE41" t="n">
-        <v>2.18</v>
+        <v>5.2</v>
       </c>
       <c r="BF41" t="n">
-        <v>2.24</v>
+        <v>5.1</v>
       </c>
       <c r="BG41" t="n">
-        <v>2.24</v>
+        <v>4.9</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8508,31 +8508,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>IA Akranes</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>KA Akureyri</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -8541,22 +8541,22 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="O42" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="P42" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.02</v>
+        <v>1.15</v>
       </c>
       <c r="R42" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S42" t="n">
-        <v>3.5</v>
+        <v>1.15</v>
       </c>
       <c r="T42" t="n">
         <v>1.01</v>
@@ -8565,10 +8565,10 @@
         <v>1.01</v>
       </c>
       <c r="V42" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -8625,52 +8625,52 @@
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF42" t="n">
         <v>1.01</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
         <v>2.7</v>
       </c>
       <c r="G43" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H43" t="n">
         <v>2.54</v>
@@ -8874,14 +8874,14 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8896,186 +8896,186 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="G44" t="n">
-        <v>1.22</v>
+        <v>2.12</v>
       </c>
       <c r="H44" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="I44" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="J44" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="K44" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L44" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M44" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N44" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="O44" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="P44" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="R44" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="S44" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="T44" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U44" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="V44" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="W44" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="X44" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z44" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA44" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB44" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD44" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE44" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF44" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG44" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AI44" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK44" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL44" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM44" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN44" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO44" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="AT44" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG44" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9090,112 +9090,112 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="G45" t="n">
-        <v>23</v>
+        <v>1.22</v>
       </c>
       <c r="H45" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="I45" t="n">
-        <v>1.17</v>
+        <v>1000</v>
       </c>
       <c r="J45" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="K45" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="L45" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M45" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="O45" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="P45" t="n">
-        <v>3.5</v>
+        <v>1.67</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="R45" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="S45" t="n">
-        <v>1.96</v>
+        <v>1.04</v>
       </c>
       <c r="T45" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="U45" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="V45" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="W45" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X45" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Y45" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z45" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AA45" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AB45" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AC45" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AD45" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE45" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AF45" t="n">
         <v>1000</v>
       </c>
       <c r="AG45" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AH45" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AI45" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ45" t="n">
         <v>1000</v>
       </c>
       <c r="AK45" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AL45" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AM45" t="n">
         <v>1000</v>
@@ -9204,65 +9204,65 @@
         <v>1000</v>
       </c>
       <c r="AO45" t="n">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AQ45" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR45" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS45" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT45" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AU45" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AV45" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW45" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AX45" t="n">
-        <v>110</v>
+        <v>1.01</v>
       </c>
       <c r="AY45" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AZ45" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BA45" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BB45" t="n">
-        <v>150</v>
+        <v>1.01</v>
       </c>
       <c r="BC45" t="n">
-        <v>110</v>
+        <v>1.01</v>
       </c>
       <c r="BD45" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BE45" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BF45" t="n">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="BG45" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -9284,179 +9284,179 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.08</v>
+        <v>23</v>
       </c>
       <c r="G46" t="n">
-        <v>2.12</v>
+        <v>24</v>
       </c>
       <c r="H46" t="n">
-        <v>3.8</v>
+        <v>1.16</v>
       </c>
       <c r="I46" t="n">
-        <v>3.9</v>
+        <v>1.17</v>
       </c>
       <c r="J46" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="K46" t="n">
-        <v>3.8</v>
+        <v>10.5</v>
       </c>
       <c r="L46" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="M46" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N46" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="O46" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="P46" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="R46" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="T46" t="n">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="U46" t="n">
-        <v>2.36</v>
+        <v>1.82</v>
       </c>
       <c r="V46" t="n">
-        <v>1.35</v>
+        <v>7</v>
       </c>
       <c r="W46" t="n">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="X46" t="n">
-        <v>16.5</v>
+        <v>44</v>
       </c>
       <c r="Y46" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Z46" t="n">
-        <v>28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA46" t="n">
-        <v>70</v>
+        <v>8.6</v>
       </c>
       <c r="AB46" t="n">
-        <v>11.5</v>
+        <v>120</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="AD46" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AE46" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="AF46" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG46" t="n">
-        <v>10.5</v>
+        <v>80</v>
       </c>
       <c r="AH46" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="AI46" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ46" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK46" t="n">
-        <v>20</v>
+        <v>360</v>
       </c>
       <c r="AL46" t="n">
-        <v>32</v>
+        <v>240</v>
       </c>
       <c r="AM46" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO46" t="n">
-        <v>36</v>
+        <v>2.76</v>
       </c>
       <c r="AP46" t="n">
-        <v>15.5</v>
+        <v>38</v>
       </c>
       <c r="AQ46" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS46" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT46" t="n">
         <v>60</v>
       </c>
-      <c r="AT46" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AU46" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AV46" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AW46" t="n">
-        <v>36</v>
+        <v>12.5</v>
       </c>
       <c r="AX46" t="n">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="AY46" t="n">
-        <v>9.800000000000001</v>
+        <v>60</v>
       </c>
       <c r="AZ46" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="BA46" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BB46" t="n">
-        <v>23</v>
+        <v>150</v>
       </c>
       <c r="BC46" t="n">
-        <v>18.5</v>
+        <v>120</v>
       </c>
       <c r="BD46" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="BE46" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="BF46" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="BG46" t="n">
-        <v>30</v>
+        <v>2.68</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -9517,13 +9517,13 @@
         <v>1.1</v>
       </c>
       <c r="P47" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="Q47" t="n">
         <v>1.33</v>
       </c>
       <c r="R47" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="S47" t="n">
         <v>1.83</v>
@@ -9574,7 +9574,7 @@
         <v>28</v>
       </c>
       <c r="AI47" t="n">
-        <v>100</v>
+        <v>990</v>
       </c>
       <c r="AJ47" t="n">
         <v>11.5</v>
@@ -9643,14 +9643,14 @@
         <v>36</v>
       </c>
       <c r="BF47" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BG47" t="n">
         <v>42</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -9681,19 +9681,19 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.02</v>
+        <v>1.09</v>
       </c>
       <c r="G48" t="n">
-        <v>970</v>
+        <v>2.32</v>
       </c>
       <c r="H48" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I48" t="n">
-        <v>970</v>
+        <v>5.2</v>
       </c>
       <c r="J48" t="n">
-        <v>1.09</v>
+        <v>3.25</v>
       </c>
       <c r="K48" t="n">
         <v>950</v>
@@ -9729,10 +9729,10 @@
         <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="W48" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -9875,31 +9875,31 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G49" t="n">
         <v>1.83</v>
       </c>
       <c r="H49" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="I49" t="n">
         <v>1000</v>
       </c>
       <c r="J49" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="K49" t="n">
         <v>1000</v>
       </c>
       <c r="L49" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M49" t="n">
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O49" t="n">
         <v>1.24</v>
@@ -9983,52 +9983,52 @@
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF49" t="n">
         <v>1.01</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -10069,170 +10069,170 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="G50" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="H50" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I50" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="K50" t="n">
         <v>5.1</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P50" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
         <v>1.29</v>
       </c>
       <c r="G51" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="H51" t="n">
         <v>12.5</v>
@@ -10275,158 +10275,1322 @@
         <v>17.5</v>
       </c>
       <c r="J51" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K51" t="n">
         <v>6.4</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P51" t="n">
         <v>1.92</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AU51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AW51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AY51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BA51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BB51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BD51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BE51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BF51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>US MLS</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>New York Red Bulls</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>DC Utd</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I52" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J52" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K52" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N52" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X52" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH52" t="inlineStr">
+        <is>
+          <t>2026-04-20 21:52:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>US MLS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Toronto FC</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P53" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BH53" t="inlineStr">
+        <is>
+          <t>2026-04-20 21:52:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>US MLS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Columbus</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H54" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I54" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J54" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N54" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W54" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X54" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH54" t="inlineStr">
+        <is>
+          <t>2026-04-20 21:52:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>US MLS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I55" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K55" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X55" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH55" t="inlineStr">
+        <is>
+          <t>2026-04-20 21:52:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>US MLS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N56" t="n">
+        <v>5</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P56" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X56" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH56" t="inlineStr">
+        <is>
+          <t>2026-04-20 21:52:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>US MLS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>20:45:00</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Atlanta Utd</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>New England</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>2</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I57" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K57" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N57" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="X57" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH57" t="inlineStr">
+        <is>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
@@ -913,14 +913,14 @@
         <v>5.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG2" t="n">
         <v>5.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
         <v>4.2</v>
@@ -1020,7 +1020,7 @@
         <v>17</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>11</v>
@@ -1095,26 +1095,26 @@
         <v>26</v>
       </c>
       <c r="BB3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG3" t="n">
         <v>10.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>2.3</v>
       </c>
       <c r="G4" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H4" t="n">
         <v>3.25</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J4" t="n">
         <v>3.45</v>
@@ -1169,19 +1169,19 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O4" t="n">
         <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
         <v>1.92</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
         <v>3.3</v>
@@ -1196,7 +1196,7 @@
         <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X4" t="n">
         <v>17.5</v>
@@ -1253,10 +1253,10 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR4" t="n">
         <v>4.3</v>
@@ -1265,28 +1265,28 @@
         <v>4.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.95</v>
+        <v>9.4</v>
       </c>
       <c r="AU4" t="n">
         <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW4" t="n">
         <v>4.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>12</v>
+        <v>4.3</v>
       </c>
       <c r="AY4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
         <v>4.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB4" t="n">
         <v>4.5</v>
@@ -1295,20 +1295,20 @@
         <v>4.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE4" t="n">
         <v>4.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -1342,19 +1342,19 @@
         <v>2.54</v>
       </c>
       <c r="G5" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H5" t="n">
         <v>2.82</v>
       </c>
       <c r="I5" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1387,10 +1387,10 @@
         <v>2.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
         <v>16</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
         <v>6.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P6" t="n">
         <v>2.84</v>
@@ -1569,19 +1569,19 @@
         <v>1.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S6" t="n">
         <v>2.16</v>
       </c>
       <c r="T6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
         <v>2.14</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W6" t="n">
         <v>3.55</v>
@@ -1611,7 +1611,7 @@
         <v>140</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG6" t="n">
         <v>11.5</v>
@@ -1641,16 +1641,16 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT6" t="n">
         <v>10.5</v>
@@ -1659,10 +1659,10 @@
         <v>12.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX6" t="n">
         <v>9</v>
@@ -1674,29 +1674,29 @@
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC6" t="n">
         <v>12</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF6" t="n">
         <v>3.85</v>
       </c>
       <c r="BG6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H7" t="n">
         <v>2.86</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
         <v>2.86</v>
       </c>
       <c r="K7" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1766,7 +1766,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T7" t="n">
         <v>2.08</v>
@@ -1778,7 +1778,7 @@
         <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
         <v>8.800000000000001</v>
@@ -1850,7 +1850,7 @@
         <v>7.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
         <v>12</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>2.86</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
         <v>3.1</v>
@@ -1945,7 +1945,7 @@
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O8" t="n">
         <v>1.48</v>
@@ -1963,13 +1963,13 @@
         <v>4.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
         <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W8" t="n">
         <v>1.51</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -5025,19 +5025,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G24" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="H24" t="n">
         <v>4.3</v>
       </c>
       <c r="I24" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
@@ -5049,7 +5049,7 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.85</v>
+        <v>3.35</v>
       </c>
       <c r="O24" t="n">
         <v>1.27</v>
@@ -5073,10 +5073,10 @@
         <v>1.87</v>
       </c>
       <c r="V24" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W24" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="X24" t="n">
         <v>21</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
         <v>1.78</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="H25" t="n">
         <v>2.58</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
         <v>2.02</v>
       </c>
       <c r="O26" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P26" t="n">
         <v>1.97</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N27" t="n">
         <v>2.62</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6921,7 @@
         <v>11.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BE33" t="n">
         <v>13</v>
@@ -6930,11 +6930,11 @@
         <v>2.88</v>
       </c>
       <c r="BG33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
         <v>2.64</v>
       </c>
       <c r="I34" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J34" t="n">
         <v>3.9</v>
@@ -7013,7 +7013,7 @@
         <v>2.44</v>
       </c>
       <c r="V34" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W34" t="n">
         <v>1.58</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
         <v>3.9</v>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J37" t="n">
         <v>3.1</v>
@@ -7592,7 +7592,7 @@
         <v>2.16</v>
       </c>
       <c r="U37" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V37" t="n">
         <v>1.33</v>
@@ -7610,7 +7610,7 @@
         <v>25</v>
       </c>
       <c r="AA37" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB37" t="n">
         <v>7.4</v>
@@ -7664,7 +7664,7 @@
         <v>23</v>
       </c>
       <c r="AS37" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AT37" t="n">
         <v>7</v>
@@ -7688,7 +7688,7 @@
         <v>21</v>
       </c>
       <c r="BA37" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB37" t="n">
         <v>29</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7747,7 @@
         <v>2.52</v>
       </c>
       <c r="H38" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I38" t="n">
         <v>3.05</v>
@@ -7792,7 +7792,7 @@
         <v>1.48</v>
       </c>
       <c r="W38" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X38" t="n">
         <v>24</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -8347,13 +8347,13 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="O41" t="n">
-        <v>1.56</v>
+        <v>1.14</v>
       </c>
       <c r="P41" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Q41" t="n">
         <v>2.52</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -9374,10 +9374,10 @@
         <v>1000</v>
       </c>
       <c r="AG46" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AH46" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI46" t="n">
         <v>42</v>
@@ -9389,7 +9389,7 @@
         <v>360</v>
       </c>
       <c r="AL46" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AM46" t="n">
         <v>1000</v>
@@ -9440,23 +9440,23 @@
         <v>150</v>
       </c>
       <c r="BC46" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BD46" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BE46" t="n">
         <v>90</v>
       </c>
       <c r="BF46" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BG46" t="n">
         <v>2.68</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -9643,14 +9643,14 @@
         <v>36</v>
       </c>
       <c r="BF47" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BG47" t="n">
         <v>42</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.09</v>
+        <v>1.7</v>
       </c>
       <c r="G48" t="n">
         <v>2.32</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -9878,16 +9878,16 @@
         <v>1.12</v>
       </c>
       <c r="G49" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H49" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="I49" t="n">
         <v>1000</v>
       </c>
       <c r="J49" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="K49" t="n">
         <v>1000</v>
@@ -9899,13 +9899,13 @@
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>1.25</v>
+        <v>2.42</v>
       </c>
       <c r="O49" t="n">
         <v>1.24</v>
       </c>
       <c r="P49" t="n">
-        <v>1.24</v>
+        <v>2.42</v>
       </c>
       <c r="Q49" t="n">
         <v>1.24</v>
@@ -9926,7 +9926,7 @@
         <v>1.01</v>
       </c>
       <c r="W49" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X49" t="n">
         <v>1000</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -10069,19 +10069,19 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G50" t="n">
         <v>1.83</v>
       </c>
       <c r="H50" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I50" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J50" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K50" t="n">
         <v>5.1</v>
@@ -10093,16 +10093,16 @@
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O50" t="n">
         <v>1.36</v>
       </c>
       <c r="P50" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R50" t="n">
         <v>1.23</v>
@@ -10117,7 +10117,7 @@
         <v>1.01</v>
       </c>
       <c r="V50" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W50" t="n">
         <v>2.2</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
         <v>1.29</v>
       </c>
       <c r="G51" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="H51" t="n">
         <v>12.5</v>
@@ -10305,16 +10305,16 @@
         <v>2.58</v>
       </c>
       <c r="T51" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U51" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="V51" t="n">
         <v>1.06</v>
       </c>
       <c r="W51" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="X51" t="n">
         <v>28</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -10457,16 +10457,16 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G52" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H52" t="n">
         <v>4.7</v>
       </c>
       <c r="I52" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J52" t="n">
         <v>3.95</v>
@@ -10475,28 +10475,28 @@
         <v>4.3</v>
       </c>
       <c r="L52" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M52" t="n">
         <v>1.05</v>
       </c>
       <c r="N52" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O52" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P52" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R52" t="n">
         <v>1.46</v>
       </c>
       <c r="S52" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T52" t="n">
         <v>1.74</v>
@@ -10505,16 +10505,16 @@
         <v>2.18</v>
       </c>
       <c r="V52" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W52" t="n">
         <v>2.18</v>
       </c>
       <c r="X52" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y52" t="n">
         <v>21</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>22</v>
       </c>
       <c r="Z52" t="n">
         <v>1000</v>
@@ -10529,7 +10529,7 @@
         <v>10.5</v>
       </c>
       <c r="AD52" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE52" t="n">
         <v>1000</v>
@@ -10541,7 +10541,7 @@
         <v>12</v>
       </c>
       <c r="AH52" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI52" t="n">
         <v>1000</v>
@@ -10553,7 +10553,7 @@
         <v>21</v>
       </c>
       <c r="AL52" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM52" t="n">
         <v>1000</v>
@@ -10571,10 +10571,10 @@
         <v>15</v>
       </c>
       <c r="AR52" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS52" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT52" t="n">
         <v>9</v>
@@ -10586,7 +10586,7 @@
         <v>5.3</v>
       </c>
       <c r="AW52" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX52" t="n">
         <v>9.199999999999999</v>
@@ -10595,10 +10595,10 @@
         <v>9</v>
       </c>
       <c r="AZ52" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BA52" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB52" t="n">
         <v>16.5</v>
@@ -10607,10 +10607,10 @@
         <v>15.5</v>
       </c>
       <c r="BD52" t="n">
-        <v>5.9</v>
+        <v>23</v>
       </c>
       <c r="BE52" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF52" t="n">
         <v>8.6</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -10657,7 +10657,7 @@
         <v>2.62</v>
       </c>
       <c r="H53" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I53" t="n">
         <v>3</v>
@@ -10669,28 +10669,28 @@
         <v>3.65</v>
       </c>
       <c r="L53" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M53" t="n">
         <v>1.06</v>
       </c>
       <c r="N53" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O53" t="n">
         <v>1.3</v>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R53" t="n">
         <v>1.39</v>
       </c>
       <c r="S53" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T53" t="n">
         <v>1.7</v>
@@ -10702,7 +10702,7 @@
         <v>1.5</v>
       </c>
       <c r="W53" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X53" t="n">
         <v>1000</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="G54" t="n">
         <v>1.86</v>
@@ -10860,16 +10860,16 @@
         <v>4.1</v>
       </c>
       <c r="K54" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L54" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M54" t="n">
         <v>1.04</v>
       </c>
       <c r="N54" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O54" t="n">
         <v>1.2</v>
@@ -10878,13 +10878,13 @@
         <v>2.52</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="R54" t="n">
         <v>1.6</v>
       </c>
       <c r="S54" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T54" t="n">
         <v>1.6</v>
@@ -10893,13 +10893,13 @@
         <v>2.48</v>
       </c>
       <c r="V54" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W54" t="n">
         <v>2.16</v>
       </c>
       <c r="X54" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y54" t="n">
         <v>25</v>
@@ -10911,7 +10911,7 @@
         <v>110</v>
       </c>
       <c r="AB54" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC54" t="n">
         <v>10</v>
@@ -10962,7 +10962,7 @@
         <v>34</v>
       </c>
       <c r="AS54" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT54" t="n">
         <v>11</v>
@@ -10974,7 +10974,7 @@
         <v>16.5</v>
       </c>
       <c r="AW54" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX54" t="n">
         <v>12</v>
@@ -10986,7 +10986,7 @@
         <v>14.5</v>
       </c>
       <c r="BA54" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB54" t="n">
         <v>18</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -11039,46 +11039,46 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G55" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="H55" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="I55" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="J55" t="n">
-        <v>2.86</v>
+        <v>3.85</v>
       </c>
       <c r="K55" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L55" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M55" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N55" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="O55" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P55" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.24</v>
+        <v>1.77</v>
       </c>
       <c r="R55" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="S55" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="T55" t="n">
         <v>1.67</v>
@@ -11087,10 +11087,10 @@
         <v>2.26</v>
       </c>
       <c r="V55" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="W55" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="X55" t="n">
         <v>21</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -11233,46 +11233,46 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G56" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H56" t="n">
         <v>2.7</v>
       </c>
-      <c r="H56" t="n">
-        <v>2.66</v>
-      </c>
       <c r="I56" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="J56" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K56" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L56" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N56" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O56" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P56" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q56" t="n">
         <v>1.63</v>
       </c>
       <c r="R56" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S56" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T56" t="n">
         <v>1.55</v>
@@ -11281,10 +11281,10 @@
         <v>2.56</v>
       </c>
       <c r="V56" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W56" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X56" t="n">
         <v>26</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G57" t="n">
         <v>2.1</v>
@@ -11442,31 +11442,31 @@
         <v>3.8</v>
       </c>
       <c r="K57" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L57" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M57" t="n">
         <v>1.05</v>
       </c>
       <c r="N57" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O57" t="n">
         <v>1.28</v>
       </c>
       <c r="P57" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R57" t="n">
         <v>1.43</v>
       </c>
       <c r="S57" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T57" t="n">
         <v>1.73</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
@@ -772,7 +772,7 @@
         <v>4.9</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.3</v>
@@ -802,7 +802,7 @@
         <v>1.79</v>
       </c>
       <c r="U2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="n">
         <v>1.15</v>
@@ -844,10 +844,10 @@
         <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK2" t="n">
         <v>18</v>
@@ -871,10 +871,10 @@
         <v>6.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
         <v>9</v>
@@ -886,7 +886,7 @@
         <v>19.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX2" t="n">
         <v>8.800000000000001</v>
@@ -898,7 +898,7 @@
         <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>55</v>
+        <v>7.4</v>
       </c>
       <c r="BB2" t="n">
         <v>11.5</v>
@@ -910,17 +910,17 @@
         <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF2" t="n">
         <v>5.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G3" t="n">
         <v>3.95</v>
@@ -966,7 +966,7 @@
         <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.36</v>
@@ -1071,7 +1071,7 @@
         <v>19</v>
       </c>
       <c r="AT3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU3" t="n">
         <v>7.6</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1184,7 +1184,7 @@
         <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
         <v>1.73</v>
@@ -1193,7 +1193,7 @@
         <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W4" t="n">
         <v>1.7</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>2.56</v>
       </c>
       <c r="G5" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H5" t="n">
         <v>2.8</v>
@@ -1354,10 +1354,10 @@
         <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
@@ -1390,10 +1390,10 @@
         <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X5" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
         <v>13</v>
@@ -1402,7 +1402,7 @@
         <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB5" t="n">
         <v>12</v>
@@ -1426,7 +1426,7 @@
         <v>970</v>
       </c>
       <c r="AI5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ5" t="n">
         <v>40</v>
@@ -1453,10 +1453,10 @@
         <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
         <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
@@ -1480,29 +1480,29 @@
         <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG5" t="n">
         <v>19</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -1533,31 +1533,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="G6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K6" t="n">
         <v>6.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
         <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>1.17</v>
@@ -1569,7 +1569,7 @@
         <v>1.53</v>
       </c>
       <c r="R6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S6" t="n">
         <v>2.28</v>
@@ -1578,10 +1578,10 @@
         <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
         <v>3.35</v>
@@ -1590,19 +1590,19 @@
         <v>34</v>
       </c>
       <c r="Y6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z6" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
         <v>290</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD6" t="n">
         <v>34</v>
@@ -1611,13 +1611,13 @@
         <v>130</v>
       </c>
       <c r="AF6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
         <v>100</v>
@@ -1641,28 +1641,28 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.8</v>
+        <v>19.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.6</v>
+        <v>34</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.199999999999999</v>
+        <v>95</v>
       </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU6" t="n">
         <v>11.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.6</v>
+        <v>19</v>
       </c>
       <c r="AW6" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="AX6" t="n">
         <v>9</v>
@@ -1674,29 +1674,29 @@
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BB6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC6" t="n">
         <v>12</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -1730,28 +1730,28 @@
         <v>2.78</v>
       </c>
       <c r="G7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
         <v>2.86</v>
       </c>
       <c r="K7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M7" t="n">
         <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O7" t="n">
         <v>1.55</v>
@@ -1775,10 +1775,10 @@
         <v>1.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
         <v>8.800000000000001</v>
@@ -1787,7 +1787,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
         <v>60</v>
@@ -1805,7 +1805,7 @@
         <v>50</v>
       </c>
       <c r="AF7" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AG7" t="n">
         <v>14.5</v>
@@ -1817,7 +1817,7 @@
         <v>80</v>
       </c>
       <c r="AJ7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="n">
         <v>46</v>
@@ -1832,7 +1832,7 @@
         <v>60</v>
       </c>
       <c r="AO7" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AP7" t="n">
         <v>7.2</v>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX7" t="n">
         <v>15</v>
@@ -1871,16 +1871,16 @@
         <v>8</v>
       </c>
       <c r="BB7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD7" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>8</v>
-      </c>
       <c r="BE7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF7" t="n">
         <v>40</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="G8" t="n">
         <v>2.96</v>
@@ -1933,7 +1933,7 @@
         <v>3.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K8" t="n">
         <v>3.3</v>
@@ -1951,10 +1951,10 @@
         <v>1.48</v>
       </c>
       <c r="P8" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R8" t="n">
         <v>1.22</v>
@@ -1963,13 +1963,13 @@
         <v>4.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U8" t="n">
         <v>1.86</v>
       </c>
       <c r="V8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W8" t="n">
         <v>1.51</v>
@@ -2077,14 +2077,14 @@
         <v>4.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I9" t="n">
         <v>4.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
         <v>1.54</v>
@@ -2142,7 +2142,7 @@
         <v>1.46</v>
       </c>
       <c r="O9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
         <v>1.45</v>
@@ -2166,7 +2166,7 @@
         <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X9" t="n">
         <v>8.6</v>
@@ -2193,7 +2193,7 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG9" t="n">
         <v>14.5</v>
@@ -2208,7 +2208,7 @@
         <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2223,16 +2223,16 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT9" t="n">
         <v>6</v>
@@ -2244,7 +2244,7 @@
         <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX9" t="n">
         <v>11</v>
@@ -2256,29 +2256,29 @@
         <v>20</v>
       </c>
       <c r="BA9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD9" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD9" t="n">
+      <c r="BE9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF9" t="n">
         <v>4.7</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BG9" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H10" t="n">
         <v>4.6</v>
@@ -2333,7 +2333,7 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
@@ -2348,7 +2348,7 @@
         <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T10" t="n">
         <v>1.63</v>
@@ -2360,16 +2360,16 @@
         <v>1.24</v>
       </c>
       <c r="W10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X10" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
         <v>29</v>
       </c>
       <c r="Z10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
@@ -2417,19 +2417,19 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="AQ10" t="n">
         <v>15.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AU10" t="n">
         <v>7.2</v>
@@ -2438,19 +2438,19 @@
         <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.76</v>
+        <v>2.48</v>
       </c>
       <c r="AX10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY10" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AZ10" t="n">
         <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.76</v>
+        <v>2.48</v>
       </c>
       <c r="BB10" t="n">
         <v>15.5</v>
@@ -2459,20 +2459,20 @@
         <v>13</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BF10" t="n">
         <v>7.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>4.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -2727,7 +2727,7 @@
         <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
         <v>1.76</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
         <v>1.25</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v>3.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
@@ -3145,7 +3145,7 @@
         <v>17</v>
       </c>
       <c r="Z14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA14" t="n">
         <v>60</v>
@@ -3157,7 +3157,7 @@
         <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
         <v>40</v>
@@ -3169,10 +3169,10 @@
         <v>14.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ14" t="n">
         <v>38</v>
@@ -3187,7 +3187,7 @@
         <v>90</v>
       </c>
       <c r="AN14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO14" t="n">
         <v>32</v>
@@ -3202,7 +3202,7 @@
         <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT14" t="n">
         <v>10.5</v>
@@ -3214,7 +3214,7 @@
         <v>11.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX14" t="n">
         <v>13</v>
@@ -3226,19 +3226,19 @@
         <v>11</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.7</v>
+        <v>28</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BC14" t="n">
         <v>19</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.7</v>
+        <v>25</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF14" t="n">
         <v>13.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
         <v>1.25</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G18" t="n">
         <v>2.3</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -4055,31 +4055,31 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G19" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I19" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J19" t="n">
         <v>4.3</v>
       </c>
       <c r="K19" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
         <v>1.17</v>
@@ -4091,7 +4091,7 @@
         <v>1.51</v>
       </c>
       <c r="R19" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="S19" t="n">
         <v>2.26</v>
@@ -4103,10 +4103,10 @@
         <v>2.46</v>
       </c>
       <c r="V19" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W19" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="X19" t="n">
         <v>29</v>
@@ -4121,58 +4121,58 @@
         <v>130</v>
       </c>
       <c r="AB19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC19" t="n">
         <v>11.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE19" t="n">
         <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
         <v>970</v>
       </c>
       <c r="AI19" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ19" t="n">
         <v>970</v>
       </c>
       <c r="AK19" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AL19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM19" t="n">
         <v>65</v>
       </c>
       <c r="AN19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO19" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT19" t="n">
         <v>11.5</v>
@@ -4181,10 +4181,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV19" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AX19" t="n">
         <v>11.5</v>
@@ -4196,29 +4196,29 @@
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC19" t="n">
         <v>13.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF19" t="n">
         <v>5.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.6</v>
+        <v>27</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="G20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H20" t="n">
         <v>2.72</v>
       </c>
-      <c r="H20" t="n">
-        <v>2.68</v>
-      </c>
       <c r="I20" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="J20" t="n">
         <v>3.65</v>
@@ -4270,43 +4270,43 @@
         <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
         <v>1.21</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q20" t="n">
         <v>1.68</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.46</v>
       </c>
-      <c r="T20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.28</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W20" t="n">
         <v>1.58</v>
       </c>
       <c r="X20" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z20" t="n">
         <v>29</v>
@@ -4315,40 +4315,40 @@
         <v>55</v>
       </c>
       <c r="AB20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH20" t="n">
         <v>20</v>
       </c>
-      <c r="AC20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>21</v>
-      </c>
       <c r="AI20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>48</v>
       </c>
-      <c r="AJ20" t="n">
-        <v>50</v>
-      </c>
       <c r="AK20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL20" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM20" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN20" t="n">
         <v>1000</v>
@@ -4357,62 +4357,62 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AV20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB20" t="n">
         <v>2.32</v>
       </c>
-      <c r="AX20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BC20" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -4443,61 +4443,61 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="G21" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="H21" t="n">
-        <v>3.05</v>
+        <v>9</v>
       </c>
       <c r="I21" t="n">
-        <v>40</v>
+        <v>10.5</v>
       </c>
       <c r="J21" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>2.26</v>
+        <v>4.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="S21" t="n">
-        <v>1.63</v>
+        <v>2.82</v>
       </c>
       <c r="T21" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W21" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y21" t="n">
         <v>1000</v>
@@ -4509,7 +4509,7 @@
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC21" t="n">
         <v>1000</v>
@@ -4524,7 +4524,7 @@
         <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH21" t="n">
         <v>1000</v>
@@ -4533,7 +4533,7 @@
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK21" t="n">
         <v>1000</v>
@@ -4545,68 +4545,68 @@
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
         <v>3.75</v>
       </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
         <v>3.55</v>
@@ -4655,16 +4655,16 @@
         <v>4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>1.98</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P22" t="n">
         <v>1.98</v>
@@ -4673,19 +4673,19 @@
         <v>1.89</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U22" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="V22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
         <v>1.86</v>
@@ -4694,113 +4694,113 @@
         <v>1000</v>
       </c>
       <c r="Y22" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK22" t="n">
         <v>22</v>
       </c>
-      <c r="Z22" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.97</v>
+        <v>6.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>17.5</v>
+        <v>7.4</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.97</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV22" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>10</v>
-      </c>
       <c r="AW22" t="n">
-        <v>1.97</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG22" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AY22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>1.97</v>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -4864,10 +4864,10 @@
         <v>2.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R23" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
         <v>2.4</v>
@@ -4909,7 +4909,7 @@
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG23" t="n">
         <v>15</v>
@@ -4921,10 +4921,10 @@
         <v>85</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL23" t="n">
         <v>44</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AQ23" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AT23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AU23" t="n">
         <v>2.1</v>
       </c>
-      <c r="AU23" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AV23" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AX23" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AY23" t="n">
-        <v>2.08</v>
+        <v>8.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BB23" t="n">
         <v>2.22</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BF23" t="n">
         <v>5.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>1.57</v>
       </c>
       <c r="G24" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H24" t="n">
         <v>4.3</v>
@@ -5037,10 +5037,10 @@
         <v>6.8</v>
       </c>
       <c r="J24" t="n">
-        <v>3.85</v>
+        <v>2.86</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L24" t="n">
         <v>1.33</v>
@@ -5076,7 +5076,7 @@
         <v>1.17</v>
       </c>
       <c r="W24" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X24" t="n">
         <v>21</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
         <v>1.78</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="H25" t="n">
         <v>2.58</v>
@@ -5252,13 +5252,13 @@
         <v>1.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="R25" t="n">
         <v>1.08</v>
       </c>
       <c r="S25" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -5413,19 +5413,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G26" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H26" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I26" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J26" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K26" t="n">
         <v>4.1</v>
@@ -5434,46 +5434,46 @@
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>1.02</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R26" t="n">
         <v>1.43</v>
       </c>
-      <c r="Q26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.42</v>
-      </c>
       <c r="S26" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="T26" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V26" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W26" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X26" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="n">
         <v>40</v>
@@ -5482,10 +5482,10 @@
         <v>23</v>
       </c>
       <c r="AC26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE26" t="n">
         <v>30</v>
@@ -5500,7 +5500,7 @@
         <v>23</v>
       </c>
       <c r="AI26" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ26" t="n">
         <v>90</v>
@@ -5518,65 +5518,65 @@
         <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.18</v>
+        <v>2.58</v>
       </c>
       <c r="AQ26" t="n">
-        <v>2.08</v>
+        <v>9.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.14</v>
+        <v>11</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.16</v>
+        <v>12.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.2</v>
+        <v>17</v>
       </c>
       <c r="AX26" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="AY26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2.16</v>
+        <v>13</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="BB26" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="BD26" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="BG26" t="n">
-        <v>2.38</v>
+        <v>9.6</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -5610,55 +5610,55 @@
         <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H27" t="n">
         <v>2.34</v>
       </c>
       <c r="I27" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J27" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K27" t="n">
         <v>3.75</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M27" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O27" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P27" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T27" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U27" t="n">
         <v>2.2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W27" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X27" t="n">
         <v>17.5</v>
@@ -5709,7 +5709,7 @@
         <v>100</v>
       </c>
       <c r="AN27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO27" t="n">
         <v>19.5</v>
@@ -5724,7 +5724,7 @@
         <v>14</v>
       </c>
       <c r="AS27" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT27" t="n">
         <v>11.5</v>
@@ -5736,7 +5736,7 @@
         <v>10</v>
       </c>
       <c r="AW27" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AX27" t="n">
         <v>20</v>
@@ -5748,29 +5748,29 @@
         <v>14.5</v>
       </c>
       <c r="BA27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF27" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BB27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BG27" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -5801,170 +5801,170 @@
         </is>
       </c>
       <c r="F28" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S28" t="n">
         <v>2.84</v>
       </c>
-      <c r="G28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K28" t="n">
+      <c r="T28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X28" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS28" t="n">
         <v>4.4</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G29" t="n">
         <v>2.74</v>
       </c>
       <c r="H29" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I29" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J29" t="n">
         <v>3.9</v>
@@ -6148,7 +6148,7 @@
         <v>30</v>
       </c>
       <c r="BE29" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BF29" t="n">
         <v>17</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="G30" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="H30" t="n">
         <v>3.65</v>
       </c>
       <c r="I30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J30" t="n">
         <v>3.1</v>
       </c>
       <c r="K30" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -6213,19 +6213,19 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O30" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="P30" t="n">
         <v>1.61</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R30" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S30" t="n">
         <v>3.85</v>
@@ -6240,7 +6240,7 @@
         <v>1.32</v>
       </c>
       <c r="W30" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="X30" t="n">
         <v>14.5</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
         <v>3.3</v>
       </c>
       <c r="H31" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I31" t="n">
         <v>2.6</v>
@@ -6398,7 +6398,7 @@
         <v>3.4</v>
       </c>
       <c r="K31" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L31" t="n">
         <v>1.32</v>
@@ -6434,7 +6434,7 @@
         <v>1.62</v>
       </c>
       <c r="W31" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X31" t="n">
         <v>18.5</v>
@@ -6449,7 +6449,7 @@
         <v>36</v>
       </c>
       <c r="AB31" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC31" t="n">
         <v>8.6</v>
@@ -6461,10 +6461,10 @@
         <v>27</v>
       </c>
       <c r="AF31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG31" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH31" t="n">
         <v>16.5</v>
@@ -6494,59 +6494,59 @@
         <v>12</v>
       </c>
       <c r="AQ31" t="n">
-        <v>9.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="AR31" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT31" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AU31" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="AW31" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="AX31" t="n">
         <v>17</v>
       </c>
       <c r="AY31" t="n">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="AZ31" t="n">
         <v>12</v>
       </c>
       <c r="BA31" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD31" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE31" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="BF31" t="n">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="BG31" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
         <v>18</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
         <v>7.4</v>
@@ -6595,34 +6595,34 @@
         <v>8.4</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N32" t="n">
-        <v>2.62</v>
+        <v>5.9</v>
       </c>
       <c r="O32" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P32" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="Q32" t="n">
         <v>1.54</v>
       </c>
       <c r="R32" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="S32" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="T32" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="U32" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="V32" t="n">
         <v>1.05</v>
@@ -6631,116 +6631,116 @@
         <v>5.2</v>
       </c>
       <c r="X32" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="Y32" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AA32" t="n">
         <v>1000</v>
       </c>
       <c r="AB32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>390</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>270</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ32" t="n">
         <v>13</v>
       </c>
-      <c r="AC32" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>95</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ32" t="n">
+      <c r="AR32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ32" t="n">
         <v>12</v>
       </c>
-      <c r="AK32" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU32" t="n">
+      <c r="BA32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC32" t="n">
         <v>12.5</v>
       </c>
-      <c r="AV32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>10</v>
-      </c>
       <c r="BD32" t="n">
-        <v>3.05</v>
+        <v>12</v>
       </c>
       <c r="BE32" t="n">
-        <v>3.15</v>
+        <v>15.5</v>
       </c>
       <c r="BF32" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BG32" t="n">
-        <v>3.15</v>
+        <v>16</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>1.2</v>
       </c>
       <c r="G33" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H33" t="n">
         <v>15.5</v>
@@ -6795,7 +6795,7 @@
         <v>1.02</v>
       </c>
       <c r="N33" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="O33" t="n">
         <v>1.11</v>
@@ -6810,19 +6810,19 @@
         <v>2.04</v>
       </c>
       <c r="S33" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="T33" t="n">
         <v>1.94</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V33" t="n">
         <v>1.06</v>
       </c>
       <c r="W33" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6837,13 +6837,13 @@
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC33" t="n">
         <v>22</v>
       </c>
       <c r="AD33" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
         <v>1000</v>
@@ -6861,7 +6861,7 @@
         <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK33" t="n">
         <v>13</v>
@@ -6873,13 +6873,13 @@
         <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="AO33" t="n">
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AQ33" t="n">
         <v>30</v>
@@ -6888,7 +6888,7 @@
         <v>44</v>
       </c>
       <c r="AS33" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="AT33" t="n">
         <v>13</v>
@@ -6921,7 +6921,7 @@
         <v>12</v>
       </c>
       <c r="BD33" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BE33" t="n">
         <v>42</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
         <v>1.25</v>
       </c>
       <c r="J34" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="K34" t="n">
         <v>9</v>
@@ -7097,7 +7097,7 @@
         <v>3.65</v>
       </c>
       <c r="AX34" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AY34" t="n">
         <v>4.4</v>
@@ -7115,10 +7115,10 @@
         <v>4.6</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BF34" t="n">
         <v>4.6</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -7159,170 +7159,170 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="G35" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="H35" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="I35" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="J35" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K35" t="n">
+        <v>5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X35" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX35" t="n">
         <v>11.5</v>
       </c>
-      <c r="L35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AY35" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -7353,40 +7353,40 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="G36" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="H36" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I36" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="J36" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="K36" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M36" t="n">
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="O36" t="n">
         <v>1.17</v>
       </c>
       <c r="P36" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="R36" t="n">
         <v>1.48</v>
@@ -7401,122 +7401,122 @@
         <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W36" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA36" t="n">
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM36" t="n">
         <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7553,7 @@
         <v>2.52</v>
       </c>
       <c r="H37" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I37" t="n">
         <v>3.05</v>
@@ -7562,13 +7562,13 @@
         <v>3.8</v>
       </c>
       <c r="K37" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L37" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M37" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N37" t="n">
         <v>5.1</v>
@@ -7586,7 +7586,7 @@
         <v>1.56</v>
       </c>
       <c r="S37" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T37" t="n">
         <v>1.57</v>
@@ -7664,7 +7664,7 @@
         <v>19.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="AT37" t="n">
         <v>12</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -7741,16 +7741,16 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G38" t="n">
         <v>2.64</v>
       </c>
       <c r="H38" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="J38" t="n">
         <v>3.8</v>
@@ -7759,19 +7759,19 @@
         <v>4.1</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M38" t="n">
         <v>1.04</v>
       </c>
       <c r="N38" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O38" t="n">
         <v>1.2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q38" t="n">
         <v>1.6</v>
@@ -7780,7 +7780,7 @@
         <v>1.57</v>
       </c>
       <c r="S38" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="T38" t="n">
         <v>1.53</v>
@@ -7810,7 +7810,7 @@
         <v>16</v>
       </c>
       <c r="AC38" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD38" t="n">
         <v>13.5</v>
@@ -7858,7 +7858,7 @@
         <v>18</v>
       </c>
       <c r="AS38" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT38" t="n">
         <v>12.5</v>
@@ -7882,10 +7882,10 @@
         <v>12.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB38" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC38" t="n">
         <v>20</v>
@@ -7894,7 +7894,7 @@
         <v>7.2</v>
       </c>
       <c r="BE38" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF38" t="n">
         <v>11.5</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -7935,79 +7935,79 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="G39" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H39" t="n">
         <v>1.82</v>
       </c>
       <c r="I39" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="J39" t="n">
         <v>3.3</v>
       </c>
       <c r="K39" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L39" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N39" t="n">
-        <v>1.54</v>
+        <v>2.94</v>
       </c>
       <c r="O39" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P39" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="Q39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T39" t="n">
         <v>2.02</v>
       </c>
-      <c r="R39" t="n">
+      <c r="U39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V39" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="W39" t="n">
         <v>1.19</v>
       </c>
-      <c r="S39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.17</v>
-      </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y39" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z39" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB39" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC39" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE39" t="n">
         <v>1000</v>
@@ -8016,10 +8016,10 @@
         <v>1000</v>
       </c>
       <c r="AG39" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AH39" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI39" t="n">
         <v>1000</v>
@@ -8040,65 +8040,65 @@
         <v>1000</v>
       </c>
       <c r="AO39" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -8132,16 +8132,16 @@
         <v>2.92</v>
       </c>
       <c r="G40" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="H40" t="n">
         <v>2.28</v>
       </c>
       <c r="I40" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="K40" t="n">
         <v>3.95</v>
@@ -8153,13 +8153,13 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="O40" t="n">
-        <v>1.14</v>
+        <v>1.56</v>
       </c>
       <c r="P40" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="Q40" t="n">
         <v>2.52</v>
@@ -8171,16 +8171,16 @@
         <v>5</v>
       </c>
       <c r="T40" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U40" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V40" t="n">
         <v>1.5</v>
       </c>
       <c r="W40" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X40" t="n">
         <v>8.800000000000001</v>
@@ -8192,7 +8192,7 @@
         <v>1000</v>
       </c>
       <c r="AA40" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB40" t="n">
         <v>10.5</v>
@@ -8201,19 +8201,19 @@
         <v>8</v>
       </c>
       <c r="AD40" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE40" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF40" t="n">
         <v>1000</v>
       </c>
       <c r="AG40" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH40" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI40" t="n">
         <v>1000</v>
@@ -8234,7 +8234,7 @@
         <v>1000</v>
       </c>
       <c r="AO40" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP40" t="n">
         <v>6.8</v>
@@ -8246,7 +8246,7 @@
         <v>13</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT40" t="n">
         <v>7.8</v>
@@ -8258,7 +8258,7 @@
         <v>11.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AX40" t="n">
         <v>18.5</v>
@@ -8270,29 +8270,29 @@
         <v>20</v>
       </c>
       <c r="BA40" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB40" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BC40" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BD40" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BE40" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>55</v>
+      </c>
+      <c r="BG40" t="n">
         <v>5.3</v>
       </c>
-      <c r="BF40" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N41" t="n">
         <v>1.01</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -8517,46 +8517,46 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G42" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H42" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="I42" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J42" t="n">
         <v>3.1</v>
       </c>
       <c r="K42" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L42" t="n">
         <v>1.58</v>
       </c>
       <c r="M42" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N42" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O42" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P42" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R42" t="n">
         <v>1.21</v>
       </c>
       <c r="S42" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T42" t="n">
         <v>2.16</v>
@@ -8565,31 +8565,31 @@
         <v>1.83</v>
       </c>
       <c r="V42" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W42" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="X42" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y42" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z42" t="n">
         <v>25</v>
       </c>
       <c r="AA42" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB42" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC42" t="n">
         <v>7</v>
       </c>
       <c r="AD42" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE42" t="n">
         <v>65</v>
@@ -8601,10 +8601,10 @@
         <v>12</v>
       </c>
       <c r="AH42" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI42" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ42" t="n">
         <v>32</v>
@@ -8616,13 +8616,13 @@
         <v>60</v>
       </c>
       <c r="AM42" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN42" t="n">
         <v>32</v>
       </c>
       <c r="AO42" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP42" t="n">
         <v>8.4</v>
@@ -8637,7 +8637,7 @@
         <v>75</v>
       </c>
       <c r="AT42" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU42" t="n">
         <v>6.6</v>
@@ -8655,16 +8655,16 @@
         <v>11</v>
       </c>
       <c r="AZ42" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA42" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BB42" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC42" t="n">
         <v>28</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>29</v>
       </c>
       <c r="BD42" t="n">
         <v>50</v>
@@ -8676,11 +8676,11 @@
         <v>28</v>
       </c>
       <c r="BG42" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -8714,167 +8714,167 @@
         <v>2.7</v>
       </c>
       <c r="G43" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H43" t="n">
         <v>2.54</v>
       </c>
       <c r="I43" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J43" t="n">
         <v>3.65</v>
       </c>
       <c r="K43" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M43" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N43" t="n">
-        <v>2.24</v>
+        <v>4.6</v>
       </c>
       <c r="O43" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P43" t="n">
         <v>2.24</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S43" t="n">
-        <v>2.46</v>
+        <v>2.78</v>
       </c>
       <c r="T43" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="U43" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="V43" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W43" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X43" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y43" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP43" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z43" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC43" t="n">
+      <c r="AQ43" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG43" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD43" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>42</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>2.84</v>
-      </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -8905,13 +8905,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G44" t="n">
         <v>2.12</v>
       </c>
       <c r="H44" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I44" t="n">
         <v>3.9</v>
@@ -8920,31 +8920,31 @@
         <v>3.75</v>
       </c>
       <c r="K44" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L44" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M44" t="n">
         <v>1.06</v>
       </c>
       <c r="N44" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O44" t="n">
         <v>1.27</v>
       </c>
       <c r="P44" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R44" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T44" t="n">
         <v>1.7</v>
@@ -8959,7 +8959,7 @@
         <v>1.89</v>
       </c>
       <c r="X44" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y44" t="n">
         <v>16.5</v>
@@ -8968,7 +8968,7 @@
         <v>28</v>
       </c>
       <c r="AA44" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB44" t="n">
         <v>11.5</v>
@@ -8980,7 +8980,7 @@
         <v>15</v>
       </c>
       <c r="AE44" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF44" t="n">
         <v>14</v>
@@ -8992,7 +8992,7 @@
         <v>15</v>
       </c>
       <c r="AI44" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ44" t="n">
         <v>25</v>
@@ -9004,7 +9004,7 @@
         <v>32</v>
       </c>
       <c r="AM44" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN44" t="n">
         <v>12.5</v>
@@ -9013,7 +9013,7 @@
         <v>36</v>
       </c>
       <c r="AP44" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ44" t="n">
         <v>15.5</v>
@@ -9043,16 +9043,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ44" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB44" t="n">
         <v>23</v>
       </c>
       <c r="BC44" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD44" t="n">
         <v>29</v>
@@ -9064,11 +9064,11 @@
         <v>12</v>
       </c>
       <c r="BG44" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G45" t="n">
         <v>25</v>
@@ -9117,7 +9117,7 @@
         <v>10.5</v>
       </c>
       <c r="L45" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M45" t="n">
         <v>1.02</v>
@@ -9135,10 +9135,10 @@
         <v>1.37</v>
       </c>
       <c r="R45" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S45" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="T45" t="n">
         <v>2.18</v>
@@ -9162,10 +9162,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AA45" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB45" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC45" t="n">
         <v>24</v>
@@ -9186,16 +9186,16 @@
         <v>46</v>
       </c>
       <c r="AI45" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ45" t="n">
         <v>1000</v>
       </c>
       <c r="AK45" t="n">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="AL45" t="n">
-        <v>230</v>
+        <v>270</v>
       </c>
       <c r="AM45" t="n">
         <v>1000</v>
@@ -9216,7 +9216,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS45" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT45" t="n">
         <v>60</v>
@@ -9225,7 +9225,7 @@
         <v>21</v>
       </c>
       <c r="AV45" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW45" t="n">
         <v>12</v>
@@ -9249,7 +9249,7 @@
         <v>110</v>
       </c>
       <c r="BD45" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BE45" t="n">
         <v>90</v>
@@ -9258,11 +9258,11 @@
         <v>110</v>
       </c>
       <c r="BG45" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
         <v>12</v>
       </c>
       <c r="I47" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J47" t="n">
         <v>7.8</v>
@@ -9553,7 +9553,7 @@
         <v>450</v>
       </c>
       <c r="AB47" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC47" t="n">
         <v>19</v>
@@ -9562,7 +9562,7 @@
         <v>44</v>
       </c>
       <c r="AE47" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF47" t="n">
         <v>11.5</v>
@@ -9571,10 +9571,10 @@
         <v>12</v>
       </c>
       <c r="AH47" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI47" t="n">
-        <v>990</v>
+        <v>95</v>
       </c>
       <c r="AJ47" t="n">
         <v>11.5</v>
@@ -9589,16 +9589,16 @@
         <v>990</v>
       </c>
       <c r="AN47" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AO47" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP47" t="n">
         <v>42</v>
       </c>
       <c r="AQ47" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AR47" t="n">
         <v>42</v>
@@ -9616,7 +9616,7 @@
         <v>38</v>
       </c>
       <c r="AW47" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX47" t="n">
         <v>10.5</v>
@@ -9628,7 +9628,7 @@
         <v>24</v>
       </c>
       <c r="BA47" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB47" t="n">
         <v>10.5</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -9681,64 +9681,64 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="G48" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="H48" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I48" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J48" t="n">
         <v>3.25</v>
       </c>
-      <c r="I48" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.46</v>
-      </c>
       <c r="K48" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N48" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="O48" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P48" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R48" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="S48" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="T48" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U48" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V48" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="W48" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="X48" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y48" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z48" t="n">
         <v>1000</v>
@@ -9747,34 +9747,34 @@
         <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC48" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD48" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE48" t="n">
         <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG48" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH48" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI48" t="n">
         <v>1000</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK48" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL48" t="n">
         <v>1000</v>
@@ -9783,68 +9783,68 @@
         <v>1000</v>
       </c>
       <c r="AN48" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO48" t="n">
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT48" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV48" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BD48" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG48" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -9878,16 +9878,16 @@
         <v>1.12</v>
       </c>
       <c r="G49" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H49" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="I49" t="n">
         <v>1000</v>
       </c>
       <c r="J49" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="K49" t="n">
         <v>1000</v>
@@ -9926,7 +9926,7 @@
         <v>1.01</v>
       </c>
       <c r="W49" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X49" t="n">
         <v>1000</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G50" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H50" t="n">
         <v>6.2</v>
@@ -10087,10 +10087,10 @@
         <v>4.4</v>
       </c>
       <c r="L50" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M50" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N50" t="n">
         <v>3.25</v>
@@ -10099,140 +10099,140 @@
         <v>1.36</v>
       </c>
       <c r="P50" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q50" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T50" t="n">
         <v>2.04</v>
       </c>
-      <c r="R50" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S50" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1.86</v>
-      </c>
       <c r="U50" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="V50" t="n">
         <v>1.15</v>
       </c>
       <c r="W50" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X50" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y50" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Z50" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA50" t="n">
         <v>1000</v>
       </c>
       <c r="AB50" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE50" t="n">
         <v>8.4</v>
       </c>
-      <c r="AC50" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>3.25</v>
-      </c>
       <c r="BF50" t="n">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="BG50" t="n">
-        <v>3.2</v>
+        <v>8.4</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10308,7 @@
         <v>1.87</v>
       </c>
       <c r="U51" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="V51" t="n">
         <v>1.06</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G52" t="n">
         <v>1.86</v>
@@ -10508,16 +10508,16 @@
         <v>1.27</v>
       </c>
       <c r="W52" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X52" t="n">
         <v>25</v>
       </c>
       <c r="Y52" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z52" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA52" t="n">
         <v>110</v>
@@ -10529,7 +10529,7 @@
         <v>10</v>
       </c>
       <c r="AD52" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE52" t="n">
         <v>50</v>
@@ -10559,10 +10559,10 @@
         <v>70</v>
       </c>
       <c r="AN52" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO52" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP52" t="n">
         <v>20</v>
@@ -10571,10 +10571,10 @@
         <v>20</v>
       </c>
       <c r="AR52" t="n">
-        <v>34</v>
+        <v>8.4</v>
       </c>
       <c r="AS52" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT52" t="n">
         <v>11</v>
@@ -10586,19 +10586,19 @@
         <v>16</v>
       </c>
       <c r="AW52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX52" t="n">
         <v>12</v>
       </c>
       <c r="AY52" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ52" t="n">
         <v>14.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB52" t="n">
         <v>18</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -10663,7 +10663,7 @@
         <v>5.1</v>
       </c>
       <c r="J53" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K53" t="n">
         <v>4.3</v>
@@ -10681,19 +10681,19 @@
         <v>1.26</v>
       </c>
       <c r="P53" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R53" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S53" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T53" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U53" t="n">
         <v>2.18</v>
@@ -10717,7 +10717,7 @@
         <v>1000</v>
       </c>
       <c r="AB53" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC53" t="n">
         <v>10.5</v>
@@ -10753,7 +10753,7 @@
         <v>1000</v>
       </c>
       <c r="AN53" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO53" t="n">
         <v>1000</v>
@@ -10780,7 +10780,7 @@
         <v>5.3</v>
       </c>
       <c r="AW53" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX53" t="n">
         <v>9.199999999999999</v>
@@ -10789,10 +10789,10 @@
         <v>9</v>
       </c>
       <c r="AZ53" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BA53" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB53" t="n">
         <v>16.5</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -10854,7 +10854,7 @@
         <v>2.7</v>
       </c>
       <c r="I54" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J54" t="n">
         <v>3.85</v>
@@ -10869,13 +10869,13 @@
         <v>1.04</v>
       </c>
       <c r="N54" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O54" t="n">
         <v>1.2</v>
       </c>
       <c r="P54" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q54" t="n">
         <v>1.63</v>
@@ -10947,10 +10947,10 @@
         <v>1000</v>
       </c>
       <c r="AN54" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO54" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP54" t="n">
         <v>19</v>
@@ -10962,7 +10962,7 @@
         <v>18</v>
       </c>
       <c r="AS54" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT54" t="n">
         <v>11.5</v>
@@ -10986,19 +10986,19 @@
         <v>11.5</v>
       </c>
       <c r="BA54" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB54" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC54" t="n">
         <v>19</v>
       </c>
       <c r="BD54" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE54" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF54" t="n">
         <v>12</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -11045,16 +11045,16 @@
         <v>1.96</v>
       </c>
       <c r="H55" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K55" t="n">
         <v>4.2</v>
-      </c>
-      <c r="I55" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J55" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K55" t="n">
-        <v>4.3</v>
       </c>
       <c r="L55" t="n">
         <v>1.35</v>
@@ -11072,13 +11072,13 @@
         <v>2.24</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R55" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S55" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T55" t="n">
         <v>1.67</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -11233,7 +11233,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="G56" t="n">
         <v>2.62</v>
@@ -11242,7 +11242,7 @@
         <v>2.96</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>3.5</v>
@@ -11251,22 +11251,22 @@
         <v>3.65</v>
       </c>
       <c r="L56" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M56" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N56" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O56" t="n">
         <v>1.3</v>
       </c>
       <c r="P56" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R56" t="n">
         <v>1.39</v>
@@ -11275,128 +11275,128 @@
         <v>3.35</v>
       </c>
       <c r="T56" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U56" t="n">
         <v>2.22</v>
       </c>
       <c r="V56" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W56" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X56" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y56" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR56" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z56" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AQ56" t="n">
+      <c r="AS56" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT56" t="n">
         <v>10</v>
       </c>
-      <c r="AR56" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AU56" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV56" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY56" t="n">
         <v>10</v>
       </c>
-      <c r="AW56" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ56" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>2.18</v>
+        <v>8</v>
       </c>
       <c r="BB56" t="n">
-        <v>2.16</v>
+        <v>7.8</v>
       </c>
       <c r="BC56" t="n">
-        <v>2.14</v>
+        <v>23</v>
       </c>
       <c r="BD56" t="n">
-        <v>2.16</v>
+        <v>7.8</v>
       </c>
       <c r="BE56" t="n">
-        <v>2.24</v>
+        <v>9</v>
       </c>
       <c r="BF56" t="n">
-        <v>2.24</v>
+        <v>15</v>
       </c>
       <c r="BG56" t="n">
-        <v>2.24</v>
+        <v>20</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -11436,7 +11436,7 @@
         <v>3.8</v>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J57" t="n">
         <v>3.8</v>
@@ -11451,22 +11451,22 @@
         <v>1.05</v>
       </c>
       <c r="N57" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O57" t="n">
         <v>1.28</v>
       </c>
       <c r="P57" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R57" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S57" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T57" t="n">
         <v>1.73</v>
@@ -11478,7 +11478,7 @@
         <v>1.33</v>
       </c>
       <c r="W57" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X57" t="n">
         <v>20</v>
@@ -11502,7 +11502,7 @@
         <v>18</v>
       </c>
       <c r="AE57" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF57" t="n">
         <v>15.5</v>
@@ -11514,7 +11514,7 @@
         <v>20</v>
       </c>
       <c r="AI57" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ57" t="n">
         <v>26</v>
@@ -11526,13 +11526,13 @@
         <v>34</v>
       </c>
       <c r="AM57" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN57" t="n">
         <v>14</v>
       </c>
       <c r="AO57" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP57" t="n">
         <v>15.5</v>
@@ -11541,10 +11541,10 @@
         <v>12.5</v>
       </c>
       <c r="AR57" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS57" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT57" t="n">
         <v>9.4</v>
@@ -11556,7 +11556,7 @@
         <v>12.5</v>
       </c>
       <c r="AW57" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX57" t="n">
         <v>10</v>
@@ -11571,26 +11571,26 @@
         <v>36</v>
       </c>
       <c r="BB57" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC57" t="n">
         <v>15.5</v>
       </c>
       <c r="BD57" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE57" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF57" t="n">
         <v>11</v>
       </c>
       <c r="BG57" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -11824,40 +11824,40 @@
         <v>3.8</v>
       </c>
       <c r="I59" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J59" t="n">
         <v>2.9</v>
       </c>
       <c r="K59" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L59" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="M59" t="n">
         <v>1.14</v>
       </c>
       <c r="N59" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="O59" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="P59" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="R59" t="n">
         <v>1.17</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T59" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U59" t="n">
         <v>1.67</v>
@@ -11881,16 +11881,16 @@
         <v>1000</v>
       </c>
       <c r="AB59" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AC59" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD59" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AE59" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF59" t="n">
         <v>13.5</v>
@@ -11917,7 +11917,7 @@
         <v>270</v>
       </c>
       <c r="AN59" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO59" t="n">
         <v>1000</v>
@@ -11929,13 +11929,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS59" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT59" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU59" t="n">
         <v>6.2</v>
@@ -11944,7 +11944,7 @@
         <v>15.5</v>
       </c>
       <c r="AW59" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX59" t="n">
         <v>11</v>
@@ -11953,32 +11953,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ59" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BA59" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB59" t="n">
         <v>7.2</v>
       </c>
-      <c r="BB59" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BC59" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD59" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE59" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF59" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG59" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12009,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G60" t="n">
         <v>2.2</v>
@@ -12039,19 +12039,19 @@
         <v>1.24</v>
       </c>
       <c r="P60" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R60" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S60" t="n">
         <v>2.88</v>
       </c>
       <c r="T60" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U60" t="n">
         <v>2.38</v>
@@ -12075,7 +12075,7 @@
         <v>1000</v>
       </c>
       <c r="AB60" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC60" t="n">
         <v>11</v>
@@ -12087,10 +12087,10 @@
         <v>1000</v>
       </c>
       <c r="AF60" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG60" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH60" t="n">
         <v>19</v>
@@ -12099,7 +12099,7 @@
         <v>48</v>
       </c>
       <c r="AJ60" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK60" t="n">
         <v>24</v>
@@ -12126,7 +12126,7 @@
         <v>19.5</v>
       </c>
       <c r="AS60" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT60" t="n">
         <v>10</v>
@@ -12138,7 +12138,7 @@
         <v>11</v>
       </c>
       <c r="AW60" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX60" t="n">
         <v>12</v>
@@ -12150,7 +12150,7 @@
         <v>12.5</v>
       </c>
       <c r="BA60" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BB60" t="n">
         <v>21</v>
@@ -12159,10 +12159,10 @@
         <v>18</v>
       </c>
       <c r="BD60" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE60" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF60" t="n">
         <v>10</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -12203,10 +12203,10 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G61" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H61" t="n">
         <v>3.65</v>
@@ -12218,7 +12218,7 @@
         <v>3.95</v>
       </c>
       <c r="K61" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L61" t="n">
         <v>1.31</v>
@@ -12239,7 +12239,7 @@
         <v>1.63</v>
       </c>
       <c r="R61" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S61" t="n">
         <v>2.6</v>
@@ -12254,7 +12254,7 @@
         <v>1.35</v>
       </c>
       <c r="W61" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X61" t="n">
         <v>28</v>
@@ -12290,7 +12290,7 @@
         <v>17.5</v>
       </c>
       <c r="AI61" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AJ61" t="n">
         <v>25</v>
@@ -12317,10 +12317,10 @@
         <v>16</v>
       </c>
       <c r="AR61" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS61" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT61" t="n">
         <v>10.5</v>
@@ -12332,7 +12332,7 @@
         <v>13.5</v>
       </c>
       <c r="AW61" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX61" t="n">
         <v>12</v>
@@ -12356,17 +12356,17 @@
         <v>20</v>
       </c>
       <c r="BE61" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF61" t="n">
         <v>8.6</v>
       </c>
       <c r="BG61" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G62" t="n">
         <v>1.87</v>
@@ -12409,158 +12409,158 @@
         <v>5.9</v>
       </c>
       <c r="J62" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K62" t="n">
         <v>4.2</v>
       </c>
       <c r="L62" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M62" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N62" t="n">
-        <v>1.78</v>
+        <v>3.7</v>
       </c>
       <c r="O62" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P62" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="R62" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S62" t="n">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="T62" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U62" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V62" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W62" t="n">
         <v>2.14</v>
       </c>
       <c r="X62" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y62" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z62" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA62" t="n">
         <v>1000</v>
       </c>
       <c r="AB62" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC62" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD62" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE62" t="n">
         <v>1000</v>
       </c>
       <c r="AF62" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG62" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH62" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI62" t="n">
         <v>1000</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK62" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL62" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM62" t="n">
         <v>1000</v>
       </c>
       <c r="AN62" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO62" t="n">
         <v>1000</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT62" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU62" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV62" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX62" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY62" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ62" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA62" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB62" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC62" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD62" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE62" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF62" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG62" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -12669,7 +12669,7 @@
         <v>15</v>
       </c>
       <c r="AF63" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AG63" t="n">
         <v>30</v>
@@ -12687,7 +12687,7 @@
         <v>90</v>
       </c>
       <c r="AL63" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM63" t="n">
         <v>85</v>
@@ -12723,7 +12723,7 @@
         <v>12</v>
       </c>
       <c r="AX63" t="n">
-        <v>8.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="AY63" t="n">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>8.4</v>
       </c>
       <c r="BD63" t="n">
-        <v>8.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="BE63" t="n">
         <v>8.4</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -12788,7 +12788,7 @@
         <v>4.6</v>
       </c>
       <c r="G64" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H64" t="n">
         <v>1.87</v>
@@ -12806,25 +12806,25 @@
         <v>1.38</v>
       </c>
       <c r="M64" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N64" t="n">
-        <v>1.79</v>
+        <v>3.45</v>
       </c>
       <c r="O64" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="P64" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="R64" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S64" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="T64" t="n">
         <v>1.9</v>
@@ -12833,13 +12833,13 @@
         <v>1.98</v>
       </c>
       <c r="V64" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W64" t="n">
         <v>1.24</v>
       </c>
       <c r="X64" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y64" t="n">
         <v>9.6</v>
@@ -12851,7 +12851,7 @@
         <v>25</v>
       </c>
       <c r="AB64" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC64" t="n">
         <v>9.6</v>
@@ -12887,7 +12887,7 @@
         <v>1000</v>
       </c>
       <c r="AN64" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO64" t="n">
         <v>16.5</v>
@@ -12917,7 +12917,7 @@
         <v>16</v>
       </c>
       <c r="AX64" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY64" t="n">
         <v>14.5</v>
@@ -12926,29 +12926,29 @@
         <v>17.5</v>
       </c>
       <c r="BA64" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB64" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD64" t="n">
         <v>5.3</v>
       </c>
-      <c r="BC64" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD64" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BE64" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF64" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG64" t="n">
         <v>11</v>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -12979,7 +12979,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="G65" t="n">
         <v>1.8</v>
@@ -12997,10 +12997,10 @@
         <v>4.9</v>
       </c>
       <c r="L65" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M65" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N65" t="n">
         <v>5.6</v>
@@ -13027,7 +13027,7 @@
         <v>2.44</v>
       </c>
       <c r="V65" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W65" t="n">
         <v>2.24</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -13188,155 +13188,155 @@
         <v>3</v>
       </c>
       <c r="K66" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L66" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M66" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N66" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="O66" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P66" t="n">
         <v>1.6</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R66" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="T66" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="U66" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="V66" t="n">
         <v>1.56</v>
       </c>
       <c r="W66" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X66" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD66" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y66" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA66" t="n">
+      <c r="AE66" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI66" t="n">
         <v>65</v>
       </c>
-      <c r="AB66" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>85</v>
-      </c>
       <c r="AJ66" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AK66" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL66" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AM66" t="n">
         <v>1000</v>
       </c>
       <c r="AN66" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO66" t="n">
         <v>1000</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.22</v>
+        <v>8.4</v>
       </c>
       <c r="AQ66" t="n">
-        <v>2.18</v>
+        <v>7.4</v>
       </c>
       <c r="AR66" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV66" t="n">
         <v>11</v>
       </c>
-      <c r="AS66" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AU66" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AV66" t="n">
-        <v>2.32</v>
-      </c>
       <c r="AW66" t="n">
-        <v>2.52</v>
+        <v>7.2</v>
       </c>
       <c r="AX66" t="n">
-        <v>2.44</v>
+        <v>17.5</v>
       </c>
       <c r="AY66" t="n">
-        <v>2.36</v>
+        <v>12</v>
       </c>
       <c r="AZ66" t="n">
-        <v>2.44</v>
+        <v>17.5</v>
       </c>
       <c r="BA66" t="n">
-        <v>2.58</v>
+        <v>7.8</v>
       </c>
       <c r="BB66" t="n">
-        <v>2.58</v>
+        <v>8</v>
       </c>
       <c r="BC66" t="n">
-        <v>2.54</v>
+        <v>7.6</v>
       </c>
       <c r="BD66" t="n">
-        <v>2.58</v>
+        <v>7.8</v>
       </c>
       <c r="BE66" t="n">
-        <v>2.64</v>
+        <v>8.4</v>
       </c>
       <c r="BF66" t="n">
-        <v>2.64</v>
+        <v>7.8</v>
       </c>
       <c r="BG66" t="n">
-        <v>2.64</v>
+        <v>7.4</v>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -13370,10 +13370,10 @@
         <v>2.32</v>
       </c>
       <c r="G67" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H67" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I67" t="n">
         <v>2.98</v>
@@ -13412,13 +13412,13 @@
         <v>1.47</v>
       </c>
       <c r="U67" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="V67" t="n">
         <v>1.5</v>
       </c>
       <c r="W67" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X67" t="n">
         <v>30</v>
@@ -13430,7 +13430,7 @@
         <v>27</v>
       </c>
       <c r="AA67" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AB67" t="n">
         <v>18</v>
@@ -13448,7 +13448,7 @@
         <v>21</v>
       </c>
       <c r="AG67" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH67" t="n">
         <v>14.5</v>
@@ -13478,7 +13478,7 @@
         <v>27</v>
       </c>
       <c r="AQ67" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR67" t="n">
         <v>22</v>
@@ -13490,7 +13490,7 @@
         <v>15.5</v>
       </c>
       <c r="AU67" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV67" t="n">
         <v>12.5</v>
@@ -13499,7 +13499,7 @@
         <v>23</v>
       </c>
       <c r="AX67" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AY67" t="n">
         <v>10.5</v>
@@ -13523,14 +13523,14 @@
         <v>25</v>
       </c>
       <c r="BF67" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG67" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -13561,46 +13561,46 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G68" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H68" t="n">
         <v>7</v>
       </c>
       <c r="I68" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J68" t="n">
         <v>5.7</v>
       </c>
       <c r="K68" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L68" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M68" t="n">
         <v>1.02</v>
       </c>
       <c r="N68" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O68" t="n">
         <v>1.15</v>
       </c>
       <c r="P68" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R68" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S68" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="T68" t="n">
         <v>1.68</v>
@@ -13612,7 +13612,7 @@
         <v>1.14</v>
       </c>
       <c r="W68" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X68" t="n">
         <v>1000</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>
@@ -13755,106 +13755,106 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G69" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="H69" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I69" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J69" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K69" t="n">
         <v>4.9</v>
       </c>
       <c r="L69" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M69" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N69" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O69" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P69" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R69" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S69" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="T69" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U69" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V69" t="n">
         <v>1.2</v>
       </c>
       <c r="W69" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="X69" t="n">
         <v>27</v>
       </c>
       <c r="Y69" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z69" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA69" t="n">
         <v>1000</v>
       </c>
       <c r="AB69" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC69" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD69" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE69" t="n">
         <v>70</v>
       </c>
       <c r="AF69" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG69" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH69" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI69" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ69" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK69" t="n">
         <v>16.5</v>
       </c>
       <c r="AL69" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM69" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN69" t="n">
         <v>7.4</v>
@@ -13869,10 +13869,10 @@
         <v>20</v>
       </c>
       <c r="AR69" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AS69" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="AT69" t="n">
         <v>9.6</v>
@@ -13881,10 +13881,10 @@
         <v>9</v>
       </c>
       <c r="AV69" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW69" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX69" t="n">
         <v>10</v>
@@ -13896,29 +13896,29 @@
         <v>15.5</v>
       </c>
       <c r="BA69" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB69" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC69" t="n">
         <v>13.5</v>
       </c>
       <c r="BD69" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BE69" t="n">
-        <v>5.5</v>
+        <v>55</v>
       </c>
       <c r="BF69" t="n">
         <v>5.9</v>
       </c>
       <c r="BG69" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-21 02:18:52</t>
+          <t>2026-04-21 04:33:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
@@ -766,7 +766,7 @@
         <v>7.2</v>
       </c>
       <c r="I2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J2" t="n">
         <v>4.9</v>
@@ -778,31 +778,31 @@
         <v>1.3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
         <v>5.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P2" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T2" t="n">
         <v>1.79</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V2" t="n">
         <v>1.15</v>
@@ -811,43 +811,43 @@
         <v>2.98</v>
       </c>
       <c r="X2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y2" t="n">
         <v>32</v>
       </c>
       <c r="Z2" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AA2" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF2" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>11</v>
-      </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI2" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AJ2" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AK2" t="n">
         <v>18</v>
@@ -859,37 +859,37 @@
         <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="AT2" t="n">
         <v>9</v>
       </c>
       <c r="AU2" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>19.5</v>
+        <v>4.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY2" t="n">
         <v>8.800000000000001</v>
@@ -898,29 +898,29 @@
         <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="BB2" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BC2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
         <v>5.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -951,61 +951,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G3" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="H3" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="I3" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="U3" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="W3" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
         <v>11.5</v>
@@ -1020,13 +1020,13 @@
         <v>17</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
         <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF3" t="n">
         <v>30</v>
@@ -1056,19 +1056,19 @@
         <v>42</v>
       </c>
       <c r="AO3" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AP3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR3" t="n">
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AT3" t="n">
         <v>13.5</v>
@@ -1077,13 +1077,13 @@
         <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AY3" t="n">
         <v>14</v>
@@ -1095,26 +1095,26 @@
         <v>26</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
         <v>1.92</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
         <v>3.3</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -1363,19 +1363,19 @@
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
         <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
         <v>3.15</v>
@@ -1453,10 +1453,10 @@
         <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
         <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
@@ -1480,29 +1480,29 @@
         <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>32</v>
+        <v>8.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>32</v>
+        <v>8.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
         <v>19</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="G6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H6" t="n">
         <v>8.199999999999999</v>
@@ -1545,7 +1545,7 @@
         <v>9.4</v>
       </c>
       <c r="J6" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="K6" t="n">
         <v>6.2</v>
@@ -1557,25 +1557,25 @@
         <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O6" t="n">
         <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R6" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="S6" t="n">
         <v>2.28</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U6" t="n">
         <v>2.16</v>
@@ -1584,25 +1584,25 @@
         <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="X6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y6" t="n">
         <v>38</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA6" t="n">
         <v>290</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD6" t="n">
         <v>34</v>
@@ -1635,13 +1635,13 @@
         <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AQ6" t="n">
         <v>21</v>
@@ -1656,10 +1656,10 @@
         <v>10.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV6" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW6" t="n">
         <v>38</v>
@@ -1668,16 +1668,16 @@
         <v>9</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC6" t="n">
         <v>12</v>
@@ -1689,14 +1689,14 @@
         <v>38</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG6" t="n">
         <v>38</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
@@ -1757,22 +1757,22 @@
         <v>1.55</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V7" t="n">
         <v>1.44</v>
@@ -1841,7 +1841,7 @@
         <v>7.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS7" t="n">
         <v>40</v>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="AX7" t="n">
         <v>15</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -1978,34 +1978,34 @@
         <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB8" t="n">
         <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG8" t="n">
         <v>16</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
         <v>75</v>
@@ -2017,7 +2017,7 @@
         <v>48</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
         <v>180</v>
@@ -2026,19 +2026,19 @@
         <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AQ8" t="n">
         <v>7.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AT8" t="n">
         <v>7.8</v>
@@ -2047,13 +2047,13 @@
         <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AX8" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AY8" t="n">
         <v>11</v>
@@ -2062,29 +2062,29 @@
         <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G9" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H9" t="n">
         <v>3.75</v>
       </c>
       <c r="I9" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
         <v>1.09</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.54</v>
@@ -2166,7 +2166,7 @@
         <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X9" t="n">
         <v>8.6</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -2450,10 +2450,10 @@
         <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="BB10" t="n">
-        <v>15.5</v>
+        <v>2.34</v>
       </c>
       <c r="BC10" t="n">
         <v>13</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G11" t="n">
         <v>2.44</v>
@@ -2518,7 +2518,7 @@
         <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -2700,10 +2700,10 @@
         <v>2.24</v>
       </c>
       <c r="G12" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I12" t="n">
         <v>3.7</v>
@@ -2721,22 +2721,22 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
         <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R12" t="n">
         <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
         <v>1.67</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>1.49</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2915,34 +2915,34 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="O13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>2.48</v>
       </c>
       <c r="Q13" t="n">
         <v>1.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.68</v>
       </c>
       <c r="S13" t="n">
-        <v>1.58</v>
+        <v>2.08</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2972,7 +2972,7 @@
         <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH13" t="n">
         <v>1000</v>
@@ -2981,7 +2981,7 @@
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>1.63</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>1.77</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>1.71</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>2.44</v>
       </c>
       <c r="G14" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H14" t="n">
         <v>2.88</v>
@@ -3124,7 +3124,7 @@
         <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T14" t="n">
         <v>1.65</v>
@@ -3181,7 +3181,7 @@
         <v>28</v>
       </c>
       <c r="AL14" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM14" t="n">
         <v>90</v>
@@ -3202,7 +3202,7 @@
         <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT14" t="n">
         <v>10.5</v>
@@ -3229,7 +3229,7 @@
         <v>28</v>
       </c>
       <c r="BB14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC14" t="n">
         <v>19</v>
@@ -3238,7 +3238,7 @@
         <v>25</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF14" t="n">
         <v>13.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -3473,58 +3473,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>1.65</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>3.95</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O16" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3542,7 +3542,7 @@
         <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD16" t="n">
         <v>1000</v>
@@ -3554,7 +3554,7 @@
         <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
         <v>1000</v>
@@ -3575,68 +3575,68 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -3667,58 +3667,58 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M17" t="n">
         <v>1.04</v>
       </c>
-      <c r="G17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N17" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O17" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="S17" t="n">
-        <v>1.15</v>
+        <v>2.32</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3775,62 +3775,62 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>1.7</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="H18" t="n">
         <v>4.1</v>
@@ -3873,7 +3873,7 @@
         <v>6.4</v>
       </c>
       <c r="J18" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="K18" t="n">
         <v>950</v>
@@ -3912,7 +3912,7 @@
         <v>1.19</v>
       </c>
       <c r="W18" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -4058,13 +4058,13 @@
         <v>1.64</v>
       </c>
       <c r="G19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H19" t="n">
         <v>4.8</v>
       </c>
       <c r="I19" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J19" t="n">
         <v>4.3</v>
@@ -4091,25 +4091,25 @@
         <v>1.51</v>
       </c>
       <c r="R19" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S19" t="n">
         <v>2.26</v>
       </c>
       <c r="T19" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U19" t="n">
         <v>2.46</v>
       </c>
       <c r="V19" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W19" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y19" t="n">
         <v>34</v>
@@ -4172,7 +4172,7 @@
         <v>9.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT19" t="n">
         <v>11.5</v>
@@ -4184,7 +4184,7 @@
         <v>17.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX19" t="n">
         <v>11.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G20" t="n">
         <v>2.7</v>
       </c>
       <c r="H20" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I20" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J20" t="n">
         <v>3.65</v>
@@ -4288,13 +4288,13 @@
         <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U20" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V20" t="n">
         <v>1.51</v>
@@ -4357,22 +4357,22 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>2.44</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>2.16</v>
-      </c>
       <c r="AR20" t="n">
-        <v>2.24</v>
+        <v>2.54</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="AV20" t="n">
         <v>9.6</v>
@@ -4381,38 +4381,38 @@
         <v>20</v>
       </c>
       <c r="AX20" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="AY20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="BA20" t="n">
         <v>24</v>
       </c>
       <c r="BB20" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -4443,52 +4443,52 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="G21" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="H21" t="n">
         <v>9</v>
       </c>
       <c r="I21" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="J21" t="n">
         <v>4.9</v>
       </c>
       <c r="K21" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N21" t="n">
         <v>4.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P21" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S21" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U21" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V21" t="n">
         <v>1.1</v>
@@ -4500,7 +4500,7 @@
         <v>24</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z21" t="n">
         <v>1000</v>
@@ -4533,13 +4533,13 @@
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK21" t="n">
         <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM21" t="n">
         <v>1000</v>
@@ -4551,62 +4551,62 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW21" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AX21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA21" t="n">
         <v>6.6</v>
       </c>
-      <c r="AY21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>7</v>
-      </c>
       <c r="BB21" t="n">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="BC21" t="n">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>1.98</v>
       </c>
       <c r="G22" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H22" t="n">
         <v>3.75</v>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
         <v>3.55</v>
@@ -4685,10 +4685,10 @@
         <v>2.12</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.53</v>
+        <v>1.09</v>
       </c>
       <c r="G23" t="n">
         <v>1.89</v>
@@ -4855,13 +4855,13 @@
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="O23" t="n">
         <v>1.21</v>
       </c>
       <c r="P23" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
         <v>1.58</v>
@@ -4966,7 +4966,7 @@
         <v>2.14</v>
       </c>
       <c r="AY23" t="n">
-        <v>8.4</v>
+        <v>2.1</v>
       </c>
       <c r="AZ23" t="n">
         <v>2.26</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>1.57</v>
       </c>
       <c r="G24" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="H24" t="n">
         <v>4.3</v>
@@ -5037,7 +5037,7 @@
         <v>6.8</v>
       </c>
       <c r="J24" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="K24" t="n">
         <v>950</v>
@@ -5046,7 +5046,7 @@
         <v>1.33</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
         <v>3.35</v>
@@ -5076,10 +5076,10 @@
         <v>1.17</v>
       </c>
       <c r="W24" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="X24" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
         <v>26</v>
@@ -5136,59 +5136,59 @@
         <v>2.64</v>
       </c>
       <c r="AQ24" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.86</v>
+        <v>2.52</v>
       </c>
       <c r="AS24" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="AV24" t="n">
         <v>14.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.92</v>
+        <v>2.58</v>
       </c>
       <c r="AX24" t="n">
-        <v>2.52</v>
+        <v>2.24</v>
       </c>
       <c r="AY24" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.72</v>
+        <v>2.42</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.92</v>
+        <v>2.58</v>
       </c>
       <c r="BB24" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="BF24" t="n">
         <v>7.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>2.98</v>
+        <v>2.64</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="G25" t="n">
         <v>2.82</v>
       </c>
       <c r="H25" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="I25" t="n">
         <v>4.5</v>
@@ -5234,7 +5234,7 @@
         <v>2.36</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5243,7 +5243,7 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="O25" t="n">
         <v>1.31</v>
@@ -5252,13 +5252,13 @@
         <v>1.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="R25" t="n">
         <v>1.08</v>
       </c>
       <c r="S25" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
         <v>30</v>
       </c>
       <c r="AF26" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG26" t="n">
         <v>21</v>
@@ -5500,7 +5500,7 @@
         <v>23</v>
       </c>
       <c r="AI26" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ26" t="n">
         <v>90</v>
@@ -5521,7 +5521,7 @@
         <v>19</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="AQ26" t="n">
         <v>9.4</v>
@@ -5533,7 +5533,7 @@
         <v>2.42</v>
       </c>
       <c r="AT26" t="n">
-        <v>12.5</v>
+        <v>2.32</v>
       </c>
       <c r="AU26" t="n">
         <v>7.4</v>
@@ -5557,7 +5557,7 @@
         <v>2.44</v>
       </c>
       <c r="BB26" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BC26" t="n">
         <v>2.46</v>
@@ -5566,17 +5566,17 @@
         <v>2.48</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
         <v>2.34</v>
       </c>
       <c r="I27" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J27" t="n">
         <v>3.55</v>
@@ -5625,7 +5625,7 @@
         <v>3.75</v>
       </c>
       <c r="L27" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M27" t="n">
         <v>1.06</v>
@@ -5634,7 +5634,7 @@
         <v>3.85</v>
       </c>
       <c r="O27" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P27" t="n">
         <v>1.98</v>
@@ -5670,7 +5670,7 @@
         <v>16.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AB27" t="n">
         <v>13.5</v>
@@ -5682,10 +5682,10 @@
         <v>12</v>
       </c>
       <c r="AE27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF27" t="n">
         <v>26</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>23</v>
       </c>
       <c r="AG27" t="n">
         <v>14</v>
@@ -5694,7 +5694,7 @@
         <v>17</v>
       </c>
       <c r="AI27" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ27" t="n">
         <v>55</v>
@@ -5709,7 +5709,7 @@
         <v>100</v>
       </c>
       <c r="AN27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO27" t="n">
         <v>19.5</v>
@@ -5724,7 +5724,7 @@
         <v>14</v>
       </c>
       <c r="AS27" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AT27" t="n">
         <v>11.5</v>
@@ -5736,10 +5736,10 @@
         <v>10</v>
       </c>
       <c r="AW27" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX27" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AY27" t="n">
         <v>12</v>
@@ -5748,29 +5748,29 @@
         <v>14.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BB27" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC27" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="BD27" t="n">
-        <v>9.4</v>
+        <v>34</v>
       </c>
       <c r="BE27" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF27" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BG27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -5948,10 +5948,10 @@
         <v>4.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>22</v>
+        <v>4.3</v>
       </c>
       <c r="BD28" t="n">
-        <v>26</v>
+        <v>4.4</v>
       </c>
       <c r="BE28" t="n">
         <v>4.6</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -5998,10 +5998,10 @@
         <v>2.72</v>
       </c>
       <c r="G29" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H29" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I29" t="n">
         <v>2.66</v>
@@ -6028,7 +6028,7 @@
         <v>2.26</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R29" t="n">
         <v>1.5</v>
@@ -6046,19 +6046,19 @@
         <v>1.6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X29" t="n">
         <v>19.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB29" t="n">
         <v>14</v>
@@ -6097,10 +6097,10 @@
         <v>70</v>
       </c>
       <c r="AN29" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP29" t="n">
         <v>17.5</v>
@@ -6118,7 +6118,7 @@
         <v>13</v>
       </c>
       <c r="AU29" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV29" t="n">
         <v>11.5</v>
@@ -6139,7 +6139,7 @@
         <v>30</v>
       </c>
       <c r="BB29" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC29" t="n">
         <v>24</v>
@@ -6151,14 +6151,14 @@
         <v>60</v>
       </c>
       <c r="BF29" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG29" t="n">
         <v>16.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
         <v>3.65</v>
       </c>
       <c r="I30" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J30" t="n">
         <v>3.1</v>
@@ -6213,16 +6213,16 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="O30" t="n">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="P30" t="n">
         <v>1.61</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="R30" t="n">
         <v>1.19</v>
@@ -6240,7 +6240,7 @@
         <v>1.32</v>
       </c>
       <c r="W30" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="X30" t="n">
         <v>14.5</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
         <v>3.75</v>
       </c>
       <c r="L31" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M31" t="n">
         <v>1.06</v>
@@ -6425,10 +6425,10 @@
         <v>3.05</v>
       </c>
       <c r="T31" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U31" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V31" t="n">
         <v>1.62</v>
@@ -6440,113 +6440,113 @@
         <v>18.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA31" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD31" t="n">
         <v>14</v>
       </c>
-      <c r="AC31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AE31" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AF31" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AG31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ31" t="n">
         <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL31" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AP31" t="n">
         <v>12</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5.2</v>
+        <v>9.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT31" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU31" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.6</v>
+        <v>19.5</v>
       </c>
       <c r="AX31" t="n">
         <v>17</v>
       </c>
       <c r="AY31" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
         <v>12</v>
       </c>
       <c r="BA31" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB31" t="n">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="BC31" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="BD31" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE31" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="BF31" t="n">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="BG31" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="G32" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="H32" t="n">
         <v>18</v>
@@ -6589,10 +6589,10 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="K32" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="L32" t="n">
         <v>1.24</v>
@@ -6601,34 +6601,34 @@
         <v>1.03</v>
       </c>
       <c r="N32" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
         <v>1.18</v>
       </c>
       <c r="P32" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q32" t="n">
         <v>1.54</v>
       </c>
       <c r="R32" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S32" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T32" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V32" t="n">
         <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="X32" t="n">
         <v>30</v>
@@ -6643,10 +6643,10 @@
         <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AD32" t="n">
         <v>70</v>
@@ -6655,19 +6655,19 @@
         <v>390</v>
       </c>
       <c r="AF32" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AG32" t="n">
         <v>12.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AI32" t="n">
         <v>270</v>
       </c>
       <c r="AJ32" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK32" t="n">
         <v>15</v>
@@ -6676,7 +6676,7 @@
         <v>48</v>
       </c>
       <c r="AM32" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AN32" t="n">
         <v>3.75</v>
@@ -6685,28 +6685,28 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ32" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AS32" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT32" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU32" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AV32" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AW32" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX32" t="n">
         <v>7</v>
@@ -6715,32 +6715,32 @@
         <v>11</v>
       </c>
       <c r="AZ32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA32" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BB32" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC32" t="n">
         <v>12.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BE32" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BF32" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -6789,13 +6789,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M33" t="n">
         <v>1.02</v>
       </c>
       <c r="N33" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="O33" t="n">
         <v>1.11</v>
@@ -6816,7 +6816,7 @@
         <v>1.94</v>
       </c>
       <c r="U33" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V33" t="n">
         <v>1.06</v>
@@ -6861,7 +6861,7 @@
         <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AK33" t="n">
         <v>13</v>
@@ -6873,7 +6873,7 @@
         <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="AO33" t="n">
         <v>1000</v>
@@ -6882,13 +6882,13 @@
         <v>38</v>
       </c>
       <c r="AQ33" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AR33" t="n">
         <v>44</v>
       </c>
       <c r="AS33" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AT33" t="n">
         <v>13</v>
@@ -6924,7 +6924,7 @@
         <v>29</v>
       </c>
       <c r="BE33" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="BF33" t="n">
         <v>2.88</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.49</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G34" t="n">
         <v>20</v>
       </c>
       <c r="H34" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="I34" t="n">
         <v>1.25</v>
       </c>
       <c r="J34" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="K34" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="L34" t="n">
         <v>1.2</v>
@@ -7007,13 +7007,13 @@
         <v>1.91</v>
       </c>
       <c r="T34" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U34" t="n">
         <v>1.73</v>
       </c>
       <c r="V34" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="W34" t="n">
         <v>1.05</v>
@@ -7040,7 +7040,7 @@
         <v>15.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AF34" t="n">
         <v>1000</v>
@@ -7079,28 +7079,28 @@
         <v>3.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AS34" t="n">
         <v>3.3</v>
       </c>
       <c r="AT34" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AV34" t="n">
         <v>3.6</v>
       </c>
       <c r="AW34" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AX34" t="n">
         <v>4.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AZ34" t="n">
         <v>4.2</v>
@@ -7109,10 +7109,10 @@
         <v>4.2</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BD34" t="n">
         <v>4.5</v>
@@ -7124,11 +7124,11 @@
         <v>4.6</v>
       </c>
       <c r="BG34" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -7159,16 +7159,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G35" t="n">
         <v>1.91</v>
       </c>
       <c r="H35" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I35" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J35" t="n">
         <v>3.9</v>
@@ -7192,22 +7192,22 @@
         <v>2.76</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R35" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="S35" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="T35" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="U35" t="n">
         <v>2.52</v>
       </c>
       <c r="V35" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W35" t="n">
         <v>2.08</v>
@@ -7219,7 +7219,7 @@
         <v>29</v>
       </c>
       <c r="Z35" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA35" t="n">
         <v>95</v>
@@ -7231,7 +7231,7 @@
         <v>13</v>
       </c>
       <c r="AD35" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE35" t="n">
         <v>50</v>
@@ -7252,7 +7252,7 @@
         <v>24</v>
       </c>
       <c r="AK35" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL35" t="n">
         <v>29</v>
@@ -7276,7 +7276,7 @@
         <v>4.6</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT35" t="n">
         <v>11</v>
@@ -7288,7 +7288,7 @@
         <v>14</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX35" t="n">
         <v>11.5</v>
@@ -7312,17 +7312,17 @@
         <v>18.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF35" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG35" t="n">
-        <v>21</v>
+        <v>4.4</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
         <v>1.84</v>
       </c>
       <c r="G36" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="H36" t="n">
         <v>3.75</v>
@@ -7365,7 +7365,7 @@
         <v>4.8</v>
       </c>
       <c r="J36" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K36" t="n">
         <v>4.7</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -7622,10 +7622,10 @@
         <v>14</v>
       </c>
       <c r="AE37" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AF37" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AG37" t="n">
         <v>12.5</v>
@@ -7652,7 +7652,7 @@
         <v>14.5</v>
       </c>
       <c r="AO37" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AP37" t="n">
         <v>19</v>
@@ -7664,22 +7664,22 @@
         <v>19.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>36</v>
+        <v>6.6</v>
       </c>
       <c r="AT37" t="n">
         <v>12</v>
       </c>
       <c r="AU37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV37" t="n">
         <v>11.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AX37" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY37" t="n">
         <v>10</v>
@@ -7688,29 +7688,29 @@
         <v>12.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BB37" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BC37" t="n">
         <v>19.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="BE37" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BF37" t="n">
         <v>10</v>
       </c>
       <c r="BG37" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -7765,13 +7765,13 @@
         <v>1.04</v>
       </c>
       <c r="N38" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="O38" t="n">
         <v>1.2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q38" t="n">
         <v>1.6</v>
@@ -7834,7 +7834,7 @@
         <v>38</v>
       </c>
       <c r="AK38" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL38" t="n">
         <v>32</v>
@@ -7843,7 +7843,7 @@
         <v>60</v>
       </c>
       <c r="AN38" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO38" t="n">
         <v>18</v>
@@ -7858,7 +7858,7 @@
         <v>18</v>
       </c>
       <c r="AS38" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT38" t="n">
         <v>12.5</v>
@@ -7870,7 +7870,7 @@
         <v>11</v>
       </c>
       <c r="AW38" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX38" t="n">
         <v>16.5</v>
@@ -7882,19 +7882,19 @@
         <v>12.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB38" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC38" t="n">
         <v>20</v>
       </c>
       <c r="BD38" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE38" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF38" t="n">
         <v>11.5</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G39" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="H39" t="n">
         <v>1.82</v>
       </c>
       <c r="I39" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="J39" t="n">
         <v>3.3</v>
       </c>
       <c r="K39" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L39" t="n">
         <v>1.47</v>
@@ -7968,7 +7968,7 @@
         <v>1.66</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R39" t="n">
         <v>1.24</v>
@@ -7983,10 +7983,10 @@
         <v>1.79</v>
       </c>
       <c r="V39" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="W39" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X39" t="n">
         <v>13</v>
@@ -8016,7 +8016,7 @@
         <v>1000</v>
       </c>
       <c r="AG39" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH39" t="n">
         <v>29</v>
@@ -8082,7 +8082,7 @@
         <v>4.3</v>
       </c>
       <c r="BC39" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BD39" t="n">
         <v>4.3</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -8129,13 +8129,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G40" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H40" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="I40" t="n">
         <v>3</v>
@@ -8144,7 +8144,7 @@
         <v>2.62</v>
       </c>
       <c r="K40" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -8153,16 +8153,16 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>2.38</v>
+        <v>1.52</v>
       </c>
       <c r="O40" t="n">
         <v>1.56</v>
       </c>
       <c r="P40" t="n">
-        <v>1.39</v>
+        <v>1.14</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="R40" t="n">
         <v>1.14</v>
@@ -8258,7 +8258,7 @@
         <v>11.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX40" t="n">
         <v>18.5</v>
@@ -8270,16 +8270,16 @@
         <v>20</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB40" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC40" t="n">
         <v>5.4</v>
       </c>
       <c r="BD40" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE40" t="n">
         <v>5.7</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -8523,13 +8523,13 @@
         <v>2.38</v>
       </c>
       <c r="H42" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I42" t="n">
         <v>3.85</v>
       </c>
       <c r="J42" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K42" t="n">
         <v>3.2</v>
@@ -8541,10 +8541,10 @@
         <v>1.12</v>
       </c>
       <c r="N42" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O42" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P42" t="n">
         <v>1.59</v>
@@ -8571,10 +8571,10 @@
         <v>1.72</v>
       </c>
       <c r="X42" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y42" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z42" t="n">
         <v>25</v>
@@ -8595,7 +8595,7 @@
         <v>65</v>
       </c>
       <c r="AF42" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG42" t="n">
         <v>12</v>
@@ -8616,7 +8616,7 @@
         <v>60</v>
       </c>
       <c r="AM42" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN42" t="n">
         <v>32</v>
@@ -8628,7 +8628,7 @@
         <v>8.4</v>
       </c>
       <c r="AQ42" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR42" t="n">
         <v>23</v>
@@ -8664,7 +8664,7 @@
         <v>29</v>
       </c>
       <c r="BC42" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD42" t="n">
         <v>50</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -8711,16 +8711,16 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="G43" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H43" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="I43" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="J43" t="n">
         <v>3.65</v>
@@ -8744,7 +8744,7 @@
         <v>2.24</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R43" t="n">
         <v>1.5</v>
@@ -8759,10 +8759,10 @@
         <v>2.36</v>
       </c>
       <c r="V43" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W43" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X43" t="n">
         <v>21</v>
@@ -8801,10 +8801,10 @@
         <v>36</v>
       </c>
       <c r="AJ43" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK43" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL43" t="n">
         <v>38</v>
@@ -8828,7 +8828,7 @@
         <v>16</v>
       </c>
       <c r="AS43" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT43" t="n">
         <v>12</v>
@@ -8855,16 +8855,16 @@
         <v>6.8</v>
       </c>
       <c r="BB43" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC43" t="n">
         <v>6.6</v>
       </c>
       <c r="BD43" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE43" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF43" t="n">
         <v>14.5</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -8905,22 +8905,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G44" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H44" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I44" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K44" t="n">
         <v>3.75</v>
-      </c>
-      <c r="K44" t="n">
-        <v>3.8</v>
       </c>
       <c r="L44" t="n">
         <v>1.37</v>
@@ -8953,10 +8953,10 @@
         <v>2.36</v>
       </c>
       <c r="V44" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W44" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="X44" t="n">
         <v>16</v>
@@ -8974,10 +8974,10 @@
         <v>11.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD44" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE44" t="n">
         <v>42</v>
@@ -8998,7 +8998,7 @@
         <v>25</v>
       </c>
       <c r="AK44" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL44" t="n">
         <v>32</v>
@@ -9010,10 +9010,10 @@
         <v>12.5</v>
       </c>
       <c r="AO44" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP44" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ44" t="n">
         <v>15.5</v>
@@ -9022,7 +9022,7 @@
         <v>26</v>
       </c>
       <c r="AS44" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AT44" t="n">
         <v>10.5</v>
@@ -9052,7 +9052,7 @@
         <v>23</v>
       </c>
       <c r="BC44" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD44" t="n">
         <v>29</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -9099,10 +9099,10 @@
         </is>
       </c>
       <c r="F45" t="n">
+        <v>23</v>
+      </c>
+      <c r="G45" t="n">
         <v>24</v>
-      </c>
-      <c r="G45" t="n">
-        <v>25</v>
       </c>
       <c r="H45" t="n">
         <v>1.16</v>
@@ -9123,31 +9123,31 @@
         <v>1.02</v>
       </c>
       <c r="N45" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="O45" t="n">
         <v>1.12</v>
       </c>
       <c r="P45" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R45" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S45" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="T45" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U45" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V45" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="W45" t="n">
         <v>1.04</v>
@@ -9162,10 +9162,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AA45" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AB45" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AC45" t="n">
         <v>24</v>
@@ -9177,10 +9177,10 @@
         <v>13</v>
       </c>
       <c r="AF45" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AG45" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AH45" t="n">
         <v>46</v>
@@ -9192,19 +9192,19 @@
         <v>1000</v>
       </c>
       <c r="AK45" t="n">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="AL45" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AM45" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN45" t="n">
         <v>1000</v>
       </c>
       <c r="AO45" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="AP45" t="n">
         <v>42</v>
@@ -9216,7 +9216,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS45" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT45" t="n">
         <v>60</v>
@@ -9228,7 +9228,7 @@
         <v>12.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX45" t="n">
         <v>110</v>
@@ -9240,7 +9240,7 @@
         <v>38</v>
       </c>
       <c r="BA45" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB45" t="n">
         <v>150</v>
@@ -9249,20 +9249,20 @@
         <v>110</v>
       </c>
       <c r="BD45" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BE45" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BF45" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="BG45" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -9326,13 +9326,13 @@
         <v>1.67</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="R46" t="n">
         <v>1.67</v>
       </c>
       <c r="S46" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="T46" t="n">
         <v>1.01</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
         <v>12</v>
       </c>
       <c r="I47" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J47" t="n">
         <v>7.8</v>
@@ -9520,7 +9520,7 @@
         <v>3.9</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="R47" t="n">
         <v>2.16</v>
@@ -9529,10 +9529,10 @@
         <v>1.83</v>
       </c>
       <c r="T47" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U47" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V47" t="n">
         <v>1.08</v>
@@ -9562,7 +9562,7 @@
         <v>44</v>
       </c>
       <c r="AE47" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF47" t="n">
         <v>11.5</v>
@@ -9571,16 +9571,16 @@
         <v>12</v>
       </c>
       <c r="AH47" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI47" t="n">
         <v>95</v>
       </c>
       <c r="AJ47" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AK47" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AL47" t="n">
         <v>25</v>
@@ -9595,7 +9595,7 @@
         <v>100</v>
       </c>
       <c r="AP47" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AQ47" t="n">
         <v>50</v>
@@ -9646,11 +9646,11 @@
         <v>2.88</v>
       </c>
       <c r="BG47" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -9714,13 +9714,13 @@
         <v>1.7</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R48" t="n">
         <v>1.26</v>
       </c>
       <c r="S48" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="T48" t="n">
         <v>1.94</v>
@@ -9765,7 +9765,7 @@
         <v>13.5</v>
       </c>
       <c r="AH48" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI48" t="n">
         <v>1000</v>
@@ -9789,16 +9789,16 @@
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AQ48" t="n">
-        <v>3.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR48" t="n">
-        <v>3.85</v>
+        <v>21</v>
       </c>
       <c r="AS48" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT48" t="n">
         <v>7</v>
@@ -9807,16 +9807,16 @@
         <v>6.8</v>
       </c>
       <c r="AV48" t="n">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
       <c r="AW48" t="n">
         <v>4.1</v>
       </c>
       <c r="AX48" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY48" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AZ48" t="n">
         <v>3.7</v>
@@ -9825,10 +9825,10 @@
         <v>4.1</v>
       </c>
       <c r="BB48" t="n">
-        <v>3.85</v>
+        <v>19.5</v>
       </c>
       <c r="BC48" t="n">
-        <v>3.8</v>
+        <v>18.5</v>
       </c>
       <c r="BD48" t="n">
         <v>4</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="O49" t="n">
         <v>1.24</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         <v>4.4</v>
       </c>
       <c r="L50" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M50" t="n">
         <v>1.08</v>
@@ -10159,7 +10159,7 @@
         <v>1000</v>
       </c>
       <c r="AJ50" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK50" t="n">
         <v>21</v>
@@ -10183,7 +10183,7 @@
         <v>16</v>
       </c>
       <c r="AR50" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS50" t="n">
         <v>8.6</v>
@@ -10198,7 +10198,7 @@
         <v>21</v>
       </c>
       <c r="AW50" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX50" t="n">
         <v>7.8</v>
@@ -10210,7 +10210,7 @@
         <v>20</v>
       </c>
       <c r="BA50" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB50" t="n">
         <v>13.5</v>
@@ -10222,17 +10222,17 @@
         <v>7.4</v>
       </c>
       <c r="BE50" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF50" t="n">
         <v>10</v>
       </c>
       <c r="BG50" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -10287,16 +10287,16 @@
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O51" t="n">
         <v>1.25</v>
       </c>
       <c r="P51" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="R51" t="n">
         <v>1.35</v>
@@ -10305,13 +10305,13 @@
         <v>2.66</v>
       </c>
       <c r="T51" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U51" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="V51" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W51" t="n">
         <v>3.75</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G52" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H52" t="n">
         <v>4.4</v>
@@ -10502,13 +10502,13 @@
         <v>1.6</v>
       </c>
       <c r="U52" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V52" t="n">
         <v>1.27</v>
       </c>
       <c r="W52" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X52" t="n">
         <v>25</v>
@@ -10559,22 +10559,22 @@
         <v>70</v>
       </c>
       <c r="AN52" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO52" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP52" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ52" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AR52" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS52" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT52" t="n">
         <v>11</v>
@@ -10586,19 +10586,19 @@
         <v>16</v>
       </c>
       <c r="AW52" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="AX52" t="n">
         <v>12</v>
       </c>
       <c r="AY52" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ52" t="n">
         <v>14.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BB52" t="n">
         <v>18</v>
@@ -10610,17 +10610,17 @@
         <v>23</v>
       </c>
       <c r="BE52" t="n">
-        <v>55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF52" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG52" t="n">
         <v>30</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -10663,7 +10663,7 @@
         <v>5.1</v>
       </c>
       <c r="J53" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K53" t="n">
         <v>4.3</v>
@@ -10687,16 +10687,16 @@
         <v>1.79</v>
       </c>
       <c r="R53" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
       </c>
       <c r="T53" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U53" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V53" t="n">
         <v>1.25</v>
@@ -10705,19 +10705,19 @@
         <v>2.18</v>
       </c>
       <c r="X53" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y53" t="n">
         <v>22</v>
       </c>
       <c r="Z53" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA53" t="n">
         <v>1000</v>
       </c>
       <c r="AB53" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC53" t="n">
         <v>10.5</v>
@@ -10741,7 +10741,7 @@
         <v>1000</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK53" t="n">
         <v>21</v>
@@ -10759,28 +10759,28 @@
         <v>1000</v>
       </c>
       <c r="AP53" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AQ53" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR53" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AS53" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="AT53" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AU53" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV53" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW53" t="n">
         <v>5.3</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>6.4</v>
       </c>
       <c r="AX53" t="n">
         <v>9.199999999999999</v>
@@ -10789,32 +10789,32 @@
         <v>9</v>
       </c>
       <c r="AZ53" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA53" t="n">
         <v>5.3</v>
       </c>
-      <c r="BA53" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BB53" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC53" t="n">
         <v>15.5</v>
       </c>
       <c r="BD53" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="BE53" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BF53" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BG53" t="n">
-        <v>42</v>
+        <v>5.3</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G54" t="n">
         <v>2.64</v>
@@ -10878,40 +10878,40 @@
         <v>2.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R54" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S54" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T54" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="U54" t="n">
         <v>2.56</v>
       </c>
       <c r="V54" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W54" t="n">
         <v>1.61</v>
       </c>
       <c r="X54" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z54" t="n">
         <v>26</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>25</v>
       </c>
       <c r="AA54" t="n">
         <v>46</v>
       </c>
       <c r="AB54" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC54" t="n">
         <v>11</v>
@@ -10929,16 +10929,16 @@
         <v>14.5</v>
       </c>
       <c r="AH54" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI54" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ54" t="n">
         <v>42</v>
       </c>
       <c r="AK54" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL54" t="n">
         <v>36</v>
@@ -10950,28 +10950,28 @@
         <v>17</v>
       </c>
       <c r="AO54" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AP54" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ54" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT54" t="n">
         <v>12</v>
       </c>
-      <c r="AR54" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AU54" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV54" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW54" t="n">
         <v>20</v>
@@ -10983,32 +10983,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ54" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF54" t="n">
         <v>11.5</v>
       </c>
-      <c r="BA54" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC54" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD54" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE54" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF54" t="n">
-        <v>12</v>
-      </c>
       <c r="BG54" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -11042,167 +11042,167 @@
         <v>1.88</v>
       </c>
       <c r="G55" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="H55" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I55" t="n">
         <v>4.5</v>
       </c>
       <c r="J55" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K55" t="n">
         <v>4.2</v>
       </c>
       <c r="L55" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M55" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N55" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O55" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P55" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="R55" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="S55" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="T55" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="U55" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="V55" t="n">
         <v>1.28</v>
       </c>
       <c r="W55" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X55" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Y55" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z55" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA55" t="n">
         <v>1000</v>
       </c>
       <c r="AB55" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC55" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD55" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AE55" t="n">
         <v>1000</v>
       </c>
       <c r="AF55" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AG55" t="n">
         <v>12</v>
       </c>
       <c r="AH55" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI55" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ55" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK55" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AL55" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM55" t="n">
         <v>1000</v>
       </c>
       <c r="AN55" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AO55" t="n">
         <v>1000</v>
       </c>
       <c r="AP55" t="n">
-        <v>4.4</v>
+        <v>16.5</v>
       </c>
       <c r="AQ55" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AR55" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AS55" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AT55" t="n">
         <v>9.4</v>
       </c>
       <c r="AU55" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV55" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW55" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AX55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY55" t="n">
         <v>9</v>
       </c>
       <c r="AZ55" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BA55" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BB55" t="n">
-        <v>17.5</v>
+        <v>4.2</v>
       </c>
       <c r="BC55" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BD55" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE55" t="n">
         <v>4.8</v>
       </c>
-      <c r="BE55" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BF55" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG55" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -11287,49 +11287,49 @@
         <v>1.61</v>
       </c>
       <c r="X56" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="Z56" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AA56" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AB56" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AC56" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD56" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AE56" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK56" t="n">
         <v>34</v>
       </c>
-      <c r="AF56" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>28</v>
-      </c>
       <c r="AL56" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AM56" t="n">
         <v>1000</v>
@@ -11338,65 +11338,65 @@
         <v>26</v>
       </c>
       <c r="AO56" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AP56" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ56" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AR56" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AS56" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="AT56" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV56" t="n">
         <v>10</v>
       </c>
-      <c r="AU56" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AW56" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="AX56" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AY56" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ56" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BA56" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="BB56" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="BC56" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BD56" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="BE56" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="BF56" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG56" t="n">
         <v>20</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G57" t="n">
         <v>2.1</v>
@@ -11436,7 +11436,7 @@
         <v>3.8</v>
       </c>
       <c r="I57" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J57" t="n">
         <v>3.8</v>
@@ -11481,16 +11481,16 @@
         <v>1.92</v>
       </c>
       <c r="X57" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y57" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z57" t="n">
         <v>34</v>
       </c>
       <c r="AA57" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB57" t="n">
         <v>12</v>
@@ -11499,7 +11499,7 @@
         <v>10</v>
       </c>
       <c r="AD57" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE57" t="n">
         <v>50</v>
@@ -11532,34 +11532,34 @@
         <v>14</v>
       </c>
       <c r="AO57" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP57" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ57" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR57" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AS57" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AT57" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV57" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AW57" t="n">
-        <v>5.4</v>
+        <v>34</v>
       </c>
       <c r="AX57" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY57" t="n">
         <v>9.4</v>
@@ -11568,7 +11568,7 @@
         <v>13.5</v>
       </c>
       <c r="BA57" t="n">
-        <v>36</v>
+        <v>5.2</v>
       </c>
       <c r="BB57" t="n">
         <v>21</v>
@@ -11577,20 +11577,20 @@
         <v>15.5</v>
       </c>
       <c r="BD57" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE57" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BF57" t="n">
         <v>11</v>
       </c>
       <c r="BG57" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -11624,16 +11624,16 @@
         <v>1.04</v>
       </c>
       <c r="G58" t="n">
-        <v>310</v>
+        <v>2.46</v>
       </c>
       <c r="H58" t="n">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="I58" t="n">
         <v>1000</v>
       </c>
       <c r="J58" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K58" t="n">
         <v>950</v>
@@ -11645,7 +11645,7 @@
         <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="O58" t="n">
         <v>1.1</v>
@@ -11672,7 +11672,7 @@
         <v>1.01</v>
       </c>
       <c r="W58" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="X58" t="n">
         <v>1000</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -11839,7 +11839,7 @@
         <v>1.14</v>
       </c>
       <c r="N59" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="O59" t="n">
         <v>1.61</v>
@@ -11857,10 +11857,10 @@
         <v>6.2</v>
       </c>
       <c r="T59" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U59" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V59" t="n">
         <v>1.31</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -12063,19 +12063,19 @@
         <v>1.83</v>
       </c>
       <c r="X60" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y60" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z60" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA60" t="n">
         <v>1000</v>
       </c>
       <c r="AB60" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC60" t="n">
         <v>11</v>
@@ -12087,10 +12087,10 @@
         <v>1000</v>
       </c>
       <c r="AF60" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG60" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH60" t="n">
         <v>19</v>
@@ -12099,10 +12099,10 @@
         <v>48</v>
       </c>
       <c r="AJ60" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK60" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL60" t="n">
         <v>1000</v>
@@ -12111,7 +12111,7 @@
         <v>85</v>
       </c>
       <c r="AN60" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO60" t="n">
         <v>34</v>
@@ -12123,10 +12123,10 @@
         <v>13.5</v>
       </c>
       <c r="AR60" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS60" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AT60" t="n">
         <v>10</v>
@@ -12138,10 +12138,10 @@
         <v>11</v>
       </c>
       <c r="AW60" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AX60" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY60" t="n">
         <v>9.4</v>
@@ -12150,29 +12150,29 @@
         <v>12.5</v>
       </c>
       <c r="BA60" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BB60" t="n">
-        <v>21</v>
+        <v>4.3</v>
       </c>
       <c r="BC60" t="n">
         <v>18</v>
       </c>
       <c r="BD60" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BE60" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BF60" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG60" t="n">
         <v>21</v>
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -12206,13 +12206,13 @@
         <v>1.98</v>
       </c>
       <c r="G61" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H61" t="n">
         <v>3.65</v>
       </c>
       <c r="I61" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J61" t="n">
         <v>3.95</v>
@@ -12239,7 +12239,7 @@
         <v>1.63</v>
       </c>
       <c r="R61" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S61" t="n">
         <v>2.6</v>
@@ -12254,7 +12254,7 @@
         <v>1.35</v>
       </c>
       <c r="W61" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X61" t="n">
         <v>28</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -12397,13 +12397,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G62" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="H62" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I62" t="n">
         <v>5.9</v>
@@ -12424,7 +12424,7 @@
         <v>3.7</v>
       </c>
       <c r="O62" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P62" t="n">
         <v>1.93</v>
@@ -12436,19 +12436,19 @@
         <v>1.36</v>
       </c>
       <c r="S62" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T62" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U62" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V62" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W62" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="X62" t="n">
         <v>18.5</v>
@@ -12463,13 +12463,13 @@
         <v>1000</v>
       </c>
       <c r="AB62" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC62" t="n">
         <v>10.5</v>
       </c>
       <c r="AD62" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE62" t="n">
         <v>1000</v>
@@ -12511,25 +12511,25 @@
         <v>12.5</v>
       </c>
       <c r="AR62" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AS62" t="n">
         <v>4.2</v>
       </c>
       <c r="AT62" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU62" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV62" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW62" t="n">
         <v>4.1</v>
       </c>
       <c r="AX62" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY62" t="n">
         <v>7.6</v>
@@ -12541,7 +12541,7 @@
         <v>4.1</v>
       </c>
       <c r="BB62" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC62" t="n">
         <v>14</v>
@@ -12550,17 +12550,17 @@
         <v>3.95</v>
       </c>
       <c r="BE62" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF62" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG62" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -12594,10 +12594,10 @@
         <v>7</v>
       </c>
       <c r="G63" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="I63" t="n">
         <v>1.48</v>
@@ -12624,16 +12624,16 @@
         <v>2.84</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R63" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S63" t="n">
         <v>2.14</v>
       </c>
       <c r="T63" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U63" t="n">
         <v>2.22</v>
@@ -12642,7 +12642,7 @@
         <v>3.05</v>
       </c>
       <c r="W63" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X63" t="n">
         <v>34</v>
@@ -12723,7 +12723,7 @@
         <v>12</v>
       </c>
       <c r="AX63" t="n">
-        <v>55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY63" t="n">
         <v>7</v>
@@ -12741,20 +12741,20 @@
         <v>8.4</v>
       </c>
       <c r="BD63" t="n">
-        <v>55</v>
+        <v>8.4</v>
       </c>
       <c r="BE63" t="n">
         <v>8.4</v>
       </c>
       <c r="BF63" t="n">
-        <v>55</v>
+        <v>8.4</v>
       </c>
       <c r="BG63" t="n">
         <v>4.1</v>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
         <v>1.87</v>
       </c>
       <c r="I64" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="J64" t="n">
         <v>3.55</v>
@@ -12803,7 +12803,7 @@
         <v>3.85</v>
       </c>
       <c r="L64" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M64" t="n">
         <v>1.08</v>
@@ -12812,7 +12812,7 @@
         <v>3.45</v>
       </c>
       <c r="O64" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P64" t="n">
         <v>1.85</v>
@@ -12824,10 +12824,10 @@
         <v>1.32</v>
       </c>
       <c r="S64" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="T64" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U64" t="n">
         <v>1.98</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -13021,7 +13021,7 @@
         <v>2.32</v>
       </c>
       <c r="T65" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U65" t="n">
         <v>2.44</v>
@@ -13033,7 +13033,7 @@
         <v>2.24</v>
       </c>
       <c r="X65" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Y65" t="n">
         <v>25</v>
@@ -13048,101 +13048,101 @@
         <v>13</v>
       </c>
       <c r="AC65" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD65" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AE65" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AF65" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG65" t="n">
         <v>10.5</v>
       </c>
       <c r="AH65" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AI65" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AJ65" t="n">
         <v>19.5</v>
       </c>
       <c r="AK65" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AL65" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AM65" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AN65" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO65" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AP65" t="n">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="AQ65" t="n">
         <v>21</v>
       </c>
       <c r="AR65" t="n">
-        <v>9.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="AS65" t="n">
-        <v>11.5</v>
+        <v>5.2</v>
       </c>
       <c r="AT65" t="n">
         <v>11.5</v>
       </c>
       <c r="AU65" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV65" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AW65" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX65" t="n">
         <v>10</v>
-      </c>
-      <c r="AX65" t="n">
-        <v>12</v>
       </c>
       <c r="AY65" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ65" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BA65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BB65" t="n">
         <v>16.5</v>
       </c>
       <c r="BC65" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD65" t="n">
-        <v>8.6</v>
+        <v>18.5</v>
       </c>
       <c r="BE65" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="BF65" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG65" t="n">
-        <v>9.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -13179,22 +13179,22 @@
         <v>3.45</v>
       </c>
       <c r="H66" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I66" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="J66" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K66" t="n">
         <v>3.3</v>
       </c>
       <c r="L66" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="M66" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N66" t="n">
         <v>2.78</v>
@@ -13203,10 +13203,10 @@
         <v>1.47</v>
       </c>
       <c r="P66" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R66" t="n">
         <v>1.22</v>
@@ -13293,7 +13293,7 @@
         <v>7.4</v>
       </c>
       <c r="AT66" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU66" t="n">
         <v>6.2</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -13367,16 +13367,16 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="G67" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H67" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I67" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="J67" t="n">
         <v>4.2</v>
@@ -13391,7 +13391,7 @@
         <v>1.02</v>
       </c>
       <c r="N67" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O67" t="n">
         <v>1.16</v>
@@ -13412,13 +13412,13 @@
         <v>1.47</v>
       </c>
       <c r="U67" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="V67" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W67" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="X67" t="n">
         <v>30</v>
@@ -13430,7 +13430,7 @@
         <v>27</v>
       </c>
       <c r="AA67" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB67" t="n">
         <v>18</v>
@@ -13442,7 +13442,7 @@
         <v>14</v>
       </c>
       <c r="AE67" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AF67" t="n">
         <v>21</v>
@@ -13457,7 +13457,7 @@
         <v>30</v>
       </c>
       <c r="AJ67" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK67" t="n">
         <v>21</v>
@@ -13469,16 +13469,16 @@
         <v>48</v>
       </c>
       <c r="AN67" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO67" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP67" t="n">
         <v>27</v>
       </c>
       <c r="AQ67" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR67" t="n">
         <v>22</v>
@@ -13493,28 +13493,28 @@
         <v>9.4</v>
       </c>
       <c r="AV67" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW67" t="n">
         <v>23</v>
       </c>
       <c r="AX67" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY67" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ67" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA67" t="n">
         <v>26</v>
       </c>
       <c r="BB67" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BC67" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD67" t="n">
         <v>22</v>
@@ -13523,14 +13523,14 @@
         <v>25</v>
       </c>
       <c r="BF67" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BG67" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -13564,7 +13564,7 @@
         <v>1.44</v>
       </c>
       <c r="G68" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H68" t="n">
         <v>7</v>
@@ -13591,13 +13591,13 @@
         <v>1.15</v>
       </c>
       <c r="P68" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="Q68" t="n">
         <v>1.48</v>
       </c>
       <c r="R68" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="S68" t="n">
         <v>2.18</v>
@@ -13612,13 +13612,13 @@
         <v>1.14</v>
       </c>
       <c r="W68" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X68" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y68" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z68" t="n">
         <v>1000</v>
@@ -13627,13 +13627,13 @@
         <v>1000</v>
       </c>
       <c r="AB68" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AC68" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AD68" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE68" t="n">
         <v>1000</v>
@@ -13642,43 +13642,43 @@
         <v>12.5</v>
       </c>
       <c r="AG68" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH68" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI68" t="n">
         <v>1000</v>
       </c>
       <c r="AJ68" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AK68" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AL68" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM68" t="n">
         <v>1000</v>
       </c>
       <c r="AN68" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AO68" t="n">
         <v>1000</v>
       </c>
       <c r="AP68" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="AQ68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AR68" t="n">
-        <v>50</v>
+        <v>5.3</v>
       </c>
       <c r="AS68" t="n">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="AT68" t="n">
         <v>11</v>
@@ -13690,7 +13690,7 @@
         <v>21</v>
       </c>
       <c r="AW68" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="AX68" t="n">
         <v>9</v>
@@ -13699,10 +13699,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ68" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA68" t="n">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="BB68" t="n">
         <v>11.5</v>
@@ -13714,17 +13714,17 @@
         <v>20</v>
       </c>
       <c r="BE68" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="BF68" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG68" t="n">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
         <v>1.61</v>
       </c>
       <c r="G69" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H69" t="n">
         <v>5.4</v>
@@ -13773,10 +13773,10 @@
         <v>4.9</v>
       </c>
       <c r="L69" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M69" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N69" t="n">
         <v>5.5</v>
@@ -13788,7 +13788,7 @@
         <v>2.5</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R69" t="n">
         <v>1.59</v>
@@ -13797,7 +13797,7 @@
         <v>2.58</v>
       </c>
       <c r="T69" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U69" t="n">
         <v>2.26</v>
@@ -13806,7 +13806,7 @@
         <v>1.2</v>
       </c>
       <c r="W69" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="X69" t="n">
         <v>27</v>
@@ -13842,7 +13842,7 @@
         <v>20</v>
       </c>
       <c r="AI69" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ69" t="n">
         <v>17</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="G2" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="H2" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="I2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.31</v>
@@ -781,16 +781,16 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R2" t="n">
         <v>1.6</v>
@@ -799,28 +799,28 @@
         <v>2.58</v>
       </c>
       <c r="T2" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="X2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA2" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB2" t="n">
         <v>11.5</v>
@@ -829,10 +829,10 @@
         <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
         <v>11.5</v>
@@ -847,7 +847,7 @@
         <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AK2" t="n">
         <v>15</v>
@@ -856,71 +856,71 @@
         <v>27</v>
       </c>
       <c r="AM2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AR2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AS2" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
         <v>32</v>
       </c>
       <c r="AX2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BB2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE2" t="n">
         <v>75</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="G3" t="n">
         <v>3.7</v>
       </c>
-      <c r="G3" t="n">
-        <v>3.75</v>
-      </c>
       <c r="H3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I3" t="n">
         <v>2.3</v>
@@ -999,10 +999,10 @@
         <v>2.06</v>
       </c>
       <c r="V3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="W3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X3" t="n">
         <v>12.5</v>
@@ -1107,14 +1107,14 @@
         <v>90</v>
       </c>
       <c r="BF3" t="n">
-        <v>16.5</v>
+        <v>40</v>
       </c>
       <c r="BG3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H4" t="n">
         <v>3.25</v>
       </c>
       <c r="I4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J4" t="n">
         <v>3.45</v>
@@ -1163,7 +1163,7 @@
         <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1175,10 +1175,10 @@
         <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R4" t="n">
         <v>1.38</v>
@@ -1196,13 +1196,13 @@
         <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>26</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
         <v>24</v>
@@ -1214,7 +1214,7 @@
         <v>11</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
         <v>14.5</v>
@@ -1229,7 +1229,7 @@
         <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AI4" t="n">
         <v>100</v>
@@ -1247,7 +1247,7 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1256,13 +1256,13 @@
         <v>13</v>
       </c>
       <c r="AQ4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS4" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>11</v>
       </c>
       <c r="AT4" t="n">
         <v>9.6</v>
@@ -1274,7 +1274,7 @@
         <v>12.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX4" t="n">
         <v>13.5</v>
@@ -1286,29 +1286,29 @@
         <v>14.5</v>
       </c>
       <c r="BA4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD4" t="n">
         <v>10.5</v>
       </c>
-      <c r="BB4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>10</v>
-      </c>
       <c r="BE4" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF4" t="n">
         <v>16</v>
       </c>
       <c r="BG4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="G5" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="J5" t="n">
         <v>3.35</v>
@@ -1357,7 +1357,7 @@
         <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
@@ -1387,43 +1387,43 @@
         <v>2.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W5" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X5" t="n">
         <v>15</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="AA5" t="n">
         <v>95</v>
       </c>
       <c r="AB5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC5" t="n">
         <v>7.6</v>
       </c>
       <c r="AD5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG5" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AH5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI5" t="n">
         <v>150</v>
@@ -1438,13 +1438,13 @@
         <v>95</v>
       </c>
       <c r="AM5" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AN5" t="n">
         <v>44</v>
       </c>
       <c r="AO5" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AP5" t="n">
         <v>13</v>
@@ -1453,25 +1453,25 @@
         <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU5" t="n">
         <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY5" t="n">
         <v>11.5</v>
@@ -1483,26 +1483,26 @@
         <v>32</v>
       </c>
       <c r="BB5" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BC5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD5" t="n">
         <v>34</v>
       </c>
       <c r="BE5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>1.39</v>
       </c>
       <c r="H6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>9.800000000000001</v>
@@ -1557,25 +1557,25 @@
         <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O6" t="n">
         <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="Q6" t="n">
         <v>1.51</v>
       </c>
       <c r="R6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S6" t="n">
         <v>2.28</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U6" t="n">
         <v>2.16</v>
@@ -1587,7 +1587,7 @@
         <v>3.55</v>
       </c>
       <c r="X6" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="Y6" t="n">
         <v>40</v>
@@ -1641,13 +1641,13 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AQ6" t="n">
         <v>32</v>
       </c>
       <c r="AR6" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AS6" t="n">
         <v>95</v>
@@ -1659,22 +1659,22 @@
         <v>12</v>
       </c>
       <c r="AV6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AW6" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AX6" t="n">
         <v>9</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6" t="n">
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BB6" t="n">
         <v>10.5</v>
@@ -1686,17 +1686,17 @@
         <v>22</v>
       </c>
       <c r="BE6" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="G7" t="n">
         <v>2.86</v>
@@ -1736,7 +1736,7 @@
         <v>3.15</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="J7" t="n">
         <v>2.96</v>
@@ -1745,19 +1745,19 @@
         <v>3.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M7" t="n">
         <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O7" t="n">
         <v>1.55</v>
       </c>
       <c r="P7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q7" t="n">
         <v>2.66</v>
@@ -1772,10 +1772,10 @@
         <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
         <v>1.53</v>
@@ -1799,7 +1799,7 @@
         <v>7.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
         <v>55</v>
@@ -1868,7 +1868,7 @@
         <v>19.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB7" t="n">
         <v>18</v>
@@ -1877,7 +1877,7 @@
         <v>18</v>
       </c>
       <c r="BD7" t="n">
-        <v>29</v>
+        <v>8.6</v>
       </c>
       <c r="BE7" t="n">
         <v>9</v>
@@ -1886,11 +1886,11 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG7" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.83</v>
+        <v>2.34</v>
       </c>
       <c r="G8" t="n">
-        <v>8.800000000000001</v>
+        <v>2.74</v>
       </c>
       <c r="H8" t="n">
-        <v>2.18</v>
+        <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="J8" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>3.35</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>1.02</v>
+        <v>2.36</v>
       </c>
       <c r="O8" t="n">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="P8" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="R8" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.48</v>
+        <v>4.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.57</v>
+        <v>6</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.61</v>
+        <v>7.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.48</v>
+        <v>4</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.48</v>
+        <v>3.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.55</v>
+        <v>5.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.61</v>
+        <v>7.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.55</v>
+        <v>5.3</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.54</v>
+        <v>5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.59</v>
+        <v>6</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.61</v>
+        <v>7.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.61</v>
+        <v>7.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.62</v>
+        <v>7.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.59</v>
+        <v>6.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.61</v>
+        <v>7.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="G9" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H9" t="n">
         <v>3.6</v>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.02</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
         <v>1.22</v>
       </c>
       <c r="P9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T9" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2175,110 +2175,110 @@
         <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AC9" t="n">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AF9" t="n">
         <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.7</v>
+        <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.74</v>
+        <v>9</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.74</v>
+        <v>7</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.77</v>
+        <v>5.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.63</v>
+        <v>7</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.57</v>
+        <v>7.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.66</v>
+        <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.74</v>
+        <v>7.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.67</v>
+        <v>7.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.62</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.76</v>
+        <v>7.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.74</v>
+        <v>6.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.71</v>
+        <v>10.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.73</v>
+        <v>7.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.76</v>
+        <v>3.35</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.68</v>
+        <v>10</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.78</v>
+        <v>7.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.02</v>
+        <v>2.08</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>110</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="K11" t="n">
         <v>8.4</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
         <v>5.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U12" t="n">
         <v>1.68</v>
@@ -2763,16 +2763,16 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AC12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE12" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
         <v>12</v>
@@ -2805,19 +2805,19 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ12" t="n">
         <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU12" t="n">
         <v>6.6</v>
@@ -2826,10 +2826,10 @@
         <v>19</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY12" t="n">
         <v>9.4</v>
@@ -2838,7 +2838,7 @@
         <v>13</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB12" t="n">
         <v>20</v>
@@ -2847,20 +2847,20 @@
         <v>13</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BF12" t="n">
         <v>20</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>2.74</v>
       </c>
       <c r="G13" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="H13" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I13" t="n">
         <v>3.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
         <v>3.35</v>
@@ -2942,13 +2942,13 @@
         <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X13" t="n">
         <v>11</v>
       </c>
       <c r="Y13" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z13" t="n">
         <v>20</v>
@@ -2993,7 +2993,7 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO13" t="n">
         <v>48</v>
@@ -3008,10 +3008,10 @@
         <v>16.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT13" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU13" t="n">
         <v>6.6</v>
@@ -3020,7 +3020,7 @@
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX13" t="n">
         <v>14</v>
@@ -3032,29 +3032,29 @@
         <v>18.5</v>
       </c>
       <c r="BA13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB13" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BC13" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC13" t="n">
-        <v>8</v>
-      </c>
       <c r="BD13" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF13" t="n">
         <v>30</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
         <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3175,7 +3175,7 @@
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
         <v>1000</v>
@@ -3184,7 +3184,7 @@
         <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
         <v>1000</v>
@@ -3193,10 +3193,10 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AR14" t="n">
         <v>1.92</v>
@@ -3205,7 +3205,7 @@
         <v>1.96</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AU14" t="n">
         <v>5.1</v>
@@ -3214,10 +3214,10 @@
         <v>1.82</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AY14" t="n">
         <v>1.76</v>
@@ -3226,13 +3226,13 @@
         <v>1.82</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BB14" t="n">
         <v>1.93</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BD14" t="n">
         <v>1.91</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
         <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AD15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
         <v>1.63</v>
       </c>
       <c r="U16" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
         <v>1.32</v>
@@ -3527,7 +3527,7 @@
         <v>1.9</v>
       </c>
       <c r="X16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y16" t="n">
         <v>19.5</v>
@@ -3551,7 +3551,7 @@
         <v>110</v>
       </c>
       <c r="AF16" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG16" t="n">
         <v>11.5</v>
@@ -3563,10 +3563,10 @@
         <v>160</v>
       </c>
       <c r="AJ16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
         <v>34</v>
@@ -3581,16 +3581,16 @@
         <v>240</v>
       </c>
       <c r="AP16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AR16" t="n">
         <v>6.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT16" t="n">
         <v>5.8</v>
@@ -3614,29 +3614,29 @@
         <v>5.8</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC16" t="n">
         <v>6.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>18</v>
+        <v>6.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG16" t="n">
         <v>12</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>1.6</v>
       </c>
       <c r="G17" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="H17" t="n">
         <v>3.9</v>
@@ -3745,7 +3745,7 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG17" t="n">
         <v>20</v>
@@ -3757,10 +3757,10 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL17" t="n">
         <v>1000</v>
@@ -3793,7 +3793,7 @@
         <v>5.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW17" t="n">
         <v>4.4</v>
@@ -3805,7 +3805,7 @@
         <v>6.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA17" t="n">
         <v>4.4</v>
@@ -3814,23 +3814,23 @@
         <v>8.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE17" t="n">
         <v>4.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BG17" t="n">
         <v>4.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
         <v>3.05</v>
       </c>
       <c r="I18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J18" t="n">
         <v>3.45</v>
@@ -3891,7 +3891,7 @@
         <v>1.27</v>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q18" t="n">
         <v>1.78</v>
@@ -3915,16 +3915,16 @@
         <v>1.69</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
         <v>18</v>
@@ -3933,7 +3933,7 @@
         <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
@@ -3954,7 +3954,7 @@
         <v>900</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -3969,7 +3969,7 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="AQ18" t="n">
         <v>11</v>
@@ -3987,13 +3987,13 @@
         <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AW18" t="n">
         <v>6.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY18" t="n">
         <v>8.800000000000001</v>
@@ -4011,7 +4011,7 @@
         <v>6.2</v>
       </c>
       <c r="BD18" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BE18" t="n">
         <v>7.4</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>2.24</v>
       </c>
       <c r="G19" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H19" t="n">
         <v>3.2</v>
@@ -4079,7 +4079,7 @@
         <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="O19" t="n">
         <v>1.37</v>
@@ -4088,7 +4088,7 @@
         <v>1.62</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R19" t="n">
         <v>1.07</v>
@@ -4163,10 +4163,10 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.28</v>
+        <v>5.8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.93</v>
+        <v>1.35</v>
       </c>
       <c r="AR19" t="n">
         <v>1.36</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -4273,22 +4273,22 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="O20" t="n">
         <v>1.05</v>
       </c>
       <c r="P20" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="R20" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>1.69</v>
+        <v>2.6</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -4369,7 +4369,7 @@
         <v>1.92</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU20" t="n">
         <v>5.6</v>
@@ -4381,10 +4381,10 @@
         <v>1.91</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.75</v>
+        <v>5.8</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.72</v>
+        <v>6.4</v>
       </c>
       <c r="AZ20" t="n">
         <v>1.84</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G21" t="n">
         <v>2.28</v>
@@ -4455,7 +4455,7 @@
         <v>4.7</v>
       </c>
       <c r="J21" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K21" t="n">
         <v>3.1</v>
@@ -4470,7 +4470,7 @@
         <v>2.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="P21" t="n">
         <v>1.48</v>
@@ -4500,7 +4500,7 @@
         <v>8</v>
       </c>
       <c r="Y21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
         <v>32</v>
@@ -4515,7 +4515,7 @@
         <v>7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
@@ -4557,10 +4557,10 @@
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT21" t="n">
         <v>6</v>
@@ -4572,7 +4572,7 @@
         <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX21" t="n">
         <v>9.6</v>
@@ -4584,29 +4584,29 @@
         <v>21</v>
       </c>
       <c r="BA21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE21" t="n">
         <v>11</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BF21" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BC21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BG21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="G22" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>2.28</v>
       </c>
       <c r="I22" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J22" t="n">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="K22" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="L22" t="n">
         <v>1.48</v>
@@ -4661,37 +4661,37 @@
         <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>2.18</v>
+        <v>1.5</v>
       </c>
       <c r="O22" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P22" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="R22" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="T22" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
         <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="X22" t="n">
-        <v>90</v>
+        <v>16.5</v>
       </c>
       <c r="Y22" t="n">
         <v>970</v>
@@ -4748,59 +4748,59 @@
         <v>6.8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AT22" t="n">
         <v>5.1</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AV22" t="n">
         <v>5.8</v>
       </c>
       <c r="AW22" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AX22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AY22" t="n">
         <v>4.8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="BA22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BD22" t="n">
         <v>3.5</v>
       </c>
-      <c r="BB22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BE22" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -4990,11 +4990,11 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="G24" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="H24" t="n">
         <v>1.89</v>
@@ -5049,22 +5049,22 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="O24" t="n">
         <v>1.04</v>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
         <v>1.04</v>
       </c>
       <c r="R24" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="S24" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -5076,7 +5076,7 @@
         <v>1.54</v>
       </c>
       <c r="W24" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5100,7 +5100,7 @@
         <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
         <v>1000</v>
@@ -5115,7 +5115,7 @@
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK24" t="n">
         <v>1000</v>
@@ -5130,65 +5130,65 @@
         <v>55</v>
       </c>
       <c r="AO24" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.8</v>
+        <v>2.26</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="AR24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU24" t="n">
         <v>5.2</v>
       </c>
-      <c r="AS24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AV24" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="AX24" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="AY24" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>5.6</v>
+        <v>3.65</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -5225,16 +5225,16 @@
         <v>1.49</v>
       </c>
       <c r="H25" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="I25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="K25" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5243,7 +5243,7 @@
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>5.1</v>
+        <v>1.02</v>
       </c>
       <c r="O25" t="n">
         <v>1.14</v>
@@ -5252,7 +5252,7 @@
         <v>2.52</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="R25" t="n">
         <v>1.59</v>
@@ -5309,7 +5309,7 @@
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>25</v>
+        <v>900</v>
       </c>
       <c r="AK25" t="n">
         <v>1000</v>
@@ -5321,13 +5321,13 @@
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="AQ25" t="n">
         <v>4.2</v>
@@ -5342,47 +5342,47 @@
         <v>4.9</v>
       </c>
       <c r="AU25" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="AV25" t="n">
         <v>22</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AX25" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AY25" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="BA25" t="n">
         <v>4.2</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BC25" t="n">
         <v>5.2</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.74</v>
+        <v>2.46</v>
       </c>
       <c r="BF25" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BG25" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G26" t="n">
         <v>2.62</v>
@@ -5464,7 +5464,7 @@
         <v>1.41</v>
       </c>
       <c r="W26" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X26" t="n">
         <v>16.5</v>
@@ -5506,19 +5506,19 @@
         <v>36</v>
       </c>
       <c r="AK26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL26" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM26" t="n">
         <v>200</v>
       </c>
       <c r="AN26" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AP26" t="n">
         <v>12.5</v>
@@ -5554,7 +5554,7 @@
         <v>11</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BB26" t="n">
         <v>14.5</v>
@@ -5566,17 +5566,17 @@
         <v>25</v>
       </c>
       <c r="BE26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF26" t="n">
         <v>13.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
         <v>1.3</v>
       </c>
       <c r="I28" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="J28" t="n">
         <v>5.9</v>
@@ -5819,7 +5819,7 @@
         <v>8.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
         <v>1.02</v>
@@ -5909,40 +5909,40 @@
         <v>4</v>
       </c>
       <c r="AP28" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS28" t="n">
         <v>6.4</v>
       </c>
       <c r="AT28" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AV28" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AW28" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX28" t="n">
         <v>4.2</v>
       </c>
       <c r="AY28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA28" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>6.2</v>
       </c>
       <c r="BB28" t="n">
         <v>4.2</v>
@@ -5951,20 +5951,20 @@
         <v>4.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF28" t="n">
         <v>10.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         <v>6.8</v>
       </c>
       <c r="H29" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I29" t="n">
         <v>1.81</v>
@@ -6055,7 +6055,7 @@
         <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
@@ -6067,7 +6067,7 @@
         <v>42</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE29" t="n">
         <v>1000</v>
@@ -6103,7 +6103,7 @@
         <v>29</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AQ29" t="n">
         <v>8.199999999999999</v>
@@ -6115,7 +6115,7 @@
         <v>12</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AU29" t="n">
         <v>7.6</v>
@@ -6127,38 +6127,38 @@
         <v>11.5</v>
       </c>
       <c r="AX29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY29" t="n">
         <v>5.6</v>
       </c>
-      <c r="AY29" t="n">
-        <v>5</v>
-      </c>
       <c r="AZ29" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BB29" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG29" t="n">
         <v>5.6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -6192,16 +6192,16 @@
         <v>2.04</v>
       </c>
       <c r="G30" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H30" t="n">
         <v>4.2</v>
       </c>
       <c r="I30" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="K30" t="n">
         <v>3.5</v>
@@ -6237,10 +6237,10 @@
         <v>1.6</v>
       </c>
       <c r="V30" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6300,49 +6300,49 @@
         <v>4.9</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AU30" t="n">
         <v>4.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="BF30" t="n">
         <v>5</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>1.44</v>
       </c>
       <c r="G31" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H31" t="n">
         <v>6.6</v>
@@ -6434,7 +6434,7 @@
         <v>1.14</v>
       </c>
       <c r="W31" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="X31" t="n">
         <v>90</v>
@@ -6464,7 +6464,7 @@
         <v>11</v>
       </c>
       <c r="AG31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH31" t="n">
         <v>1000</v>
@@ -6491,28 +6491,28 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ31" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AS31" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AU31" t="n">
         <v>10</v>
       </c>
       <c r="AV31" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW31" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
         <v>9</v>
@@ -6524,7 +6524,7 @@
         <v>13.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB31" t="n">
         <v>11.5</v>
@@ -6536,17 +6536,17 @@
         <v>20</v>
       </c>
       <c r="BE31" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF31" t="n">
         <v>5</v>
       </c>
       <c r="BG31" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -6580,10 +6580,10 @@
         <v>2.54</v>
       </c>
       <c r="G32" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H32" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I32" t="n">
         <v>2.96</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G33" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="H33" t="n">
         <v>10.5</v>
@@ -6783,10 +6783,10 @@
         <v>12</v>
       </c>
       <c r="J33" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="K33" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -6795,34 +6795,34 @@
         <v>1.04</v>
       </c>
       <c r="N33" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P33" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="R33" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S33" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="T33" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U33" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V33" t="n">
         <v>1.09</v>
       </c>
       <c r="W33" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X33" t="n">
         <v>38</v>
@@ -6837,10 +6837,10 @@
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD33" t="n">
         <v>1000</v>
@@ -6885,10 +6885,10 @@
         <v>14.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS33" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AT33" t="n">
         <v>8.199999999999999</v>
@@ -6900,7 +6900,7 @@
         <v>26</v>
       </c>
       <c r="AW33" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AX33" t="n">
         <v>7</v>
@@ -6909,32 +6909,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA33" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>7.8</v>
       </c>
       <c r="BB33" t="n">
         <v>9.4</v>
       </c>
       <c r="BC33" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD33" t="n">
         <v>28</v>
       </c>
       <c r="BE33" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BG33" t="n">
         <v>15</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -6965,40 +6965,40 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="G34" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="H34" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I34" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J34" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="K34" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="L34" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N34" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O34" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P34" t="n">
         <v>2.04</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R34" t="n">
         <v>1.38</v>
@@ -7013,10 +7013,10 @@
         <v>2.16</v>
       </c>
       <c r="V34" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W34" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="X34" t="n">
         <v>19</v>
@@ -7040,7 +7040,7 @@
         <v>21</v>
       </c>
       <c r="AE34" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AF34" t="n">
         <v>16</v>
@@ -7052,7 +7052,7 @@
         <v>22</v>
       </c>
       <c r="AI34" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
         <v>30</v>
@@ -7070,31 +7070,31 @@
         <v>18</v>
       </c>
       <c r="AO34" t="n">
-        <v>260</v>
+        <v>60</v>
       </c>
       <c r="AP34" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ34" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR34" t="n">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT34" t="n">
         <v>8.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AV34" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX34" t="n">
         <v>6.4</v>
@@ -7103,32 +7103,32 @@
         <v>5.8</v>
       </c>
       <c r="AZ34" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BA34" t="n">
         <v>4.4</v>
       </c>
       <c r="BB34" t="n">
-        <v>17.5</v>
+        <v>4.1</v>
       </c>
       <c r="BC34" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD34" t="n">
         <v>16</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF34" t="n">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="BG34" t="n">
         <v>9</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -7159,13 +7159,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="G35" t="n">
         <v>1.43</v>
       </c>
       <c r="H35" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I35" t="n">
         <v>17.5</v>
@@ -7174,7 +7174,7 @@
         <v>4.4</v>
       </c>
       <c r="K35" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L35" t="n">
         <v>1.39</v>
@@ -7201,10 +7201,10 @@
         <v>4.1</v>
       </c>
       <c r="T35" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="U35" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V35" t="n">
         <v>1.06</v>
@@ -7228,7 +7228,7 @@
         <v>6</v>
       </c>
       <c r="AC35" t="n">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="AD35" t="n">
         <v>1000</v>
@@ -7237,7 +7237,7 @@
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AG35" t="n">
         <v>12.5</v>
@@ -7252,7 +7252,7 @@
         <v>11</v>
       </c>
       <c r="AK35" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
         <v>1000</v>
@@ -7267,49 +7267,49 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ35" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR35" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS35" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AT35" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AU35" t="n">
         <v>6.2</v>
       </c>
       <c r="AV35" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AW35" t="n">
         <v>9</v>
       </c>
       <c r="AX35" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AY35" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ35" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="BA35" t="n">
         <v>9</v>
       </c>
       <c r="BB35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC35" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE35" t="n">
         <v>9</v>
@@ -7318,11 +7318,11 @@
         <v>7.6</v>
       </c>
       <c r="BG35" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
         <v>4.9</v>
       </c>
       <c r="L36" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M36" t="n">
         <v>1.03</v>
@@ -7410,7 +7410,7 @@
         <v>48</v>
       </c>
       <c r="Y36" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z36" t="n">
         <v>100</v>
@@ -7461,13 +7461,13 @@
         <v>50</v>
       </c>
       <c r="AP36" t="n">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="AQ36" t="n">
         <v>15</v>
       </c>
       <c r="AR36" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS36" t="n">
         <v>11.5</v>
@@ -7488,16 +7488,16 @@
         <v>11.5</v>
       </c>
       <c r="AY36" t="n">
-        <v>9.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="AZ36" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BA36" t="n">
         <v>10.5</v>
       </c>
       <c r="BB36" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC36" t="n">
         <v>13.5</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7616,7 @@
         <v>1000</v>
       </c>
       <c r="AC37" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD37" t="n">
         <v>1000</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -7798,22 +7798,22 @@
         <v>1000</v>
       </c>
       <c r="Y38" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z38" t="n">
         <v>1000</v>
       </c>
       <c r="AA38" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB38" t="n">
         <v>1000</v>
       </c>
       <c r="AC38" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD38" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE38" t="n">
         <v>1000</v>
@@ -7846,31 +7846,31 @@
         <v>1000</v>
       </c>
       <c r="AO38" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.26</v>
+        <v>5.1</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.26</v>
+        <v>5.1</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AT38" t="n">
         <v>13</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.33</v>
+        <v>5.8</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.29</v>
+        <v>6.4</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="AX38" t="n">
         <v>4.2</v>
@@ -7879,10 +7879,10 @@
         <v>4.2</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="BB38" t="n">
         <v>4.2</v>
@@ -7894,17 +7894,17 @@
         <v>4.2</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="BF38" t="n">
         <v>3.35</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.37</v>
+        <v>2.52</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7962,7 @@
         <v>2.16</v>
       </c>
       <c r="O39" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P39" t="n">
         <v>2.14</v>
@@ -8007,7 +8007,7 @@
         <v>12.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE39" t="n">
         <v>80</v>
@@ -8046,7 +8046,7 @@
         <v>16.5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR39" t="n">
         <v>20</v>
@@ -8064,7 +8064,7 @@
         <v>18</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX39" t="n">
         <v>10</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -8135,10 +8135,10 @@
         <v>1.76</v>
       </c>
       <c r="H40" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I40" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J40" t="n">
         <v>4</v>
@@ -8147,7 +8147,7 @@
         <v>4.4</v>
       </c>
       <c r="L40" t="n">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="M40" t="n">
         <v>1.06</v>
@@ -8159,7 +8159,7 @@
         <v>1.27</v>
       </c>
       <c r="P40" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="Q40" t="n">
         <v>1.9</v>
@@ -8177,7 +8177,7 @@
         <v>1.88</v>
       </c>
       <c r="V40" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W40" t="n">
         <v>2.3</v>
@@ -8207,7 +8207,7 @@
         <v>400</v>
       </c>
       <c r="AF40" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG40" t="n">
         <v>13</v>
@@ -8246,13 +8246,13 @@
         <v>18</v>
       </c>
       <c r="AS40" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AT40" t="n">
         <v>5.1</v>
       </c>
       <c r="AU40" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AV40" t="n">
         <v>14.5</v>
@@ -8267,7 +8267,7 @@
         <v>2.54</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2.82</v>
+        <v>10.5</v>
       </c>
       <c r="BA40" t="n">
         <v>3.05</v>
@@ -8276,10 +8276,10 @@
         <v>5</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD40" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BE40" t="n">
         <v>14</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -8526,10 +8526,10 @@
         <v>2.36</v>
       </c>
       <c r="I42" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K42" t="n">
         <v>3.65</v>
@@ -8541,7 +8541,7 @@
         <v>1.07</v>
       </c>
       <c r="N42" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O42" t="n">
         <v>1.3</v>
@@ -8589,7 +8589,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD42" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE42" t="n">
         <v>26</v>
@@ -8658,10 +8658,10 @@
         <v>14.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC42" t="n">
         <v>30</v>
@@ -8670,7 +8670,7 @@
         <v>10.5</v>
       </c>
       <c r="BE42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF42" t="n">
         <v>24</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
         <v>1.7</v>
       </c>
       <c r="S43" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T43" t="n">
         <v>2.3</v>
@@ -8780,7 +8780,7 @@
         <v>10.5</v>
       </c>
       <c r="AC43" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AD43" t="n">
         <v>300</v>
@@ -8813,7 +8813,7 @@
         <v>250</v>
       </c>
       <c r="AN43" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AO43" t="n">
         <v>1000</v>
@@ -8822,13 +8822,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ43" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="AR43" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS43" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AT43" t="n">
         <v>9.199999999999999</v>
@@ -8837,10 +8837,10 @@
         <v>15</v>
       </c>
       <c r="AV43" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="AW43" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AX43" t="n">
         <v>7</v>
@@ -8849,10 +8849,10 @@
         <v>11</v>
       </c>
       <c r="AZ43" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="BA43" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB43" t="n">
         <v>7.8</v>
@@ -8861,10 +8861,10 @@
         <v>12.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="BE43" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BF43" t="n">
         <v>3.4</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -8908,10 +8908,10 @@
         <v>3.4</v>
       </c>
       <c r="G44" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H44" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I44" t="n">
         <v>2.24</v>
@@ -8929,7 +8929,7 @@
         <v>1.05</v>
       </c>
       <c r="N44" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O44" t="n">
         <v>1.25</v>
@@ -8938,13 +8938,13 @@
         <v>2.14</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R44" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S44" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="T44" t="n">
         <v>1.65</v>
@@ -8956,28 +8956,28 @@
         <v>1.8</v>
       </c>
       <c r="W44" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
       </c>
       <c r="Y44" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z44" t="n">
         <v>17.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB44" t="n">
-        <v>160</v>
+        <v>18</v>
       </c>
       <c r="AC44" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD44" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE44" t="n">
         <v>150</v>
@@ -8986,10 +8986,10 @@
         <v>1000</v>
       </c>
       <c r="AG44" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="AI44" t="n">
         <v>1000</v>
@@ -9010,7 +9010,7 @@
         <v>1000</v>
       </c>
       <c r="AO44" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP44" t="n">
         <v>14.5</v>
@@ -9022,19 +9022,19 @@
         <v>11.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AT44" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AU44" t="n">
         <v>7.4</v>
       </c>
       <c r="AV44" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW44" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX44" t="n">
         <v>17</v>
@@ -9043,22 +9043,22 @@
         <v>11.5</v>
       </c>
       <c r="AZ44" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA44" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BB44" t="n">
         <v>30</v>
       </c>
       <c r="BC44" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BD44" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BE44" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BF44" t="n">
         <v>20</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -9117,7 +9117,7 @@
         <v>3.85</v>
       </c>
       <c r="L45" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M45" t="n">
         <v>1.05</v>
@@ -9162,7 +9162,7 @@
         <v>23</v>
       </c>
       <c r="AA45" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="AB45" t="n">
         <v>18</v>
@@ -9243,13 +9243,13 @@
         <v>16</v>
       </c>
       <c r="BB45" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC45" t="n">
         <v>14.5</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE45" t="n">
         <v>4.9</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -9293,22 +9293,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="G46" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H46" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="I46" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="J46" t="n">
         <v>3.85</v>
       </c>
       <c r="K46" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L46" t="n">
         <v>1.36</v>
@@ -9338,16 +9338,16 @@
         <v>1.66</v>
       </c>
       <c r="U46" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V46" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W46" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X46" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y46" t="n">
         <v>14</v>
@@ -9371,7 +9371,7 @@
         <v>29</v>
       </c>
       <c r="AF46" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG46" t="n">
         <v>11.5</v>
@@ -9380,10 +9380,10 @@
         <v>15.5</v>
       </c>
       <c r="AI46" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ46" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK46" t="n">
         <v>24</v>
@@ -9395,7 +9395,7 @@
         <v>70</v>
       </c>
       <c r="AN46" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO46" t="n">
         <v>22</v>
@@ -9413,7 +9413,7 @@
         <v>40</v>
       </c>
       <c r="AT46" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU46" t="n">
         <v>8.199999999999999</v>
@@ -9422,22 +9422,22 @@
         <v>12</v>
       </c>
       <c r="AW46" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AX46" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY46" t="n">
         <v>11</v>
       </c>
       <c r="AZ46" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA46" t="n">
         <v>34</v>
       </c>
       <c r="BB46" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC46" t="n">
         <v>22</v>
@@ -9449,14 +9449,14 @@
         <v>55</v>
       </c>
       <c r="BF46" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG46" t="n">
         <v>20</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="G47" t="n">
         <v>16</v>
@@ -9502,7 +9502,7 @@
         <v>7</v>
       </c>
       <c r="K47" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9511,19 +9511,19 @@
         <v>1.02</v>
       </c>
       <c r="N47" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O47" t="n">
         <v>1.15</v>
       </c>
       <c r="P47" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R47" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="S47" t="n">
         <v>2.1</v>
@@ -9535,7 +9535,7 @@
         <v>1.81</v>
       </c>
       <c r="V47" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="W47" t="n">
         <v>1.06</v>
@@ -9592,7 +9592,7 @@
         <v>1000</v>
       </c>
       <c r="AO47" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AP47" t="n">
         <v>13</v>
@@ -9619,7 +9619,7 @@
         <v>10</v>
       </c>
       <c r="AX47" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY47" t="n">
         <v>10</v>
@@ -9631,26 +9631,26 @@
         <v>20</v>
       </c>
       <c r="BB47" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC47" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BD47" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BE47" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF47" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG47" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -9687,13 +9687,13 @@
         <v>3.45</v>
       </c>
       <c r="H48" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I48" t="n">
         <v>2.4</v>
       </c>
       <c r="J48" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K48" t="n">
         <v>3.75</v>
@@ -9720,7 +9720,7 @@
         <v>1.4</v>
       </c>
       <c r="S48" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T48" t="n">
         <v>1.67</v>
@@ -9729,10 +9729,10 @@
         <v>2.28</v>
       </c>
       <c r="V48" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W48" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X48" t="n">
         <v>17</v>
@@ -9741,10 +9741,10 @@
         <v>12</v>
       </c>
       <c r="Z48" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AB48" t="n">
         <v>15</v>
@@ -9756,7 +9756,7 @@
         <v>12</v>
       </c>
       <c r="AE48" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF48" t="n">
         <v>25</v>
@@ -9786,7 +9786,7 @@
         <v>48</v>
       </c>
       <c r="AO48" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AP48" t="n">
         <v>12</v>
@@ -9801,7 +9801,7 @@
         <v>14.5</v>
       </c>
       <c r="AT48" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU48" t="n">
         <v>6.4</v>
@@ -9825,26 +9825,26 @@
         <v>28</v>
       </c>
       <c r="BB48" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC48" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BD48" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE48" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF48" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG48" t="n">
         <v>14</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -9875,13 +9875,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G49" t="n">
         <v>2.42</v>
       </c>
       <c r="H49" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I49" t="n">
         <v>4.1</v>
@@ -9902,7 +9902,7 @@
         <v>2.86</v>
       </c>
       <c r="O49" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P49" t="n">
         <v>1.6</v>
@@ -9914,16 +9914,16 @@
         <v>1.23</v>
       </c>
       <c r="S49" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T49" t="n">
         <v>1.96</v>
       </c>
       <c r="U49" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V49" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W49" t="n">
         <v>1.7</v>
@@ -9974,7 +9974,7 @@
         <v>1000</v>
       </c>
       <c r="AM49" t="n">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="AN49" t="n">
         <v>1000</v>
@@ -10025,20 +10025,20 @@
         <v>14.5</v>
       </c>
       <c r="BD49" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="BE49" t="n">
         <v>10</v>
       </c>
       <c r="BF49" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="BG49" t="n">
         <v>50</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -10093,7 +10093,7 @@
         <v>1.02</v>
       </c>
       <c r="N50" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="O50" t="n">
         <v>1.11</v>
@@ -10177,7 +10177,7 @@
         <v>280</v>
       </c>
       <c r="AP50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AQ50" t="n">
         <v>65</v>
@@ -10192,7 +10192,7 @@
         <v>13</v>
       </c>
       <c r="AU50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV50" t="n">
         <v>55</v>
@@ -10207,7 +10207,7 @@
         <v>11</v>
       </c>
       <c r="AZ50" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BA50" t="n">
         <v>85</v>
@@ -10219,10 +10219,10 @@
         <v>12</v>
       </c>
       <c r="BD50" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE50" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="BF50" t="n">
         <v>2.76</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
         <v>1.79</v>
       </c>
       <c r="G52" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H52" t="n">
         <v>4.1</v>
@@ -10487,7 +10487,7 @@
         <v>1.15</v>
       </c>
       <c r="P52" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="Q52" t="n">
         <v>1.5</v>
@@ -10505,16 +10505,16 @@
         <v>2.52</v>
       </c>
       <c r="V52" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W52" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X52" t="n">
         <v>32</v>
       </c>
       <c r="Y52" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Z52" t="n">
         <v>46</v>
@@ -10565,16 +10565,16 @@
         <v>34</v>
       </c>
       <c r="AP52" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ52" t="n">
         <v>21</v>
       </c>
       <c r="AR52" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS52" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT52" t="n">
         <v>12.5</v>
@@ -10586,7 +10586,7 @@
         <v>15.5</v>
       </c>
       <c r="AW52" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX52" t="n">
         <v>12.5</v>
@@ -10598,7 +10598,7 @@
         <v>13.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB52" t="n">
         <v>17</v>
@@ -10610,17 +10610,17 @@
         <v>20</v>
       </c>
       <c r="BE52" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF52" t="n">
         <v>5.9</v>
       </c>
       <c r="BG52" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -10651,22 +10651,22 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="G53" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="H53" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I53" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J53" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K53" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L53" t="n">
         <v>1.59</v>
@@ -10675,13 +10675,13 @@
         <v>1.12</v>
       </c>
       <c r="N53" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O53" t="n">
         <v>1.54</v>
       </c>
       <c r="P53" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q53" t="n">
         <v>2.64</v>
@@ -10693,37 +10693,37 @@
         <v>5.4</v>
       </c>
       <c r="T53" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U53" t="n">
         <v>1.81</v>
       </c>
       <c r="V53" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W53" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="X53" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y53" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA53" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AB53" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC53" t="n">
         <v>7.2</v>
       </c>
       <c r="AD53" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE53" t="n">
         <v>70</v>
@@ -10738,13 +10738,13 @@
         <v>24</v>
       </c>
       <c r="AI53" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ53" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK53" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL53" t="n">
         <v>60</v>
@@ -10753,25 +10753,25 @@
         <v>190</v>
       </c>
       <c r="AN53" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO53" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP53" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ53" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR53" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AS53" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AT53" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AU53" t="n">
         <v>6.8</v>
@@ -10780,10 +10780,10 @@
         <v>16</v>
       </c>
       <c r="AW53" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX53" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY53" t="n">
         <v>10.5</v>
@@ -10792,29 +10792,29 @@
         <v>21</v>
       </c>
       <c r="BA53" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BB53" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BC53" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD53" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BE53" t="n">
         <v>70</v>
       </c>
       <c r="BF53" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BG53" t="n">
         <v>85</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -10857,7 +10857,7 @@
         <v>3.4</v>
       </c>
       <c r="J54" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K54" t="n">
         <v>4.3</v>
@@ -10890,7 +10890,7 @@
         <v>1.5</v>
       </c>
       <c r="U54" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V54" t="n">
         <v>1.01</v>
@@ -10920,7 +10920,7 @@
         <v>18</v>
       </c>
       <c r="AE54" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF54" t="n">
         <v>22</v>
@@ -10953,7 +10953,7 @@
         <v>20</v>
       </c>
       <c r="AP54" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ54" t="n">
         <v>14</v>
@@ -10962,7 +10962,7 @@
         <v>19</v>
       </c>
       <c r="AS54" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT54" t="n">
         <v>11.5</v>
@@ -10989,7 +10989,7 @@
         <v>23</v>
       </c>
       <c r="BB54" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC54" t="n">
         <v>15</v>
@@ -10998,7 +10998,7 @@
         <v>19</v>
       </c>
       <c r="BE54" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF54" t="n">
         <v>8.199999999999999</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -11042,13 +11042,13 @@
         <v>3.55</v>
       </c>
       <c r="G55" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H55" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I55" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="J55" t="n">
         <v>2.86</v>
@@ -11069,7 +11069,7 @@
         <v>1.53</v>
       </c>
       <c r="P55" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q55" t="n">
         <v>1.98</v>
@@ -11090,7 +11090,7 @@
         <v>1.6</v>
       </c>
       <c r="W55" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
@@ -11129,13 +11129,13 @@
         <v>460</v>
       </c>
       <c r="AJ55" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK55" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AL55" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AM55" t="n">
         <v>1000</v>
@@ -11177,7 +11177,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ55" t="n">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
       <c r="BA55" t="n">
         <v>28</v>
@@ -11189,20 +11189,20 @@
         <v>36</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.5</v>
+        <v>2.64</v>
       </c>
       <c r="BE55" t="n">
         <v>2.62</v>
       </c>
       <c r="BF55" t="n">
-        <v>3.5</v>
+        <v>2.64</v>
       </c>
       <c r="BG55" t="n">
         <v>32</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -11233,22 +11233,22 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.86</v>
+        <v>4</v>
       </c>
       <c r="G56" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="H56" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="I56" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="J56" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K56" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L56" t="n">
         <v>1.01</v>
@@ -11263,16 +11263,16 @@
         <v>1.13</v>
       </c>
       <c r="P56" t="n">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="Q56" t="n">
         <v>1.4</v>
       </c>
       <c r="R56" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S56" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="T56" t="n">
         <v>1.01</v>
@@ -11287,116 +11287,116 @@
         <v>1.01</v>
       </c>
       <c r="X56" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y56" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z56" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA56" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AB56" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC56" t="n">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="AD56" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE56" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF56" t="n">
         <v>1000</v>
       </c>
       <c r="AG56" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH56" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI56" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AJ56" t="n">
         <v>1000</v>
       </c>
       <c r="AK56" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL56" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM56" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN56" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO56" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.62</v>
+        <v>6.2</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.56</v>
+        <v>12.5</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.56</v>
+        <v>12.5</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.61</v>
+        <v>17</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.61</v>
+        <v>21</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.48</v>
+        <v>9.6</v>
       </c>
       <c r="AV56" t="n">
-        <v>1.49</v>
+        <v>9.4</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.56</v>
+        <v>14</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.63</v>
+        <v>6.6</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.65</v>
+        <v>13.5</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.54</v>
+        <v>13.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.59</v>
+        <v>20</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.65</v>
+        <v>7.2</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.63</v>
+        <v>6.8</v>
       </c>
       <c r="BD56" t="n">
-        <v>1.63</v>
+        <v>6.6</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.64</v>
+        <v>7</v>
       </c>
       <c r="BF56" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BG56" t="n">
-        <v>1.84</v>
+        <v>6</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -11430,13 +11430,13 @@
         <v>2.48</v>
       </c>
       <c r="G57" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H57" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="J57" t="n">
         <v>3.95</v>
@@ -11460,7 +11460,7 @@
         <v>2.5</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R57" t="n">
         <v>1.61</v>
@@ -11478,7 +11478,7 @@
         <v>1.52</v>
       </c>
       <c r="W57" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X57" t="n">
         <v>24</v>
@@ -11487,7 +11487,7 @@
         <v>17.5</v>
       </c>
       <c r="Z57" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA57" t="n">
         <v>44</v>
@@ -11529,10 +11529,10 @@
         <v>60</v>
       </c>
       <c r="AN57" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO57" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP57" t="n">
         <v>20</v>
@@ -11541,7 +11541,7 @@
         <v>15</v>
       </c>
       <c r="AR57" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS57" t="n">
         <v>36</v>
@@ -11574,7 +11574,7 @@
         <v>30</v>
       </c>
       <c r="BC57" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD57" t="n">
         <v>26</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -11621,10 +11621,10 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G58" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H58" t="n">
         <v>3.1</v>
@@ -11633,7 +11633,7 @@
         <v>3.3</v>
       </c>
       <c r="J58" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K58" t="n">
         <v>3.95</v>
@@ -11645,43 +11645,43 @@
         <v>1.04</v>
       </c>
       <c r="N58" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O58" t="n">
         <v>1.21</v>
       </c>
       <c r="P58" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q58" t="n">
         <v>1.67</v>
       </c>
       <c r="R58" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S58" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U58" t="n">
         <v>2.58</v>
       </c>
-      <c r="T58" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U58" t="n">
-        <v>2.5</v>
-      </c>
       <c r="V58" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W58" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="X58" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y58" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z58" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA58" t="n">
         <v>60</v>
@@ -11690,7 +11690,7 @@
         <v>14</v>
       </c>
       <c r="AC58" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD58" t="n">
         <v>15.5</v>
@@ -11705,7 +11705,7 @@
         <v>12</v>
       </c>
       <c r="AH58" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI58" t="n">
         <v>38</v>
@@ -11738,10 +11738,10 @@
         <v>19.5</v>
       </c>
       <c r="AS58" t="n">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="AT58" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU58" t="n">
         <v>7.8</v>
@@ -11750,7 +11750,7 @@
         <v>12.5</v>
       </c>
       <c r="AW58" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AX58" t="n">
         <v>13.5</v>
@@ -11771,20 +11771,20 @@
         <v>18</v>
       </c>
       <c r="BD58" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BE58" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BF58" t="n">
         <v>10</v>
       </c>
       <c r="BG58" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -11818,28 +11818,28 @@
         <v>4.5</v>
       </c>
       <c r="G59" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H59" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I59" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J59" t="n">
         <v>3.2</v>
       </c>
       <c r="K59" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L59" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="M59" t="n">
         <v>1.1</v>
       </c>
       <c r="N59" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="O59" t="n">
         <v>1.44</v>
@@ -11857,7 +11857,7 @@
         <v>4.5</v>
       </c>
       <c r="T59" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U59" t="n">
         <v>1.8</v>
@@ -11869,16 +11869,16 @@
         <v>1.23</v>
       </c>
       <c r="X59" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y59" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z59" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA59" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AB59" t="n">
         <v>16.5</v>
@@ -11887,16 +11887,16 @@
         <v>9.4</v>
       </c>
       <c r="AD59" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE59" t="n">
         <v>65</v>
       </c>
       <c r="AF59" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AG59" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AH59" t="n">
         <v>28</v>
@@ -11938,7 +11938,7 @@
         <v>11.5</v>
       </c>
       <c r="AU59" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV59" t="n">
         <v>9</v>
@@ -11947,7 +11947,7 @@
         <v>11.5</v>
       </c>
       <c r="AX59" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AY59" t="n">
         <v>10.5</v>
@@ -11956,29 +11956,29 @@
         <v>13</v>
       </c>
       <c r="BA59" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BB59" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BC59" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BD59" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BE59" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF59" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BG59" t="n">
         <v>12.5</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -12015,10 +12015,10 @@
         <v>2.84</v>
       </c>
       <c r="H60" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I60" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J60" t="n">
         <v>3.5</v>
@@ -12033,7 +12033,7 @@
         <v>1.05</v>
       </c>
       <c r="N60" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O60" t="n">
         <v>1.23</v>
@@ -12057,7 +12057,7 @@
         <v>2.4</v>
       </c>
       <c r="V60" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W60" t="n">
         <v>1.54</v>
@@ -12078,7 +12078,7 @@
         <v>15</v>
       </c>
       <c r="AC60" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD60" t="n">
         <v>13.5</v>
@@ -12126,13 +12126,13 @@
         <v>17</v>
       </c>
       <c r="AS60" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT60" t="n">
         <v>12</v>
       </c>
       <c r="AU60" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV60" t="n">
         <v>10.5</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -12227,13 +12227,13 @@
         <v>1.12</v>
       </c>
       <c r="N61" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O61" t="n">
         <v>1.5</v>
       </c>
       <c r="P61" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q61" t="n">
         <v>2.5</v>
@@ -12242,7 +12242,7 @@
         <v>1.2</v>
       </c>
       <c r="S61" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T61" t="n">
         <v>2</v>
@@ -12251,122 +12251,122 @@
         <v>1.81</v>
       </c>
       <c r="V61" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W61" t="n">
         <v>1.56</v>
       </c>
       <c r="X61" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y61" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y61" t="n">
-        <v>12</v>
-      </c>
       <c r="Z61" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA61" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB61" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC61" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD61" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AE61" t="n">
         <v>1000</v>
       </c>
       <c r="AF61" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG61" t="n">
         <v>14.5</v>
       </c>
       <c r="AH61" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI61" t="n">
         <v>1000</v>
       </c>
       <c r="AJ61" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AK61" t="n">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="AL61" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AM61" t="n">
         <v>1000</v>
       </c>
       <c r="AN61" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO61" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AP61" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT61" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ61" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR61" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS61" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT61" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AU61" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AV61" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW61" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AX61" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AY61" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ61" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA61" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BB61" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BC61" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BD61" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BE61" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BF61" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="BG61" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -12397,16 +12397,16 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="G62" t="n">
         <v>1.21</v>
       </c>
       <c r="H62" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="J62" t="n">
         <v>9.199999999999999</v>
@@ -12421,7 +12421,7 @@
         <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>2.32</v>
+        <v>1.02</v>
       </c>
       <c r="O62" t="n">
         <v>1.05</v>
@@ -12448,7 +12448,7 @@
         <v>1.05</v>
       </c>
       <c r="W62" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="X62" t="n">
         <v>1000</v>
@@ -12466,7 +12466,7 @@
         <v>80</v>
       </c>
       <c r="AC62" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AD62" t="n">
         <v>1000</v>
@@ -12475,10 +12475,10 @@
         <v>1000</v>
       </c>
       <c r="AF62" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG62" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AH62" t="n">
         <v>1000</v>
@@ -12487,58 +12487,58 @@
         <v>1000</v>
       </c>
       <c r="AJ62" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK62" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AL62" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM62" t="n">
         <v>1000</v>
       </c>
       <c r="AN62" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="AO62" t="n">
         <v>1000</v>
       </c>
       <c r="AP62" t="n">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="AQ62" t="n">
-        <v>5.1</v>
+        <v>9.6</v>
       </c>
       <c r="AR62" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AS62" t="n">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="AT62" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU62" t="n">
         <v>11.5</v>
       </c>
       <c r="AV62" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW62" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="AX62" t="n">
         <v>11</v>
       </c>
       <c r="AY62" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ62" t="n">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="BA62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BB62" t="n">
         <v>9.4</v>
@@ -12547,10 +12547,10 @@
         <v>11.5</v>
       </c>
       <c r="BD62" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE62" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="BF62" t="n">
         <v>2.18</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -12630,13 +12630,13 @@
         <v>2.04</v>
       </c>
       <c r="S63" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="T63" t="n">
         <v>2.16</v>
       </c>
       <c r="U63" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V63" t="n">
         <v>6.6</v>
@@ -12648,10 +12648,10 @@
         <v>50</v>
       </c>
       <c r="Y63" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z63" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA63" t="n">
         <v>8.800000000000001</v>
@@ -12660,7 +12660,7 @@
         <v>80</v>
       </c>
       <c r="AC63" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AD63" t="n">
         <v>13</v>
@@ -12669,7 +12669,7 @@
         <v>13</v>
       </c>
       <c r="AF63" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AG63" t="n">
         <v>75</v>
@@ -12678,61 +12678,61 @@
         <v>46</v>
       </c>
       <c r="AI63" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ63" t="n">
         <v>1000</v>
       </c>
       <c r="AK63" t="n">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="AL63" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AM63" t="n">
         <v>200</v>
       </c>
       <c r="AN63" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AO63" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AP63" t="n">
         <v>44</v>
       </c>
       <c r="AQ63" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR63" t="n">
         <v>8.6</v>
       </c>
       <c r="AS63" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT63" t="n">
         <v>65</v>
       </c>
       <c r="AU63" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV63" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW63" t="n">
         <v>12</v>
       </c>
       <c r="AX63" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="AY63" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AZ63" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BA63" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB63" t="n">
         <v>160</v>
@@ -12750,11 +12750,11 @@
         <v>110</v>
       </c>
       <c r="BG63" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -12797,7 +12797,7 @@
         <v>4.1</v>
       </c>
       <c r="J64" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K64" t="n">
         <v>3.8</v>
@@ -12824,7 +12824,7 @@
         <v>1.5</v>
       </c>
       <c r="S64" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T64" t="n">
         <v>1.67</v>
@@ -12833,7 +12833,7 @@
         <v>2.42</v>
       </c>
       <c r="V64" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W64" t="n">
         <v>1.92</v>
@@ -12845,7 +12845,7 @@
         <v>17.5</v>
       </c>
       <c r="Z64" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA64" t="n">
         <v>75</v>
@@ -12920,7 +12920,7 @@
         <v>13</v>
       </c>
       <c r="AY64" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ64" t="n">
         <v>14</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -12979,19 +12979,19 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="G65" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="H65" t="n">
         <v>12</v>
       </c>
       <c r="I65" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J65" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="K65" t="n">
         <v>8.199999999999999</v>
@@ -13015,34 +13015,34 @@
         <v>1.31</v>
       </c>
       <c r="R65" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="S65" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="T65" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U65" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V65" t="n">
         <v>1.08</v>
       </c>
       <c r="W65" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="X65" t="n">
         <v>55</v>
       </c>
       <c r="Y65" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Z65" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA65" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AB65" t="n">
         <v>17</v>
@@ -13051,19 +13051,19 @@
         <v>19.5</v>
       </c>
       <c r="AD65" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AE65" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF65" t="n">
         <v>12</v>
       </c>
       <c r="AG65" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH65" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI65" t="n">
         <v>100</v>
@@ -13075,16 +13075,16 @@
         <v>12.5</v>
       </c>
       <c r="AL65" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM65" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN65" t="n">
         <v>2.96</v>
       </c>
       <c r="AO65" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP65" t="n">
         <v>50</v>
@@ -13099,7 +13099,7 @@
         <v>110</v>
       </c>
       <c r="AT65" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU65" t="n">
         <v>18.5</v>
@@ -13117,10 +13117,10 @@
         <v>11</v>
       </c>
       <c r="AZ65" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA65" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BB65" t="n">
         <v>11</v>
@@ -13129,20 +13129,20 @@
         <v>12</v>
       </c>
       <c r="BD65" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE65" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BF65" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BG65" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -13182,13 +13182,13 @@
         <v>4.6</v>
       </c>
       <c r="I66" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J66" t="n">
         <v>3.35</v>
       </c>
       <c r="K66" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L66" t="n">
         <v>1.48</v>
@@ -13206,7 +13206,7 @@
         <v>1.71</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R66" t="n">
         <v>1.26</v>
@@ -13218,7 +13218,7 @@
         <v>1.98</v>
       </c>
       <c r="U66" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="V66" t="n">
         <v>1.24</v>
@@ -13317,26 +13317,26 @@
         <v>6.8</v>
       </c>
       <c r="BB66" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="BC66" t="n">
         <v>11.5</v>
       </c>
       <c r="BD66" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE66" t="n">
         <v>7</v>
       </c>
       <c r="BF66" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BG66" t="n">
         <v>7</v>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -13370,7 +13370,7 @@
         <v>1.49</v>
       </c>
       <c r="G67" t="n">
-        <v>2.64</v>
+        <v>5.2</v>
       </c>
       <c r="H67" t="n">
         <v>2.86</v>
@@ -13382,7 +13382,7 @@
         <v>3.05</v>
       </c>
       <c r="K67" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="L67" t="n">
         <v>1.01</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -13564,7 +13564,7 @@
         <v>1.67</v>
       </c>
       <c r="G68" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H68" t="n">
         <v>4.4</v>
@@ -13573,10 +13573,10 @@
         <v>5.4</v>
       </c>
       <c r="J68" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="K68" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L68" t="n">
         <v>1.01</v>
@@ -13591,10 +13591,10 @@
         <v>1.24</v>
       </c>
       <c r="P68" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R68" t="n">
         <v>1.46</v>
@@ -13606,13 +13606,13 @@
         <v>1.68</v>
       </c>
       <c r="U68" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V68" t="n">
         <v>1.23</v>
       </c>
       <c r="W68" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X68" t="n">
         <v>21</v>
@@ -13624,7 +13624,7 @@
         <v>42</v>
       </c>
       <c r="AA68" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB68" t="n">
         <v>11</v>
@@ -13645,7 +13645,7 @@
         <v>10</v>
       </c>
       <c r="AH68" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI68" t="n">
         <v>60</v>
@@ -13654,7 +13654,7 @@
         <v>19.5</v>
       </c>
       <c r="AK68" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL68" t="n">
         <v>32</v>
@@ -13669,10 +13669,10 @@
         <v>60</v>
       </c>
       <c r="AP68" t="n">
-        <v>18</v>
+        <v>6.4</v>
       </c>
       <c r="AQ68" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR68" t="n">
         <v>7.8</v>
@@ -13681,16 +13681,16 @@
         <v>8.6</v>
       </c>
       <c r="AT68" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU68" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AV68" t="n">
         <v>10.5</v>
       </c>
       <c r="AW68" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX68" t="n">
         <v>10</v>
@@ -13699,16 +13699,16 @@
         <v>5.8</v>
       </c>
       <c r="AZ68" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA68" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB68" t="n">
         <v>16</v>
       </c>
       <c r="BC68" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="BD68" t="n">
         <v>16</v>
@@ -13717,14 +13717,14 @@
         <v>8.6</v>
       </c>
       <c r="BF68" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BG68" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -13758,13 +13758,13 @@
         <v>1.63</v>
       </c>
       <c r="G69" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H69" t="n">
         <v>6</v>
       </c>
       <c r="I69" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J69" t="n">
         <v>3.75</v>
@@ -13785,22 +13785,22 @@
         <v>1.37</v>
       </c>
       <c r="P69" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R69" t="n">
         <v>1.28</v>
       </c>
       <c r="S69" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T69" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U69" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V69" t="n">
         <v>1.15</v>
@@ -13821,13 +13821,13 @@
         <v>1000</v>
       </c>
       <c r="AB69" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC69" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD69" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE69" t="n">
         <v>120</v>
@@ -13839,13 +13839,13 @@
         <v>12</v>
       </c>
       <c r="AH69" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI69" t="n">
         <v>120</v>
       </c>
       <c r="AJ69" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AK69" t="n">
         <v>23</v>
@@ -13869,10 +13869,10 @@
         <v>15.5</v>
       </c>
       <c r="AR69" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AS69" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AT69" t="n">
         <v>6</v>
@@ -13884,7 +13884,7 @@
         <v>21</v>
       </c>
       <c r="AW69" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX69" t="n">
         <v>7.8</v>
@@ -13896,7 +13896,7 @@
         <v>20</v>
       </c>
       <c r="BA69" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB69" t="n">
         <v>14</v>
@@ -13905,20 +13905,20 @@
         <v>16.5</v>
       </c>
       <c r="BD69" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BE69" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF69" t="n">
         <v>9.4</v>
       </c>
       <c r="BG69" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -13973,13 +13973,13 @@
         <v>1.01</v>
       </c>
       <c r="N70" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O70" t="n">
         <v>1.23</v>
       </c>
       <c r="P70" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q70" t="n">
         <v>1.23</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -14176,7 +14176,7 @@
         <v>2.1</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R71" t="n">
         <v>1.43</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -14337,22 +14337,22 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G72" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="H72" t="n">
         <v>4.2</v>
       </c>
       <c r="I72" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J72" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K72" t="n">
         <v>4</v>
-      </c>
-      <c r="K72" t="n">
-        <v>4.2</v>
       </c>
       <c r="L72" t="n">
         <v>1.32</v>
@@ -14367,7 +14367,7 @@
         <v>1.22</v>
       </c>
       <c r="P72" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q72" t="n">
         <v>1.67</v>
@@ -14376,7 +14376,7 @@
         <v>1.56</v>
       </c>
       <c r="S72" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T72" t="n">
         <v>1.64</v>
@@ -14385,31 +14385,31 @@
         <v>2.44</v>
       </c>
       <c r="V72" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W72" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X72" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y72" t="n">
         <v>27</v>
       </c>
       <c r="Z72" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AA72" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB72" t="n">
         <v>12.5</v>
       </c>
       <c r="AC72" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD72" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE72" t="n">
         <v>1000</v>
@@ -14424,19 +14424,19 @@
         <v>16.5</v>
       </c>
       <c r="AI72" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ72" t="n">
         <v>22</v>
       </c>
       <c r="AK72" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL72" t="n">
         <v>29</v>
       </c>
       <c r="AM72" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN72" t="n">
         <v>9.6</v>
@@ -14445,7 +14445,7 @@
         <v>90</v>
       </c>
       <c r="AP72" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AQ72" t="n">
         <v>17.5</v>
@@ -14466,19 +14466,19 @@
         <v>14.5</v>
       </c>
       <c r="AW72" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AX72" t="n">
         <v>12</v>
       </c>
       <c r="AY72" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ72" t="n">
         <v>14.5</v>
       </c>
       <c r="BA72" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BB72" t="n">
         <v>18</v>
@@ -14487,10 +14487,10 @@
         <v>15.5</v>
       </c>
       <c r="BD72" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BE72" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BF72" t="n">
         <v>8.4</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -14534,10 +14534,10 @@
         <v>2.64</v>
       </c>
       <c r="G73" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H73" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="I73" t="n">
         <v>2.68</v>
@@ -14555,7 +14555,7 @@
         <v>1.04</v>
       </c>
       <c r="N73" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O73" t="n">
         <v>1.2</v>
@@ -14567,19 +14567,19 @@
         <v>1.63</v>
       </c>
       <c r="R73" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S73" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T73" t="n">
         <v>1.55</v>
       </c>
       <c r="U73" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V73" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W73" t="n">
         <v>1.58</v>
@@ -14609,7 +14609,7 @@
         <v>25</v>
       </c>
       <c r="AF73" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG73" t="n">
         <v>12.5</v>
@@ -14639,7 +14639,7 @@
         <v>15.5</v>
       </c>
       <c r="AP73" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ73" t="n">
         <v>14</v>
@@ -14660,7 +14660,7 @@
         <v>11</v>
       </c>
       <c r="AW73" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX73" t="n">
         <v>19</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -14728,7 +14728,7 @@
         <v>2.52</v>
       </c>
       <c r="G74" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H74" t="n">
         <v>2.98</v>
@@ -14758,16 +14758,16 @@
         <v>2</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R74" t="n">
         <v>1.39</v>
       </c>
       <c r="S74" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T74" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U74" t="n">
         <v>2.22</v>
@@ -14776,7 +14776,7 @@
         <v>1.48</v>
       </c>
       <c r="W74" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X74" t="n">
         <v>18.5</v>
@@ -14806,7 +14806,7 @@
         <v>17.5</v>
       </c>
       <c r="AG74" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH74" t="n">
         <v>17</v>
@@ -14815,19 +14815,19 @@
         <v>44</v>
       </c>
       <c r="AJ74" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL74" t="n">
         <v>38</v>
       </c>
-      <c r="AK74" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL74" t="n">
-        <v>40</v>
-      </c>
       <c r="AM74" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN74" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO74" t="n">
         <v>29</v>
@@ -14854,7 +14854,7 @@
         <v>11.5</v>
       </c>
       <c r="AW74" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX74" t="n">
         <v>15</v>
@@ -14866,19 +14866,19 @@
         <v>14.5</v>
       </c>
       <c r="BA74" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB74" t="n">
-        <v>8.4</v>
+        <v>30</v>
       </c>
       <c r="BC74" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD74" t="n">
         <v>32</v>
       </c>
       <c r="BE74" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF74" t="n">
         <v>18.5</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -14919,10 +14919,10 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G75" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="H75" t="n">
         <v>4.2</v>
@@ -14931,7 +14931,7 @@
         <v>4.5</v>
       </c>
       <c r="J75" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K75" t="n">
         <v>3.95</v>
@@ -14949,13 +14949,13 @@
         <v>1.28</v>
       </c>
       <c r="P75" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R75" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S75" t="n">
         <v>3.1</v>
@@ -14964,13 +14964,13 @@
         <v>1.73</v>
       </c>
       <c r="U75" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V75" t="n">
         <v>1.29</v>
       </c>
       <c r="W75" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X75" t="n">
         <v>20</v>
@@ -14979,7 +14979,7 @@
         <v>18</v>
       </c>
       <c r="Z75" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA75" t="n">
         <v>1000</v>
@@ -15012,7 +15012,7 @@
         <v>1000</v>
       </c>
       <c r="AK75" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL75" t="n">
         <v>1000</v>
@@ -15021,19 +15021,19 @@
         <v>1000</v>
       </c>
       <c r="AN75" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO75" t="n">
         <v>1000</v>
       </c>
       <c r="AP75" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ75" t="n">
         <v>15</v>
       </c>
       <c r="AR75" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS75" t="n">
         <v>36</v>
@@ -15066,10 +15066,10 @@
         <v>19</v>
       </c>
       <c r="BC75" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD75" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BE75" t="n">
         <v>36</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -15119,13 +15119,13 @@
         <v>1.83</v>
       </c>
       <c r="H76" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I76" t="n">
         <v>4.8</v>
       </c>
       <c r="J76" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K76" t="n">
         <v>4.3</v>
@@ -15146,7 +15146,7 @@
         <v>2.58</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R76" t="n">
         <v>1.62</v>
@@ -15161,7 +15161,7 @@
         <v>2.5</v>
       </c>
       <c r="V76" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W76" t="n">
         <v>2.2</v>
@@ -15212,7 +15212,7 @@
         <v>26</v>
       </c>
       <c r="AM76" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN76" t="n">
         <v>8.199999999999999</v>
@@ -15266,17 +15266,17 @@
         <v>23</v>
       </c>
       <c r="BE76" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BF76" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG76" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -15322,7 +15322,7 @@
         <v>3.65</v>
       </c>
       <c r="K77" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L77" t="n">
         <v>1.42</v>
@@ -15337,10 +15337,10 @@
         <v>1.33</v>
       </c>
       <c r="P77" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R77" t="n">
         <v>1.36</v>
@@ -15349,16 +15349,16 @@
         <v>3.6</v>
       </c>
       <c r="T77" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U77" t="n">
         <v>2.1</v>
       </c>
       <c r="V77" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W77" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X77" t="n">
         <v>15</v>
@@ -15370,7 +15370,7 @@
         <v>27</v>
       </c>
       <c r="AA77" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB77" t="n">
         <v>9.4</v>
@@ -15385,16 +15385,16 @@
         <v>1000</v>
       </c>
       <c r="AF77" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG77" t="n">
         <v>11</v>
       </c>
       <c r="AH77" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI77" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ77" t="n">
         <v>26</v>
@@ -15412,7 +15412,7 @@
         <v>16.5</v>
       </c>
       <c r="AO77" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP77" t="n">
         <v>13</v>
@@ -15421,7 +15421,7 @@
         <v>12.5</v>
       </c>
       <c r="AR77" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AS77" t="n">
         <v>34</v>
@@ -15448,16 +15448,16 @@
         <v>17</v>
       </c>
       <c r="BA77" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="BB77" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BC77" t="n">
         <v>19.5</v>
       </c>
       <c r="BD77" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BE77" t="n">
         <v>38</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -15501,16 +15501,16 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="G78" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="H78" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I78" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J78" t="n">
         <v>4.8</v>
@@ -15543,19 +15543,19 @@
         <v>2.08</v>
       </c>
       <c r="T78" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U78" t="n">
         <v>2.48</v>
       </c>
       <c r="V78" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W78" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="X78" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Y78" t="n">
         <v>1000</v>
@@ -15579,7 +15579,7 @@
         <v>1000</v>
       </c>
       <c r="AF78" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG78" t="n">
         <v>11</v>
@@ -15594,7 +15594,7 @@
         <v>18</v>
       </c>
       <c r="AK78" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL78" t="n">
         <v>1000</v>
@@ -15603,22 +15603,22 @@
         <v>1000</v>
       </c>
       <c r="AN78" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO78" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AP78" t="n">
         <v>6.4</v>
       </c>
       <c r="AQ78" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR78" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR78" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AS78" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT78" t="n">
         <v>13</v>
@@ -15627,10 +15627,10 @@
         <v>10</v>
       </c>
       <c r="AV78" t="n">
-        <v>16.5</v>
+        <v>5.7</v>
       </c>
       <c r="AW78" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX78" t="n">
         <v>11.5</v>
@@ -15642,10 +15642,10 @@
         <v>16</v>
       </c>
       <c r="BA78" t="n">
-        <v>6.4</v>
+        <v>38</v>
       </c>
       <c r="BB78" t="n">
-        <v>5.9</v>
+        <v>13.5</v>
       </c>
       <c r="BC78" t="n">
         <v>14</v>
@@ -15654,17 +15654,17 @@
         <v>21</v>
       </c>
       <c r="BE78" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF78" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BG78" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -15695,10 +15695,10 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G79" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="H79" t="n">
         <v>3.6</v>
@@ -15710,7 +15710,7 @@
         <v>4</v>
       </c>
       <c r="K79" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L79" t="n">
         <v>1.31</v>
@@ -15746,7 +15746,7 @@
         <v>1.37</v>
       </c>
       <c r="W79" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="X79" t="n">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>17</v>
       </c>
       <c r="AI79" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ79" t="n">
         <v>26</v>
@@ -15791,10 +15791,10 @@
         <v>21</v>
       </c>
       <c r="AL79" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM79" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN79" t="n">
         <v>11</v>
@@ -15809,10 +15809,10 @@
         <v>16</v>
       </c>
       <c r="AR79" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS79" t="n">
-        <v>7.8</v>
+        <v>50</v>
       </c>
       <c r="AT79" t="n">
         <v>11.5</v>
@@ -15824,7 +15824,7 @@
         <v>13</v>
       </c>
       <c r="AW79" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="AX79" t="n">
         <v>13</v>
@@ -15836,7 +15836,7 @@
         <v>13.5</v>
       </c>
       <c r="BA79" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BB79" t="n">
         <v>21</v>
@@ -15845,10 +15845,10 @@
         <v>16.5</v>
       </c>
       <c r="BD79" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="BE79" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF79" t="n">
         <v>9.4</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -15889,10 +15889,10 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="G80" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H80" t="n">
         <v>3.9</v>
@@ -15901,10 +15901,10 @@
         <v>4.5</v>
       </c>
       <c r="J80" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K80" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L80" t="n">
         <v>1.01</v>
@@ -15922,10 +15922,10 @@
         <v>1.46</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="R80" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S80" t="n">
         <v>6</v>
@@ -15940,10 +15940,10 @@
         <v>1.29</v>
       </c>
       <c r="W80" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X80" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="Y80" t="n">
         <v>11</v>
@@ -15970,7 +15970,7 @@
         <v>13.5</v>
       </c>
       <c r="AG80" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH80" t="n">
         <v>28</v>
@@ -16003,10 +16003,10 @@
         <v>8.6</v>
       </c>
       <c r="AR80" t="n">
-        <v>23</v>
+        <v>6.2</v>
       </c>
       <c r="AS80" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT80" t="n">
         <v>5.9</v>
@@ -16018,7 +16018,7 @@
         <v>15.5</v>
       </c>
       <c r="AW80" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX80" t="n">
         <v>10.5</v>
@@ -16027,32 +16027,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ80" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA80" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB80" t="n">
         <v>6.4</v>
       </c>
-      <c r="BB80" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BC80" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BD80" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE80" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF80" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BG80" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -16107,19 +16107,19 @@
         <v>1.04</v>
       </c>
       <c r="N81" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O81" t="n">
         <v>1.2</v>
       </c>
       <c r="P81" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q81" t="n">
         <v>1.62</v>
       </c>
       <c r="R81" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S81" t="n">
         <v>2.58</v>
@@ -16137,7 +16137,7 @@
         <v>1.87</v>
       </c>
       <c r="X81" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y81" t="n">
         <v>19</v>
@@ -16158,7 +16158,7 @@
         <v>15</v>
       </c>
       <c r="AE81" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF81" t="n">
         <v>16.5</v>
@@ -16176,7 +16176,7 @@
         <v>26</v>
       </c>
       <c r="AK81" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL81" t="n">
         <v>29</v>
@@ -16188,7 +16188,7 @@
         <v>11</v>
       </c>
       <c r="AO81" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP81" t="n">
         <v>20</v>
@@ -16242,11 +16242,11 @@
         <v>9.6</v>
       </c>
       <c r="BG81" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -16286,7 +16286,7 @@
         <v>4.6</v>
       </c>
       <c r="I82" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J82" t="n">
         <v>3.65</v>
@@ -16295,37 +16295,37 @@
         <v>4.1</v>
       </c>
       <c r="L82" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M82" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N82" t="n">
-        <v>3.75</v>
+        <v>1.9</v>
       </c>
       <c r="O82" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P82" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Q82" t="n">
         <v>1.9</v>
       </c>
       <c r="R82" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S82" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="T82" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U82" t="n">
         <v>2.04</v>
       </c>
       <c r="V82" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W82" t="n">
         <v>2.1</v>
@@ -16415,7 +16415,7 @@
         <v>7.6</v>
       </c>
       <c r="AZ82" t="n">
-        <v>16.5</v>
+        <v>3.6</v>
       </c>
       <c r="BA82" t="n">
         <v>4</v>
@@ -16433,14 +16433,14 @@
         <v>4.1</v>
       </c>
       <c r="BF82" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG82" t="n">
         <v>4</v>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -16474,16 +16474,16 @@
         <v>7.4</v>
       </c>
       <c r="G83" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H83" t="n">
         <v>1.42</v>
       </c>
       <c r="I83" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="J83" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K83" t="n">
         <v>6</v>
@@ -16501,31 +16501,31 @@
         <v>1.16</v>
       </c>
       <c r="P83" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R83" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="S83" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="T83" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U83" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="V83" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="W83" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X83" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Y83" t="n">
         <v>13.5</v>
@@ -16555,10 +16555,10 @@
         <v>32</v>
       </c>
       <c r="AH83" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI83" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ83" t="n">
         <v>1000</v>
@@ -16567,7 +16567,7 @@
         <v>110</v>
       </c>
       <c r="AL83" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AM83" t="n">
         <v>85</v>
@@ -16576,65 +16576,65 @@
         <v>1000</v>
       </c>
       <c r="AO83" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AP83" t="n">
         <v>7</v>
       </c>
       <c r="AQ83" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR83" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AS83" t="n">
         <v>11.5</v>
       </c>
       <c r="AT83" t="n">
-        <v>29</v>
+        <v>7.2</v>
       </c>
       <c r="AU83" t="n">
         <v>11</v>
       </c>
       <c r="AV83" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW83" t="n">
         <v>12</v>
       </c>
       <c r="AX83" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY83" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA83" t="n">
         <v>6.8</v>
       </c>
-      <c r="AZ83" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA83" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BB83" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC83" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC83" t="n">
+      <c r="BD83" t="n">
         <v>8</v>
       </c>
-      <c r="BD83" t="n">
-        <v>50</v>
-      </c>
       <c r="BE83" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF83" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG83" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
         <v>3.5</v>
       </c>
       <c r="O84" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P84" t="n">
         <v>1.86</v>
@@ -16701,7 +16701,7 @@
         <v>2.08</v>
       </c>
       <c r="R84" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S84" t="n">
         <v>3.75</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -16859,7 +16859,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G85" t="n">
         <v>1.82</v>
@@ -16874,7 +16874,7 @@
         <v>4.3</v>
       </c>
       <c r="K85" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L85" t="n">
         <v>1.01</v>
@@ -16889,7 +16889,7 @@
         <v>1.2</v>
       </c>
       <c r="P85" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q85" t="n">
         <v>1.59</v>
@@ -16898,10 +16898,10 @@
         <v>1.58</v>
       </c>
       <c r="S85" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T85" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U85" t="n">
         <v>2.38</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -17062,10 +17062,10 @@
         <v>2.64</v>
       </c>
       <c r="I86" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J86" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K86" t="n">
         <v>3.3</v>
@@ -17074,19 +17074,19 @@
         <v>1.01</v>
       </c>
       <c r="M86" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N86" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="O86" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P86" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R86" t="n">
         <v>1.22</v>
@@ -17095,19 +17095,19 @@
         <v>4.8</v>
       </c>
       <c r="T86" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U86" t="n">
         <v>1.86</v>
       </c>
       <c r="V86" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W86" t="n">
         <v>1.41</v>
       </c>
       <c r="X86" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y86" t="n">
         <v>8.800000000000001</v>
@@ -17128,7 +17128,7 @@
         <v>13</v>
       </c>
       <c r="AE86" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF86" t="n">
         <v>22</v>
@@ -17155,7 +17155,7 @@
         <v>1000</v>
       </c>
       <c r="AN86" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO86" t="n">
         <v>46</v>
@@ -17170,7 +17170,7 @@
         <v>14</v>
       </c>
       <c r="AS86" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT86" t="n">
         <v>8.6</v>
@@ -17197,7 +17197,7 @@
         <v>9.4</v>
       </c>
       <c r="BB86" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC86" t="n">
         <v>9</v>
@@ -17209,14 +17209,14 @@
         <v>10.5</v>
       </c>
       <c r="BF86" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG86" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -17271,13 +17271,13 @@
         <v>1.01</v>
       </c>
       <c r="N87" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="O87" t="n">
         <v>1.28</v>
       </c>
       <c r="P87" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q87" t="n">
         <v>1.28</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -17441,19 +17441,19 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G88" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="H88" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I88" t="n">
         <v>3</v>
       </c>
       <c r="J88" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K88" t="n">
         <v>4.4</v>
@@ -17477,22 +17477,22 @@
         <v>1.48</v>
       </c>
       <c r="R88" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S88" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T88" t="n">
         <v>1.48</v>
       </c>
       <c r="U88" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="V88" t="n">
         <v>1.5</v>
       </c>
       <c r="W88" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X88" t="n">
         <v>30</v>
@@ -17501,10 +17501,10 @@
         <v>22</v>
       </c>
       <c r="Z88" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA88" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB88" t="n">
         <v>18</v>
@@ -17546,7 +17546,7 @@
         <v>10</v>
       </c>
       <c r="AO88" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP88" t="n">
         <v>27</v>
@@ -17567,10 +17567,10 @@
         <v>9.6</v>
       </c>
       <c r="AV88" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW88" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX88" t="n">
         <v>17.5</v>
@@ -17585,7 +17585,7 @@
         <v>26</v>
       </c>
       <c r="BB88" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC88" t="n">
         <v>18.5</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -17635,7 +17635,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G89" t="n">
         <v>1.49</v>
@@ -17647,7 +17647,7 @@
         <v>7.8</v>
       </c>
       <c r="J89" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K89" t="n">
         <v>5.6</v>
@@ -17659,13 +17659,13 @@
         <v>1.02</v>
       </c>
       <c r="N89" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O89" t="n">
         <v>1.16</v>
       </c>
       <c r="P89" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q89" t="n">
         <v>1.51</v>
@@ -17680,16 +17680,16 @@
         <v>1.7</v>
       </c>
       <c r="U89" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V89" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W89" t="n">
         <v>3</v>
       </c>
       <c r="X89" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="Y89" t="n">
         <v>1000</v>
@@ -17704,7 +17704,7 @@
         <v>13</v>
       </c>
       <c r="AC89" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD89" t="n">
         <v>1000</v>
@@ -17713,7 +17713,7 @@
         <v>1000</v>
       </c>
       <c r="AF89" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG89" t="n">
         <v>10.5</v>
@@ -17743,13 +17743,13 @@
         <v>1000</v>
       </c>
       <c r="AP89" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ89" t="n">
         <v>21</v>
       </c>
       <c r="AR89" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS89" t="n">
         <v>46</v>
@@ -17785,7 +17785,7 @@
         <v>12.5</v>
       </c>
       <c r="BD89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE89" t="n">
         <v>34</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>
@@ -17829,10 +17829,10 @@
         </is>
       </c>
       <c r="F90" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G90" t="n">
         <v>1.5</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1.51</v>
       </c>
       <c r="H90" t="n">
         <v>6.6</v>
@@ -17841,10 +17841,10 @@
         <v>7.2</v>
       </c>
       <c r="J90" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K90" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="L90" t="n">
         <v>1.29</v>
@@ -17880,7 +17880,7 @@
         <v>1.16</v>
       </c>
       <c r="W90" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X90" t="n">
         <v>26</v>
@@ -17973,7 +17973,7 @@
         <v>34</v>
       </c>
       <c r="BB90" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC90" t="n">
         <v>13</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-21 20:18:38</t>
+          <t>2026-04-21 22:33:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-22.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.63</v>
+        <v>2.88</v>
       </c>
       <c r="G2" t="n">
-        <v>1.66</v>
+        <v>2.96</v>
       </c>
       <c r="H2" t="n">
-        <v>5.7</v>
+        <v>2.66</v>
       </c>
       <c r="I2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>10</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
         <v>6</v>
       </c>
-      <c r="J2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="X2" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AF2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL2" t="n">
         <v>27</v>
       </c>
       <c r="AM2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>15.5</v>
       </c>
       <c r="AO2" t="n">
         <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>42</v>
+        <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.6</v>
+        <v>5.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AX2" t="n">
         <v>10.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="BA2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BE2" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>14.5</v>
+        <v>36</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.55</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
-        <v>2.28</v>
+        <v>1.17</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>9.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.85</v>
+        <v>7.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.14</v>
+        <v>1.14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>2.44</v>
       </c>
       <c r="S3" t="n">
-        <v>3.95</v>
+        <v>1.67</v>
       </c>
       <c r="T3" t="n">
-        <v>1.88</v>
+        <v>1.49</v>
       </c>
       <c r="U3" t="n">
-        <v>2.06</v>
+        <v>2.74</v>
       </c>
       <c r="V3" t="n">
-        <v>1.76</v>
+        <v>6.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA3" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y3" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL3" t="n">
+      <c r="BB3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF3" t="n">
         <v>60</v>
       </c>
-      <c r="AM3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>90</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>40</v>
-      </c>
       <c r="BG3" t="n">
-        <v>18.5</v>
+        <v>3.9</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G4" t="n">
         <v>2.44</v>
@@ -1169,13 +1169,13 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O4" t="n">
         <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
         <v>1.94</v>
@@ -1190,7 +1190,7 @@
         <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
         <v>1.41</v>
@@ -1199,10 +1199,10 @@
         <v>1.69</v>
       </c>
       <c r="X4" t="n">
-        <v>26</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
         <v>24</v>
@@ -1247,19 +1247,19 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AS4" t="n">
         <v>11.5</v>
@@ -1274,7 +1274,7 @@
         <v>12.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX4" t="n">
         <v>13.5</v>
@@ -1286,7 +1286,7 @@
         <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB4" t="n">
         <v>27</v>
@@ -1295,10 +1295,10 @@
         <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BE4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF4" t="n">
         <v>16</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>2.78</v>
       </c>
       <c r="G5" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H5" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I5" t="n">
         <v>2.86</v>
@@ -1354,7 +1354,7 @@
         <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
         <v>1.4</v>
@@ -1369,13 +1369,13 @@
         <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
         <v>1.95</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
         <v>3.35</v>
@@ -1387,19 +1387,19 @@
         <v>2.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA5" t="n">
         <v>95</v>
@@ -1414,19 +1414,19 @@
         <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
         <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="n">
         <v>100</v>
@@ -1441,31 +1441,31 @@
         <v>320</v>
       </c>
       <c r="AN5" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AO5" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AP5" t="n">
         <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
         <v>17</v>
       </c>
       <c r="AS5" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AT5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
         <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
         <v>24</v>
@@ -1474,35 +1474,35 @@
         <v>17</v>
       </c>
       <c r="AY5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
         <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BB5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD5" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BE5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BF5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG5" t="n">
         <v>21</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="G6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="J6" t="n">
         <v>5.8</v>
@@ -1557,13 +1557,13 @@
         <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O6" t="n">
         <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q6" t="n">
         <v>1.51</v>
@@ -1575,22 +1575,22 @@
         <v>2.28</v>
       </c>
       <c r="T6" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V6" t="n">
         <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X6" t="n">
         <v>29</v>
       </c>
       <c r="Y6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Z6" t="n">
         <v>540</v>
@@ -1629,25 +1629,25 @@
         <v>13.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AM6" t="n">
         <v>320</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AR6" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AS6" t="n">
         <v>95</v>
@@ -1656,7 +1656,7 @@
         <v>10.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV6" t="n">
         <v>25</v>
@@ -1671,7 +1671,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BA6" t="n">
         <v>48</v>
@@ -1683,7 +1683,7 @@
         <v>12</v>
       </c>
       <c r="BD6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BE6" t="n">
         <v>48</v>
@@ -1692,11 +1692,11 @@
         <v>4.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G7" t="n">
         <v>2.86</v>
@@ -1736,13 +1736,13 @@
         <v>3.15</v>
       </c>
       <c r="I7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="n">
         <v>2.96</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L7" t="n">
         <v>1.58</v>
@@ -1751,7 +1751,7 @@
         <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O7" t="n">
         <v>1.55</v>
@@ -1772,10 +1772,10 @@
         <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
         <v>1.53</v>
@@ -1793,19 +1793,19 @@
         <v>150</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC7" t="n">
         <v>7.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE7" t="n">
         <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG7" t="n">
         <v>14</v>
@@ -1817,10 +1817,10 @@
         <v>460</v>
       </c>
       <c r="AJ7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL7" t="n">
         <v>160</v>
@@ -1835,7 +1835,7 @@
         <v>180</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ7" t="n">
         <v>7.8</v>
@@ -1856,7 +1856,7 @@
         <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX7" t="n">
         <v>14</v>
@@ -1868,29 +1868,29 @@
         <v>19.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.6</v>
+        <v>60</v>
       </c>
       <c r="BB7" t="n">
         <v>18</v>
       </c>
       <c r="BC7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BE7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG7" t="n">
         <v>48</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -1921,64 +1921,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
         <v>2.82</v>
       </c>
       <c r="K8" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L8" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N8" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="O8" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="U8" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V8" t="n">
         <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X8" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
         <v>25</v>
@@ -1987,10 +1987,10 @@
         <v>85</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
         <v>17</v>
@@ -1999,7 +1999,7 @@
         <v>65</v>
       </c>
       <c r="AF8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG8" t="n">
         <v>13.5</v>
@@ -2008,7 +2008,7 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AJ8" t="n">
         <v>42</v>
@@ -2017,74 +2017,74 @@
         <v>40</v>
       </c>
       <c r="AL8" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AO8" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AR8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU8" t="n">
         <v>6</v>
       </c>
-      <c r="AS8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AV8" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AW8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>7.2</v>
       </c>
-      <c r="AX8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>6</v>
-      </c>
       <c r="BA8" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>2.04</v>
       </c>
       <c r="G9" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H9" t="n">
         <v>3.6</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
         <v>4.3</v>
@@ -2151,10 +2151,10 @@
         <v>1.67</v>
       </c>
       <c r="R9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
         <v>1.6</v>
@@ -2163,10 +2163,10 @@
         <v>2.32</v>
       </c>
       <c r="V9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2184,7 +2184,7 @@
         <v>40</v>
       </c>
       <c r="AC9" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="AD9" t="n">
         <v>90</v>
@@ -2229,10 +2229,10 @@
         <v>9</v>
       </c>
       <c r="AR9" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
@@ -2241,10 +2241,10 @@
         <v>7.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX9" t="n">
         <v>7.6</v>
@@ -2253,22 +2253,22 @@
         <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
         <v>10.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.35</v>
+        <v>8.4</v>
       </c>
       <c r="BF9" t="n">
         <v>10</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -2309,100 +2309,100 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.08</v>
+        <v>2.92</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.02</v>
+        <v>2.56</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>2.88</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>1.02</v>
+        <v>2.64</v>
       </c>
       <c r="O10" t="n">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="R10" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.92</v>
+        <v>2.46</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>2.98</v>
       </c>
       <c r="H11" t="n">
-        <v>2.02</v>
+        <v>2.78</v>
       </c>
       <c r="I11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>230</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>110</v>
       </c>
-      <c r="J11" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>95</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.27</v>
+        <v>8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.33</v>
+        <v>7.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.34</v>
+        <v>15.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.36</v>
+        <v>6.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.33</v>
+        <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.24</v>
+        <v>6</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.34</v>
+        <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.36</v>
+        <v>6.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.36</v>
+        <v>12.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.33</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.33</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.36</v>
+        <v>6.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.36</v>
+        <v>6.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.36</v>
+        <v>6.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.36</v>
+        <v>6.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.36</v>
+        <v>7.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="G12" t="n">
         <v>2.04</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J12" t="n">
         <v>3.05</v>
@@ -2715,13 +2715,13 @@
         <v>3.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M12" t="n">
         <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O12" t="n">
         <v>1.53</v>
@@ -2730,22 +2730,22 @@
         <v>1.52</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U12" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
         <v>1.96</v>
@@ -2754,10 +2754,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
@@ -2766,7 +2766,7 @@
         <v>6.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
         <v>23</v>
@@ -2775,13 +2775,13 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG12" t="n">
         <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
@@ -2811,22 +2811,22 @@
         <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU12" t="n">
         <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AX12" t="n">
         <v>8.800000000000001</v>
@@ -2838,7 +2838,7 @@
         <v>13</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB12" t="n">
         <v>20</v>
@@ -2847,20 +2847,20 @@
         <v>13</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BF12" t="n">
         <v>20</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -2894,10 +2894,10 @@
         <v>2.74</v>
       </c>
       <c r="G13" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="H13" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I13" t="n">
         <v>3.1</v>
@@ -2909,7 +2909,7 @@
         <v>3.35</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M13" t="n">
         <v>1.1</v>
@@ -2939,10 +2939,10 @@
         <v>1.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X13" t="n">
         <v>11</v>
@@ -2972,7 +2972,7 @@
         <v>17.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH13" t="n">
         <v>21</v>
@@ -3008,10 +3008,10 @@
         <v>16.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU13" t="n">
         <v>6.6</v>
@@ -3020,7 +3020,7 @@
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX13" t="n">
         <v>14</v>
@@ -3032,29 +3032,29 @@
         <v>18.5</v>
       </c>
       <c r="BA13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD13" t="n">
         <v>9.4</v>
       </c>
-      <c r="BB13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BE13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF13" t="n">
         <v>30</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="G14" t="n">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="H14" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K14" t="n">
-        <v>9.4</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>2.16</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="S14" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="W14" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC14" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="n">
-        <v>900</v>
+        <v>32</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.88</v>
+        <v>19.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.84</v>
+        <v>14.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.92</v>
+        <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.96</v>
+        <v>7.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.81</v>
+        <v>12</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.82</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.93</v>
+        <v>16</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.87</v>
+        <v>14.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.76</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.82</v>
+        <v>12.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.95</v>
+        <v>7.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.93</v>
+        <v>13</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.91</v>
+        <v>18</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.91</v>
+        <v>16</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.95</v>
+        <v>7.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.05</v>
+        <v>10</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.97</v>
+        <v>17</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -3279,67 +3279,67 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P15" t="n">
         <v>2.12</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.08</v>
-      </c>
       <c r="Q15" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="R15" t="n">
         <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
@@ -3363,17 +3363,17 @@
         <v>1000</v>
       </c>
       <c r="AH15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
         <v>130</v>
       </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
       <c r="AL15" t="n">
         <v>1000</v>
       </c>
@@ -3381,68 +3381,68 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.74</v>
+        <v>7.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.81</v>
+        <v>3.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.84</v>
+        <v>2.76</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.73</v>
+        <v>6.4</v>
       </c>
       <c r="AU15" t="n">
         <v>5.1</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.71</v>
+        <v>7.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.82</v>
+        <v>3</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.81</v>
+        <v>6.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.71</v>
+        <v>7.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.74</v>
+        <v>6.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.84</v>
+        <v>2.74</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.84</v>
+        <v>3.05</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.82</v>
+        <v>2.98</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.84</v>
+        <v>2.74</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.86</v>
+        <v>2.56</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -3473,25 +3473,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H16" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
         <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -3506,25 +3506,25 @@
         <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R16" t="n">
         <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="T16" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="X16" t="n">
         <v>19</v>
@@ -3533,16 +3533,16 @@
         <v>19.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AA16" t="n">
         <v>470</v>
       </c>
       <c r="AB16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
         <v>16.5</v>
@@ -3551,7 +3551,7 @@
         <v>110</v>
       </c>
       <c r="AF16" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG16" t="n">
         <v>11.5</v>
@@ -3563,7 +3563,7 @@
         <v>160</v>
       </c>
       <c r="AJ16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK16" t="n">
         <v>21</v>
@@ -3572,7 +3572,7 @@
         <v>34</v>
       </c>
       <c r="AM16" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
         <v>12.5</v>
@@ -3581,16 +3581,16 @@
         <v>240</v>
       </c>
       <c r="AP16" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT16" t="n">
         <v>5.8</v>
@@ -3602,7 +3602,7 @@
         <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX16" t="n">
         <v>7</v>
@@ -3611,22 +3611,22 @@
         <v>7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB16" t="n">
         <v>6.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF16" t="n">
         <v>10</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -3667,58 +3667,58 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="G17" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="H17" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K17" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>1.92</v>
+        <v>3.85</v>
       </c>
       <c r="O17" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P17" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V17" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W17" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3745,7 +3745,7 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
         <v>20</v>
@@ -3769,7 +3769,7 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
@@ -3778,13 +3778,13 @@
         <v>8.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AT17" t="n">
         <v>5.6</v>
@@ -3793,10 +3793,10 @@
         <v>5.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="AX17" t="n">
         <v>5.8</v>
@@ -3805,32 +3805,32 @@
         <v>6.4</v>
       </c>
       <c r="AZ17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB17" t="n">
         <v>4.5</v>
       </c>
-      <c r="BA17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BC17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -3873,13 +3873,13 @@
         <v>3.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
         <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
@@ -3891,7 +3891,7 @@
         <v>1.27</v>
       </c>
       <c r="P18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
         <v>1.78</v>
@@ -3921,7 +3921,7 @@
         <v>25</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA18" t="n">
         <v>900</v>
@@ -3939,7 +3939,7 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="AG18" t="n">
         <v>16.5</v>
@@ -3966,7 +3966,7 @@
         <v>19</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP18" t="n">
         <v>8.4</v>
@@ -3978,7 +3978,7 @@
         <v>18</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT18" t="n">
         <v>6.2</v>
@@ -3987,13 +3987,13 @@
         <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX18" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY18" t="n">
         <v>8.800000000000001</v>
@@ -4002,29 +4002,29 @@
         <v>12.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC18" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC18" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BD18" t="n">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G19" t="n">
         <v>2.44</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="I19" t="n">
         <v>3.65</v>
@@ -4070,34 +4070,34 @@
         <v>3.15</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M19" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>1.83</v>
+        <v>3.15</v>
       </c>
       <c r="O19" t="n">
         <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="R19" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U19" t="n">
         <v>2</v>
@@ -4109,116 +4109,116 @@
         <v>1.69</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.35</v>
+        <v>10.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.36</v>
+        <v>21</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.37</v>
+        <v>8</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.35</v>
+        <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.37</v>
+        <v>7.8</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.35</v>
+        <v>12</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.34</v>
+        <v>9.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.34</v>
+        <v>11.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.37</v>
+        <v>7.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.36</v>
+        <v>11.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.36</v>
+        <v>13</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.37</v>
+        <v>7.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.37</v>
+        <v>8.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.55</v>
+        <v>7.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -4249,170 +4249,170 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="G20" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="H20" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="I20" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K20" t="n">
-        <v>11</v>
+        <v>4.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>1.34</v>
+        <v>2.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V20" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.79</v>
+        <v>15</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.83</v>
+        <v>16.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.88</v>
+        <v>7.8</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.92</v>
+        <v>7.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="AU20" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.84</v>
+        <v>17.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.91</v>
+        <v>7.2</v>
       </c>
       <c r="AX20" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.84</v>
+        <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.91</v>
+        <v>7.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.83</v>
+        <v>15</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.85</v>
+        <v>14.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.89</v>
+        <v>18</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.91</v>
+        <v>7.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.86</v>
+        <v>8</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.92</v>
+        <v>7.2</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -4461,28 +4461,28 @@
         <v>3.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N21" t="n">
         <v>2.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="P21" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="R21" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="S21" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="T21" t="n">
         <v>2.18</v>
@@ -4521,7 +4521,7 @@
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG21" t="n">
         <v>12</v>
@@ -4533,7 +4533,7 @@
         <v>260</v>
       </c>
       <c r="AJ21" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AK21" t="n">
         <v>75</v>
@@ -4557,10 +4557,10 @@
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT21" t="n">
         <v>6</v>
@@ -4572,10 +4572,10 @@
         <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX21" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AY21" t="n">
         <v>10.5</v>
@@ -4584,29 +4584,29 @@
         <v>21</v>
       </c>
       <c r="BA21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD21" t="n">
         <v>10.5</v>
       </c>
-      <c r="BB21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>10</v>
-      </c>
       <c r="BE21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>9.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="BG21" t="n">
         <v>11</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="G22" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="H22" t="n">
-        <v>2.28</v>
+        <v>4.1</v>
       </c>
       <c r="I22" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
-        <v>2.44</v>
+        <v>2.96</v>
       </c>
       <c r="K22" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="M22" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="N22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P22" t="n">
         <v>1.5</v>
       </c>
-      <c r="O22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W22" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="X22" t="n">
         <v>16.5</v>
@@ -4739,68 +4739,68 @@
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>38</v>
+        <v>600</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AT22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV22" t="n">
         <v>5.1</v>
       </c>
-      <c r="AU22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AW22" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="AX22" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>3.4</v>
+        <v>23</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.35</v>
+        <v>23</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="BE22" t="n">
         <v>2.74</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.35</v>
+        <v>24</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.64</v>
+        <v>2.24</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G23" t="n">
         <v>1.83</v>
@@ -4849,25 +4849,25 @@
         <v>4.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M23" t="n">
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.25</v>
       </c>
       <c r="P23" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R23" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S23" t="n">
         <v>2.92</v>
@@ -4924,22 +4924,22 @@
         <v>21</v>
       </c>
       <c r="AK23" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AL23" t="n">
         <v>38</v>
       </c>
       <c r="AM23" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN23" t="n">
         <v>9.6</v>
       </c>
       <c r="AO23" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP23" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AQ23" t="n">
         <v>17.5</v>
@@ -4948,7 +4948,7 @@
         <v>34</v>
       </c>
       <c r="AS23" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AT23" t="n">
         <v>9.6</v>
@@ -4975,16 +4975,16 @@
         <v>48</v>
       </c>
       <c r="BB23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC23" t="n">
         <v>15.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE23" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="BF23" t="n">
         <v>8.800000000000001</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -5025,58 +5025,58 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="G24" t="n">
-        <v>3.35</v>
+        <v>2.28</v>
       </c>
       <c r="H24" t="n">
-        <v>1.89</v>
+        <v>2.72</v>
       </c>
       <c r="I24" t="n">
-        <v>5.7</v>
+        <v>3.25</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>85</v>
+        <v>5.9</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M24" t="n">
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>2.3</v>
+        <v>1.02</v>
       </c>
       <c r="O24" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="S24" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="V24" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="W24" t="n">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5094,7 +5094,7 @@
         <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
         <v>1000</v>
@@ -5127,68 +5127,68 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO24" t="n">
         <v>55</v>
       </c>
-      <c r="AO24" t="n">
-        <v>15</v>
-      </c>
       <c r="AP24" t="n">
-        <v>2.26</v>
+        <v>3.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AS24" t="n">
         <v>3.35</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="AU24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC24" t="n">
         <v>5.2</v>
       </c>
-      <c r="AV24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BD24" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G25" t="n">
         <v>1.49</v>
@@ -5234,7 +5234,7 @@
         <v>4.9</v>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5243,13 +5243,13 @@
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>1.02</v>
+        <v>2.4</v>
       </c>
       <c r="O25" t="n">
         <v>1.14</v>
       </c>
       <c r="P25" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
         <v>1.14</v>
@@ -5285,7 +5285,7 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
         <v>42</v>
@@ -5309,7 +5309,7 @@
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
         <v>1000</v>
@@ -5321,13 +5321,13 @@
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AQ25" t="n">
         <v>4.2</v>
@@ -5339,7 +5339,7 @@
         <v>4.2</v>
       </c>
       <c r="AT25" t="n">
-        <v>4.9</v>
+        <v>2.86</v>
       </c>
       <c r="AU25" t="n">
         <v>3</v>
@@ -5348,31 +5348,31 @@
         <v>22</v>
       </c>
       <c r="AW25" t="n">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="AX25" t="n">
         <v>5.2</v>
       </c>
       <c r="AY25" t="n">
-        <v>5.4</v>
+        <v>2.86</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BA25" t="n">
         <v>4.2</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="BC25" t="n">
-        <v>5.2</v>
+        <v>2.96</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="BF25" t="n">
         <v>3.2</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
         <v>15.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ26" t="n">
         <v>36</v>
@@ -5512,7 +5512,7 @@
         <v>38</v>
       </c>
       <c r="AM26" t="n">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="AN26" t="n">
         <v>19.5</v>
@@ -5566,17 +5566,17 @@
         <v>25</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF26" t="n">
         <v>13.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="G28" t="n">
         <v>12.5</v>
       </c>
       <c r="H28" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="I28" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="J28" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="K28" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -5834,25 +5834,25 @@
         <v>2.72</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R28" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="S28" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="T28" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U28" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V28" t="n">
         <v>3.9</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5873,10 +5873,10 @@
         <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
         <v>1000</v>
@@ -5906,43 +5906,43 @@
         <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AP28" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AS28" t="n">
         <v>6.4</v>
       </c>
       <c r="AT28" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU28" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX28" t="n">
         <v>4.2</v>
       </c>
       <c r="AY28" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BA28" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BB28" t="n">
         <v>4.2</v>
@@ -5951,20 +5951,20 @@
         <v>4.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="BF28" t="n">
         <v>10.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
         <v>1.69</v>
       </c>
       <c r="U29" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V29" t="n">
         <v>2.22</v>
@@ -6058,7 +6058,7 @@
         <v>40</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB29" t="n">
         <v>1000</v>
@@ -6103,7 +6103,7 @@
         <v>29</v>
       </c>
       <c r="AP29" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="n">
         <v>8.199999999999999</v>
@@ -6115,7 +6115,7 @@
         <v>12</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AU29" t="n">
         <v>7.6</v>
@@ -6127,38 +6127,38 @@
         <v>11.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="AY29" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BA29" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>2.9</v>
+        <v>2.46</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="BG29" t="n">
         <v>5.6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>2.04</v>
       </c>
       <c r="G30" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H30" t="n">
         <v>4.2</v>
@@ -6201,7 +6201,7 @@
         <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K30" t="n">
         <v>3.5</v>
@@ -6240,7 +6240,7 @@
         <v>1.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
         <v>11</v>
       </c>
       <c r="AG31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH31" t="n">
         <v>1000</v>
@@ -6491,25 +6491,25 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AQ31" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR31" t="n">
         <v>9.6</v>
       </c>
       <c r="AS31" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU31" t="n">
         <v>10</v>
       </c>
       <c r="AV31" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW31" t="n">
         <v>10</v>
@@ -6521,7 +6521,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ31" t="n">
-        <v>13.5</v>
+        <v>7.6</v>
       </c>
       <c r="BA31" t="n">
         <v>9.800000000000001</v>
@@ -6536,17 +6536,17 @@
         <v>20</v>
       </c>
       <c r="BE31" t="n">
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="BF31" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG31" t="n">
         <v>10</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -6718,10 +6718,10 @@
         <v>11.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB32" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC32" t="n">
         <v>21</v>
@@ -6730,17 +6730,17 @@
         <v>23</v>
       </c>
       <c r="BE32" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BF32" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG32" t="n">
         <v>13.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
         <v>10.5</v>
       </c>
       <c r="I33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J33" t="n">
         <v>5.9</v>
@@ -6795,31 +6795,31 @@
         <v>1.04</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O33" t="n">
         <v>1.21</v>
       </c>
       <c r="P33" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q33" t="n">
         <v>1.63</v>
       </c>
       <c r="R33" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S33" t="n">
         <v>2.6</v>
       </c>
       <c r="T33" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U33" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V33" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W33" t="n">
         <v>3.75</v>
@@ -6828,7 +6828,7 @@
         <v>38</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Z33" t="n">
         <v>1000</v>
@@ -6882,13 +6882,13 @@
         <v>16</v>
       </c>
       <c r="AQ33" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AR33" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AS33" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT33" t="n">
         <v>8.199999999999999</v>
@@ -6900,7 +6900,7 @@
         <v>26</v>
       </c>
       <c r="AW33" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX33" t="n">
         <v>7</v>
@@ -6909,7 +6909,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA33" t="n">
         <v>7.2</v>
@@ -6924,17 +6924,17 @@
         <v>28</v>
       </c>
       <c r="BE33" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG33" t="n">
         <v>15</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -7162,19 +7162,19 @@
         <v>1.35</v>
       </c>
       <c r="G35" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H35" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="I35" t="n">
         <v>17.5</v>
       </c>
       <c r="J35" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K35" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L35" t="n">
         <v>1.39</v>
@@ -7183,34 +7183,34 @@
         <v>1.09</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O35" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P35" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q35" t="n">
         <v>2.2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S35" t="n">
         <v>4.1</v>
       </c>
       <c r="T35" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="U35" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="V35" t="n">
         <v>1.06</v>
       </c>
       <c r="W35" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="X35" t="n">
         <v>21</v>
@@ -7225,7 +7225,7 @@
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AC35" t="n">
         <v>12.5</v>
@@ -7261,7 +7261,7 @@
         <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AO35" t="n">
         <v>1000</v>
@@ -7270,13 +7270,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ35" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR35" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT35" t="n">
         <v>4.9</v>
@@ -7285,10 +7285,10 @@
         <v>6.2</v>
       </c>
       <c r="AV35" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AW35" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AX35" t="n">
         <v>5.5</v>
@@ -7297,10 +7297,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ35" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BA35" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BB35" t="n">
         <v>9</v>
@@ -7309,20 +7309,20 @@
         <v>10.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE35" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF35" t="n">
         <v>7.6</v>
       </c>
       <c r="BG35" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -7461,10 +7461,10 @@
         <v>50</v>
       </c>
       <c r="AP36" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR36" t="n">
         <v>9.800000000000001</v>
@@ -7482,7 +7482,7 @@
         <v>17.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AX36" t="n">
         <v>11.5</v>
@@ -7491,7 +7491,7 @@
         <v>5.7</v>
       </c>
       <c r="AZ36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BA36" t="n">
         <v>10.5</v>
@@ -7506,17 +7506,17 @@
         <v>21</v>
       </c>
       <c r="BE36" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BF36" t="n">
         <v>5.7</v>
       </c>
       <c r="BG36" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="G38" t="n">
         <v>970</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7971,7 @@
         <v>1.6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S39" t="n">
         <v>2.38</v>
@@ -7983,7 +7983,7 @@
         <v>2.08</v>
       </c>
       <c r="V39" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W39" t="n">
         <v>2.44</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8246,7 @@
         <v>18</v>
       </c>
       <c r="AS40" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AT40" t="n">
         <v>5.1</v>
@@ -8258,28 +8258,28 @@
         <v>14.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AX40" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="AY40" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="AZ40" t="n">
         <v>10.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="BB40" t="n">
         <v>5</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="BD40" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BE40" t="n">
         <v>14</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G41" t="n">
         <v>2.2</v>
@@ -8332,13 +8332,13 @@
         <v>3.7</v>
       </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J41" t="n">
         <v>3.5</v>
       </c>
       <c r="K41" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L41" t="n">
         <v>1.31</v>
@@ -8353,7 +8353,7 @@
         <v>1.3</v>
       </c>
       <c r="P41" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q41" t="n">
         <v>1.9</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
         <v>3.3</v>
       </c>
       <c r="H42" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I42" t="n">
         <v>2.5</v>
@@ -8565,7 +8565,7 @@
         <v>2.26</v>
       </c>
       <c r="V42" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W42" t="n">
         <v>1.43</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
         <v>2.74</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R43" t="n">
         <v>1.7</v>
@@ -8756,7 +8756,7 @@
         <v>2.3</v>
       </c>
       <c r="U43" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V43" t="n">
         <v>1.05</v>
@@ -8831,13 +8831,13 @@
         <v>15</v>
       </c>
       <c r="AT43" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU43" t="n">
         <v>15</v>
       </c>
       <c r="AV43" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AW43" t="n">
         <v>14.5</v>
@@ -8849,7 +8849,7 @@
         <v>11</v>
       </c>
       <c r="AZ43" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BA43" t="n">
         <v>14</v>
@@ -8861,10 +8861,10 @@
         <v>12.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BE43" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BF43" t="n">
         <v>3.4</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -8911,10 +8911,10 @@
         <v>3.6</v>
       </c>
       <c r="H44" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I44" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="J44" t="n">
         <v>3.8</v>
@@ -8929,31 +8929,31 @@
         <v>1.05</v>
       </c>
       <c r="N44" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O44" t="n">
         <v>1.25</v>
       </c>
       <c r="P44" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q44" t="n">
         <v>1.77</v>
       </c>
       <c r="R44" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S44" t="n">
         <v>2.96</v>
       </c>
       <c r="T44" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U44" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V44" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W44" t="n">
         <v>1.38</v>
@@ -8962,22 +8962,22 @@
         <v>1000</v>
       </c>
       <c r="Y44" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z44" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA44" t="n">
         <v>900</v>
       </c>
       <c r="AB44" t="n">
-        <v>18</v>
+        <v>160</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD44" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE44" t="n">
         <v>150</v>
@@ -8989,7 +8989,7 @@
         <v>16.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="AI44" t="n">
         <v>1000</v>
@@ -9010,13 +9010,13 @@
         <v>1000</v>
       </c>
       <c r="AO44" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ44" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR44" t="n">
         <v>11.5</v>
@@ -9025,31 +9025,31 @@
         <v>21</v>
       </c>
       <c r="AT44" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU44" t="n">
         <v>7.4</v>
       </c>
       <c r="AV44" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW44" t="n">
         <v>17</v>
       </c>
       <c r="AX44" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AY44" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ44" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA44" t="n">
         <v>25</v>
       </c>
       <c r="BB44" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BC44" t="n">
         <v>27</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
         <v>16</v>
       </c>
       <c r="AS45" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AT45" t="n">
         <v>13</v>
@@ -9240,19 +9240,19 @@
         <v>13.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB45" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="BC45" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD45" t="n">
-        <v>5</v>
+        <v>18.5</v>
       </c>
       <c r="BE45" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF45" t="n">
         <v>18.5</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -9293,16 +9293,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="G46" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="H46" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="I46" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
         <v>3.85</v>
@@ -9332,7 +9332,7 @@
         <v>1.49</v>
       </c>
       <c r="S46" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T46" t="n">
         <v>1.66</v>
@@ -9341,10 +9341,10 @@
         <v>2.42</v>
       </c>
       <c r="V46" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W46" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="X46" t="n">
         <v>19</v>
@@ -9353,7 +9353,7 @@
         <v>14</v>
       </c>
       <c r="Z46" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA46" t="n">
         <v>46</v>
@@ -9362,10 +9362,10 @@
         <v>13</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD46" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE46" t="n">
         <v>29</v>
@@ -9395,7 +9395,7 @@
         <v>70</v>
       </c>
       <c r="AN46" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO46" t="n">
         <v>22</v>
@@ -9404,16 +9404,16 @@
         <v>17.5</v>
       </c>
       <c r="AQ46" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR46" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS46" t="n">
         <v>40</v>
       </c>
       <c r="AT46" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU46" t="n">
         <v>8.199999999999999</v>
@@ -9446,17 +9446,17 @@
         <v>30</v>
       </c>
       <c r="BE46" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF46" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG46" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
         <v>1.02</v>
       </c>
       <c r="N47" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O47" t="n">
         <v>1.15</v>
@@ -9607,7 +9607,7 @@
         <v>7.2</v>
       </c>
       <c r="AT47" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AU47" t="n">
         <v>12.5</v>
@@ -9622,7 +9622,7 @@
         <v>10.5</v>
       </c>
       <c r="AY47" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ47" t="n">
         <v>16</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -9681,10 +9681,10 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G48" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="H48" t="n">
         <v>2.32</v>
@@ -9693,10 +9693,10 @@
         <v>2.4</v>
       </c>
       <c r="J48" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K48" t="n">
         <v>3.5</v>
-      </c>
-      <c r="K48" t="n">
-        <v>3.75</v>
       </c>
       <c r="L48" t="n">
         <v>1.3</v>
@@ -9714,7 +9714,7 @@
         <v>2.02</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R48" t="n">
         <v>1.4</v>
@@ -9723,16 +9723,16 @@
         <v>3.05</v>
       </c>
       <c r="T48" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U48" t="n">
         <v>2.28</v>
       </c>
       <c r="V48" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W48" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X48" t="n">
         <v>17</v>
@@ -9786,7 +9786,7 @@
         <v>48</v>
       </c>
       <c r="AO48" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AP48" t="n">
         <v>12</v>
@@ -9798,13 +9798,13 @@
         <v>13</v>
       </c>
       <c r="AS48" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT48" t="n">
         <v>12</v>
       </c>
       <c r="AU48" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV48" t="n">
         <v>9.800000000000001</v>
@@ -9819,22 +9819,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ48" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA48" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="BB48" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BC48" t="n">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="BD48" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="BE48" t="n">
-        <v>9.6</v>
+        <v>29</v>
       </c>
       <c r="BF48" t="n">
         <v>8.199999999999999</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
         <v>1.11</v>
       </c>
       <c r="N49" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O49" t="n">
         <v>1.48</v>
@@ -9917,7 +9917,7 @@
         <v>4.8</v>
       </c>
       <c r="T49" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U49" t="n">
         <v>1.89</v>
@@ -9932,7 +9932,7 @@
         <v>10</v>
       </c>
       <c r="Y49" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z49" t="n">
         <v>85</v>
@@ -9941,7 +9941,7 @@
         <v>1000</v>
       </c>
       <c r="AB49" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC49" t="n">
         <v>7.2</v>
@@ -10028,17 +10028,17 @@
         <v>23</v>
       </c>
       <c r="BE49" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF49" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG49" t="n">
         <v>50</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -10069,16 +10069,16 @@
         </is>
       </c>
       <c r="F50" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G50" t="n">
         <v>1.19</v>
       </c>
-      <c r="G50" t="n">
-        <v>1.2</v>
-      </c>
       <c r="H50" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I50" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
         <v>9.199999999999999</v>
@@ -10108,7 +10108,7 @@
         <v>2.06</v>
       </c>
       <c r="S50" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="T50" t="n">
         <v>1.97</v>
@@ -10120,7 +10120,7 @@
         <v>1.05</v>
       </c>
       <c r="W50" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="X50" t="n">
         <v>55</v>
@@ -10141,7 +10141,7 @@
         <v>23</v>
       </c>
       <c r="AD50" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AE50" t="n">
         <v>270</v>
@@ -10156,7 +10156,7 @@
         <v>40</v>
       </c>
       <c r="AI50" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AJ50" t="n">
         <v>9.800000000000001</v>
@@ -10171,16 +10171,16 @@
         <v>160</v>
       </c>
       <c r="AN50" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AO50" t="n">
         <v>280</v>
       </c>
       <c r="AP50" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AQ50" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AR50" t="n">
         <v>46</v>
@@ -10195,7 +10195,7 @@
         <v>20</v>
       </c>
       <c r="AV50" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AW50" t="n">
         <v>50</v>
@@ -10225,14 +10225,14 @@
         <v>70</v>
       </c>
       <c r="BF50" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BG50" t="n">
         <v>50</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -10269,7 +10269,7 @@
         <v>1.9</v>
       </c>
       <c r="H51" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I51" t="n">
         <v>5.9</v>
@@ -10278,7 +10278,7 @@
         <v>3.55</v>
       </c>
       <c r="K51" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -10481,13 +10481,13 @@
         <v>1.02</v>
       </c>
       <c r="N52" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O52" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P52" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="Q52" t="n">
         <v>1.5</v>
@@ -10505,10 +10505,10 @@
         <v>2.52</v>
       </c>
       <c r="V52" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W52" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X52" t="n">
         <v>32</v>
@@ -10532,10 +10532,10 @@
         <v>22</v>
       </c>
       <c r="AE52" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF52" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG52" t="n">
         <v>13</v>
@@ -10544,7 +10544,7 @@
         <v>17</v>
       </c>
       <c r="AI52" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ52" t="n">
         <v>22</v>
@@ -10562,19 +10562,19 @@
         <v>7.2</v>
       </c>
       <c r="AO52" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AP52" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="AQ52" t="n">
         <v>21</v>
       </c>
       <c r="AR52" t="n">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="AS52" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT52" t="n">
         <v>12.5</v>
@@ -10586,7 +10586,7 @@
         <v>15.5</v>
       </c>
       <c r="AW52" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AX52" t="n">
         <v>12.5</v>
@@ -10598,7 +10598,7 @@
         <v>13.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BB52" t="n">
         <v>17</v>
@@ -10610,17 +10610,17 @@
         <v>20</v>
       </c>
       <c r="BE52" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="BF52" t="n">
         <v>5.9</v>
       </c>
       <c r="BG52" t="n">
-        <v>5.9</v>
+        <v>13.5</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -10651,16 +10651,16 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G53" t="n">
         <v>2.18</v>
       </c>
       <c r="H53" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I53" t="n">
         <v>4.3</v>
-      </c>
-      <c r="I53" t="n">
-        <v>4.4</v>
       </c>
       <c r="J53" t="n">
         <v>3.25</v>
@@ -10669,7 +10669,7 @@
         <v>3.3</v>
       </c>
       <c r="L53" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M53" t="n">
         <v>1.12</v>
@@ -10678,13 +10678,13 @@
         <v>2.82</v>
       </c>
       <c r="O53" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P53" t="n">
         <v>1.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="R53" t="n">
         <v>1.21</v>
@@ -10699,10 +10699,10 @@
         <v>1.81</v>
       </c>
       <c r="V53" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W53" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="X53" t="n">
         <v>9</v>
@@ -10717,13 +10717,13 @@
         <v>110</v>
       </c>
       <c r="AB53" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC53" t="n">
         <v>7.2</v>
       </c>
       <c r="AD53" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE53" t="n">
         <v>70</v>
@@ -10732,13 +10732,13 @@
         <v>11.5</v>
       </c>
       <c r="AG53" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH53" t="n">
         <v>24</v>
       </c>
       <c r="AI53" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ53" t="n">
         <v>27</v>
@@ -10750,7 +10750,7 @@
         <v>60</v>
       </c>
       <c r="AM53" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN53" t="n">
         <v>27</v>
@@ -10771,10 +10771,10 @@
         <v>90</v>
       </c>
       <c r="AT53" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU53" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV53" t="n">
         <v>16</v>
@@ -10792,7 +10792,7 @@
         <v>21</v>
       </c>
       <c r="BA53" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="BB53" t="n">
         <v>25</v>
@@ -10804,17 +10804,17 @@
         <v>50</v>
       </c>
       <c r="BE53" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="BF53" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BG53" t="n">
         <v>85</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -10857,7 +10857,7 @@
         <v>3.4</v>
       </c>
       <c r="J54" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K54" t="n">
         <v>4.3</v>
@@ -10932,7 +10932,7 @@
         <v>16.5</v>
       </c>
       <c r="AI54" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ54" t="n">
         <v>36</v>
@@ -10953,7 +10953,7 @@
         <v>20</v>
       </c>
       <c r="AP54" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AQ54" t="n">
         <v>14</v>
@@ -10962,7 +10962,7 @@
         <v>19</v>
       </c>
       <c r="AS54" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT54" t="n">
         <v>11.5</v>
@@ -10989,7 +10989,7 @@
         <v>23</v>
       </c>
       <c r="BB54" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BC54" t="n">
         <v>15</v>
@@ -10998,7 +10998,7 @@
         <v>19</v>
       </c>
       <c r="BE54" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF54" t="n">
         <v>8.199999999999999</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -11042,13 +11042,13 @@
         <v>3.55</v>
       </c>
       <c r="G55" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="H55" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="I55" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J55" t="n">
         <v>2.86</v>
@@ -11090,7 +11090,7 @@
         <v>1.6</v>
       </c>
       <c r="W55" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
@@ -11189,20 +11189,20 @@
         <v>36</v>
       </c>
       <c r="BD55" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BE55" t="n">
         <v>2.62</v>
       </c>
       <c r="BF55" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BG55" t="n">
         <v>32</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -11427,22 +11427,22 @@
         </is>
       </c>
       <c r="F57" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G57" t="n">
         <v>2.48</v>
       </c>
-      <c r="G57" t="n">
-        <v>2.52</v>
-      </c>
       <c r="H57" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I57" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="J57" t="n">
         <v>3.95</v>
       </c>
       <c r="K57" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L57" t="n">
         <v>1.27</v>
@@ -11457,7 +11457,7 @@
         <v>1.2</v>
       </c>
       <c r="P57" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q57" t="n">
         <v>1.6</v>
@@ -11469,16 +11469,16 @@
         <v>2.5</v>
       </c>
       <c r="T57" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U57" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V57" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W57" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X57" t="n">
         <v>24</v>
@@ -11496,13 +11496,13 @@
         <v>16</v>
       </c>
       <c r="AC57" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD57" t="n">
         <v>13</v>
       </c>
       <c r="AE57" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF57" t="n">
         <v>20</v>
@@ -11511,7 +11511,7 @@
         <v>12.5</v>
       </c>
       <c r="AH57" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI57" t="n">
         <v>32</v>
@@ -11529,7 +11529,7 @@
         <v>60</v>
       </c>
       <c r="AN57" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO57" t="n">
         <v>17.5</v>
@@ -11559,10 +11559,10 @@
         <v>23</v>
       </c>
       <c r="AX57" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY57" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ57" t="n">
         <v>13</v>
@@ -11571,13 +11571,13 @@
         <v>28</v>
       </c>
       <c r="BB57" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC57" t="n">
         <v>20</v>
       </c>
       <c r="BD57" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE57" t="n">
         <v>23</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -11621,13 +11621,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G58" t="n">
         <v>2.4</v>
       </c>
       <c r="H58" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I58" t="n">
         <v>3.3</v>
@@ -11636,7 +11636,7 @@
         <v>3.65</v>
       </c>
       <c r="K58" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
@@ -11645,7 +11645,7 @@
         <v>1.04</v>
       </c>
       <c r="N58" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O58" t="n">
         <v>1.21</v>
@@ -11735,7 +11735,7 @@
         <v>13.5</v>
       </c>
       <c r="AR58" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AS58" t="n">
         <v>40</v>
@@ -11762,7 +11762,7 @@
         <v>12.5</v>
       </c>
       <c r="BA58" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="BB58" t="n">
         <v>16</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -11818,7 +11818,7 @@
         <v>4.5</v>
       </c>
       <c r="G59" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H59" t="n">
         <v>1.91</v>
@@ -11827,7 +11827,7 @@
         <v>2.04</v>
       </c>
       <c r="J59" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K59" t="n">
         <v>3.65</v>
@@ -11839,7 +11839,7 @@
         <v>1.1</v>
       </c>
       <c r="N59" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O59" t="n">
         <v>1.44</v>
@@ -11887,19 +11887,19 @@
         <v>9.4</v>
       </c>
       <c r="AD59" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE59" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF59" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AG59" t="n">
         <v>40</v>
       </c>
       <c r="AH59" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AI59" t="n">
         <v>290</v>
@@ -11947,7 +11947,7 @@
         <v>11.5</v>
       </c>
       <c r="AX59" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AY59" t="n">
         <v>10.5</v>
@@ -11956,29 +11956,29 @@
         <v>13</v>
       </c>
       <c r="BA59" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB59" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC59" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BD59" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE59" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF59" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BG59" t="n">
         <v>12.5</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -12009,13 +12009,13 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G60" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H60" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I60" t="n">
         <v>2.84</v>
@@ -12039,10 +12039,10 @@
         <v>1.23</v>
       </c>
       <c r="P60" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R60" t="n">
         <v>1.48</v>
@@ -12060,7 +12060,7 @@
         <v>1.54</v>
       </c>
       <c r="W60" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X60" t="n">
         <v>22</v>
@@ -12126,13 +12126,13 @@
         <v>17</v>
       </c>
       <c r="AS60" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT60" t="n">
         <v>12</v>
       </c>
       <c r="AU60" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV60" t="n">
         <v>10.5</v>
@@ -12162,7 +12162,7 @@
         <v>16</v>
       </c>
       <c r="BE60" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BF60" t="n">
         <v>14</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -12203,22 +12203,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G61" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H61" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I61" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="J61" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K61" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L61" t="n">
         <v>1.48</v>
@@ -12227,13 +12227,13 @@
         <v>1.12</v>
       </c>
       <c r="N61" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O61" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P61" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q61" t="n">
         <v>2.5</v>
@@ -12248,13 +12248,13 @@
         <v>2</v>
       </c>
       <c r="U61" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V61" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W61" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X61" t="n">
         <v>9.199999999999999</v>
@@ -12263,7 +12263,7 @@
         <v>10.5</v>
       </c>
       <c r="Z61" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA61" t="n">
         <v>900</v>
@@ -12275,7 +12275,7 @@
         <v>7.2</v>
       </c>
       <c r="AD61" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE61" t="n">
         <v>1000</v>
@@ -12284,7 +12284,7 @@
         <v>16</v>
       </c>
       <c r="AG61" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH61" t="n">
         <v>22</v>
@@ -12293,7 +12293,7 @@
         <v>1000</v>
       </c>
       <c r="AJ61" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AK61" t="n">
         <v>140</v>
@@ -12308,7 +12308,7 @@
         <v>1000</v>
       </c>
       <c r="AO61" t="n">
-        <v>390</v>
+        <v>1000</v>
       </c>
       <c r="AP61" t="n">
         <v>7.6</v>
@@ -12320,7 +12320,7 @@
         <v>19</v>
       </c>
       <c r="AS61" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT61" t="n">
         <v>6.8</v>
@@ -12332,7 +12332,7 @@
         <v>13</v>
       </c>
       <c r="AW61" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX61" t="n">
         <v>13</v>
@@ -12344,29 +12344,29 @@
         <v>18</v>
       </c>
       <c r="BA61" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB61" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD61" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE61" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF61" t="n">
         <v>7.8</v>
       </c>
       <c r="BG61" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -12397,19 +12397,19 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G62" t="n">
         <v>1.21</v>
       </c>
       <c r="H62" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="I62" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K62" t="n">
         <v>11</v>
@@ -12421,13 +12421,13 @@
         <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>1.02</v>
+        <v>2.34</v>
       </c>
       <c r="O62" t="n">
         <v>1.05</v>
       </c>
       <c r="P62" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="Q62" t="n">
         <v>1.26</v>
@@ -12436,19 +12436,19 @@
         <v>2</v>
       </c>
       <c r="S62" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T62" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="U62" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V62" t="n">
         <v>1.05</v>
       </c>
       <c r="W62" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="X62" t="n">
         <v>1000</v>
@@ -12481,7 +12481,7 @@
         <v>22</v>
       </c>
       <c r="AH62" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI62" t="n">
         <v>1000</v>
@@ -12490,7 +12490,7 @@
         <v>11.5</v>
       </c>
       <c r="AK62" t="n">
-        <v>15.5</v>
+        <v>25</v>
       </c>
       <c r="AL62" t="n">
         <v>1000</v>
@@ -12505,40 +12505,40 @@
         <v>1000</v>
       </c>
       <c r="AP62" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ62" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS62" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT62" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU62" t="n">
         <v>11.5</v>
       </c>
       <c r="AV62" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX62" t="n">
         <v>11</v>
       </c>
       <c r="AY62" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AZ62" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA62" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB62" t="n">
         <v>9.4</v>
@@ -12547,20 +12547,20 @@
         <v>11.5</v>
       </c>
       <c r="BD62" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE62" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF62" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BG62" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -12594,7 +12594,7 @@
         <v>20</v>
       </c>
       <c r="G63" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H63" t="n">
         <v>1.17</v>
@@ -12630,7 +12630,7 @@
         <v>2.04</v>
       </c>
       <c r="S63" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="T63" t="n">
         <v>2.16</v>
@@ -12642,16 +12642,16 @@
         <v>6.6</v>
       </c>
       <c r="W63" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X63" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Y63" t="n">
         <v>13.5</v>
       </c>
       <c r="Z63" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA63" t="n">
         <v>8.800000000000001</v>
@@ -12684,25 +12684,25 @@
         <v>1000</v>
       </c>
       <c r="AK63" t="n">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="AL63" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AM63" t="n">
         <v>200</v>
       </c>
       <c r="AN63" t="n">
-        <v>380</v>
+        <v>430</v>
       </c>
       <c r="AO63" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="AP63" t="n">
         <v>44</v>
       </c>
       <c r="AQ63" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR63" t="n">
         <v>8.6</v>
@@ -12723,7 +12723,7 @@
         <v>12</v>
       </c>
       <c r="AX63" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AY63" t="n">
         <v>65</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -12785,22 +12785,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G64" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H64" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="I64" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J64" t="n">
         <v>3.7</v>
       </c>
       <c r="K64" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L64" t="n">
         <v>1.36</v>
@@ -12818,25 +12818,25 @@
         <v>2.26</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R64" t="n">
         <v>1.5</v>
       </c>
       <c r="S64" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T64" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U64" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V64" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W64" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="X64" t="n">
         <v>17.5</v>
@@ -12845,7 +12845,7 @@
         <v>17.5</v>
       </c>
       <c r="Z64" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA64" t="n">
         <v>75</v>
@@ -12857,13 +12857,13 @@
         <v>8.4</v>
       </c>
       <c r="AD64" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE64" t="n">
         <v>42</v>
       </c>
       <c r="AF64" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG64" t="n">
         <v>10.5</v>
@@ -12875,7 +12875,7 @@
         <v>44</v>
       </c>
       <c r="AJ64" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK64" t="n">
         <v>19</v>
@@ -12899,10 +12899,10 @@
         <v>16.5</v>
       </c>
       <c r="AR64" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS64" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT64" t="n">
         <v>10.5</v>
@@ -12917,7 +12917,7 @@
         <v>40</v>
       </c>
       <c r="AX64" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY64" t="n">
         <v>9.800000000000001</v>
@@ -12938,7 +12938,7 @@
         <v>28</v>
       </c>
       <c r="BE64" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF64" t="n">
         <v>11</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -12994,7 +12994,7 @@
         <v>7.8</v>
       </c>
       <c r="K65" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L65" t="n">
         <v>1.19</v>
@@ -13021,7 +13021,7 @@
         <v>1.8</v>
       </c>
       <c r="T65" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U65" t="n">
         <v>2.34</v>
@@ -13045,7 +13045,7 @@
         <v>440</v>
       </c>
       <c r="AB65" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC65" t="n">
         <v>19.5</v>
@@ -13063,10 +13063,10 @@
         <v>11.5</v>
       </c>
       <c r="AH65" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI65" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ65" t="n">
         <v>12</v>
@@ -13081,7 +13081,7 @@
         <v>90</v>
       </c>
       <c r="AN65" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="AO65" t="n">
         <v>110</v>
@@ -13093,10 +13093,10 @@
         <v>55</v>
       </c>
       <c r="AR65" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AS65" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AT65" t="n">
         <v>16</v>
@@ -13117,7 +13117,7 @@
         <v>11</v>
       </c>
       <c r="AZ65" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA65" t="n">
         <v>80</v>
@@ -13135,14 +13135,14 @@
         <v>75</v>
       </c>
       <c r="BF65" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BG65" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -13173,7 +13173,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="G66" t="n">
         <v>2.02</v>
@@ -13221,7 +13221,7 @@
         <v>1.87</v>
       </c>
       <c r="V66" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W66" t="n">
         <v>1.98</v>
@@ -13317,7 +13317,7 @@
         <v>6.8</v>
       </c>
       <c r="BB66" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC66" t="n">
         <v>11.5</v>
@@ -13329,14 +13329,14 @@
         <v>7</v>
       </c>
       <c r="BF66" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BG66" t="n">
         <v>7</v>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -13561,7 +13561,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G68" t="n">
         <v>1.78</v>
@@ -13570,7 +13570,7 @@
         <v>4.4</v>
       </c>
       <c r="I68" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J68" t="n">
         <v>4.1</v>
@@ -13594,19 +13594,19 @@
         <v>2.08</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R68" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S68" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="T68" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U68" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V68" t="n">
         <v>1.23</v>
@@ -13618,22 +13618,22 @@
         <v>21</v>
       </c>
       <c r="Y68" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z68" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA68" t="n">
-        <v>160</v>
+        <v>550</v>
       </c>
       <c r="AB68" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC68" t="n">
         <v>10.5</v>
       </c>
       <c r="AD68" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE68" t="n">
         <v>60</v>
@@ -13654,10 +13654,10 @@
         <v>19.5</v>
       </c>
       <c r="AK68" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL68" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM68" t="n">
         <v>95</v>
@@ -13666,22 +13666,22 @@
         <v>9.6</v>
       </c>
       <c r="AO68" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP68" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ68" t="n">
         <v>17</v>
       </c>
       <c r="AR68" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS68" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AT68" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU68" t="n">
         <v>7.2</v>
@@ -13690,19 +13690,19 @@
         <v>10.5</v>
       </c>
       <c r="AW68" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX68" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="AY68" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ68" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="BA68" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB68" t="n">
         <v>16</v>
@@ -13714,17 +13714,17 @@
         <v>16</v>
       </c>
       <c r="BE68" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF68" t="n">
         <v>6.2</v>
       </c>
       <c r="BG68" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
         <v>1.63</v>
       </c>
       <c r="G69" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="H69" t="n">
         <v>6</v>
@@ -13779,7 +13779,7 @@
         <v>1.08</v>
       </c>
       <c r="N69" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O69" t="n">
         <v>1.37</v>
@@ -13806,13 +13806,13 @@
         <v>1.15</v>
       </c>
       <c r="W69" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X69" t="n">
         <v>14.5</v>
       </c>
       <c r="Y69" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z69" t="n">
         <v>60</v>
@@ -13869,7 +13869,7 @@
         <v>15.5</v>
       </c>
       <c r="AR69" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS69" t="n">
         <v>6.4</v>
@@ -13905,10 +13905,10 @@
         <v>16.5</v>
       </c>
       <c r="BD69" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE69" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF69" t="n">
         <v>9.4</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -14146,7 +14146,7 @@
         <v>1.31</v>
       </c>
       <c r="G71" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H71" t="n">
         <v>12.5</v>
@@ -14194,7 +14194,7 @@
         <v>1.08</v>
       </c>
       <c r="W71" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="X71" t="n">
         <v>23</v>
@@ -14260,7 +14260,7 @@
         <v>8.4</v>
       </c>
       <c r="AS71" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AT71" t="n">
         <v>6.8</v>
@@ -14284,7 +14284,7 @@
         <v>7</v>
       </c>
       <c r="BA71" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB71" t="n">
         <v>8.800000000000001</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -14337,7 +14337,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="G72" t="n">
         <v>1.94</v>
@@ -14346,7 +14346,7 @@
         <v>4.2</v>
       </c>
       <c r="I72" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J72" t="n">
         <v>3.95</v>
@@ -14397,7 +14397,7 @@
         <v>27</v>
       </c>
       <c r="Z72" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA72" t="n">
         <v>1000</v>
@@ -14406,7 +14406,7 @@
         <v>12.5</v>
       </c>
       <c r="AC72" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD72" t="n">
         <v>18</v>
@@ -14415,7 +14415,7 @@
         <v>1000</v>
       </c>
       <c r="AF72" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AG72" t="n">
         <v>10.5</v>
@@ -14442,16 +14442,16 @@
         <v>9.6</v>
       </c>
       <c r="AO72" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP72" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ72" t="n">
         <v>17.5</v>
       </c>
       <c r="AR72" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS72" t="n">
         <v>36</v>
@@ -14493,14 +14493,14 @@
         <v>55</v>
       </c>
       <c r="BF72" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG72" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G73" t="n">
         <v>2.7</v>
@@ -14540,7 +14540,7 @@
         <v>2.6</v>
       </c>
       <c r="I73" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J73" t="n">
         <v>3.95</v>
@@ -14567,7 +14567,7 @@
         <v>1.63</v>
       </c>
       <c r="R73" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S73" t="n">
         <v>2.6</v>
@@ -14681,7 +14681,7 @@
         <v>22</v>
       </c>
       <c r="BD73" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE73" t="n">
         <v>29</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -14728,7 +14728,7 @@
         <v>2.52</v>
       </c>
       <c r="G74" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H74" t="n">
         <v>2.98</v>
@@ -14776,7 +14776,7 @@
         <v>1.48</v>
       </c>
       <c r="W74" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X74" t="n">
         <v>18.5</v>
@@ -14854,7 +14854,7 @@
         <v>11.5</v>
       </c>
       <c r="AW74" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="AX74" t="n">
         <v>15</v>
@@ -14884,11 +14884,11 @@
         <v>18.5</v>
       </c>
       <c r="BG74" t="n">
-        <v>20</v>
+        <v>8.4</v>
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
         <v>2.14</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R75" t="n">
         <v>1.44</v>
@@ -14967,7 +14967,7 @@
         <v>2.24</v>
       </c>
       <c r="V75" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W75" t="n">
         <v>2.04</v>
@@ -15012,7 +15012,7 @@
         <v>1000</v>
       </c>
       <c r="AK75" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL75" t="n">
         <v>1000</v>
@@ -15021,13 +15021,13 @@
         <v>1000</v>
       </c>
       <c r="AN75" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO75" t="n">
         <v>1000</v>
       </c>
       <c r="AP75" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ75" t="n">
         <v>15</v>
@@ -15066,7 +15066,7 @@
         <v>19</v>
       </c>
       <c r="BC75" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD75" t="n">
         <v>27</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -15122,7 +15122,7 @@
         <v>4.6</v>
       </c>
       <c r="I76" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J76" t="n">
         <v>4</v>
@@ -15155,7 +15155,7 @@
         <v>2.52</v>
       </c>
       <c r="T76" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U76" t="n">
         <v>2.5</v>
@@ -15272,11 +15272,11 @@
         <v>7.4</v>
       </c>
       <c r="BG76" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -15376,7 +15376,7 @@
         <v>9.4</v>
       </c>
       <c r="AC77" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD77" t="n">
         <v>16</v>
@@ -15391,7 +15391,7 @@
         <v>11</v>
       </c>
       <c r="AH77" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI77" t="n">
         <v>60</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -15501,16 +15501,16 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="G78" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="H78" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I78" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J78" t="n">
         <v>4.8</v>
@@ -15519,13 +15519,13 @@
         <v>5.6</v>
       </c>
       <c r="L78" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M78" t="n">
         <v>1.02</v>
       </c>
       <c r="N78" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O78" t="n">
         <v>1.14</v>
@@ -15543,16 +15543,16 @@
         <v>2.08</v>
       </c>
       <c r="T78" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U78" t="n">
         <v>2.48</v>
       </c>
       <c r="V78" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W78" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="X78" t="n">
         <v>1000</v>
@@ -15603,10 +15603,10 @@
         <v>1000</v>
       </c>
       <c r="AN78" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO78" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP78" t="n">
         <v>6.4</v>
@@ -15615,7 +15615,7 @@
         <v>6.2</v>
       </c>
       <c r="AR78" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS78" t="n">
         <v>7.2</v>
@@ -15642,7 +15642,7 @@
         <v>16</v>
       </c>
       <c r="BA78" t="n">
-        <v>38</v>
+        <v>6.8</v>
       </c>
       <c r="BB78" t="n">
         <v>13.5</v>
@@ -15660,11 +15660,11 @@
         <v>4.6</v>
       </c>
       <c r="BG78" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -15701,7 +15701,7 @@
         <v>2.12</v>
       </c>
       <c r="H79" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I79" t="n">
         <v>3.7</v>
@@ -15737,7 +15737,7 @@
         <v>2.6</v>
       </c>
       <c r="T79" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U79" t="n">
         <v>2.48</v>
@@ -15749,116 +15749,116 @@
         <v>1.89</v>
       </c>
       <c r="X79" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y79" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z79" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA79" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB79" t="n">
         <v>13.5</v>
       </c>
       <c r="AC79" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD79" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF79" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE79" t="n">
+      <c r="AG79" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI79" t="n">
         <v>40</v>
-      </c>
-      <c r="AF79" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG79" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI79" t="n">
-        <v>42</v>
       </c>
       <c r="AJ79" t="n">
         <v>26</v>
       </c>
       <c r="AK79" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL79" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM79" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN79" t="n">
         <v>11</v>
       </c>
       <c r="AO79" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP79" t="n">
         <v>19.5</v>
       </c>
       <c r="AQ79" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR79" t="n">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="AS79" t="n">
-        <v>50</v>
+        <v>11.5</v>
       </c>
       <c r="AT79" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU79" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV79" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW79" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX79" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY79" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ79" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA79" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB79" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC79" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD79" t="n">
-        <v>24</v>
+        <v>9.4</v>
       </c>
       <c r="BE79" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BF79" t="n">
         <v>9.4</v>
       </c>
       <c r="BG79" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -15889,10 +15889,10 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G80" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H80" t="n">
         <v>3.9</v>
@@ -15904,7 +15904,7 @@
         <v>2.96</v>
       </c>
       <c r="K80" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L80" t="n">
         <v>1.01</v>
@@ -15940,7 +15940,7 @@
         <v>1.29</v>
       </c>
       <c r="W80" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X80" t="n">
         <v>7.8</v>
@@ -15964,7 +15964,7 @@
         <v>22</v>
       </c>
       <c r="AE80" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF80" t="n">
         <v>13.5</v>
@@ -16006,7 +16006,7 @@
         <v>6.2</v>
       </c>
       <c r="AS80" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT80" t="n">
         <v>5.9</v>
@@ -16018,7 +16018,7 @@
         <v>15.5</v>
       </c>
       <c r="AW80" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX80" t="n">
         <v>10.5</v>
@@ -16027,13 +16027,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ80" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB80" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BA80" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB80" t="n">
-        <v>6.4</v>
       </c>
       <c r="BC80" t="n">
         <v>6.6</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -16092,7 +16092,7 @@
         <v>3.5</v>
       </c>
       <c r="I81" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J81" t="n">
         <v>3.95</v>
@@ -16242,11 +16242,11 @@
         <v>9.6</v>
       </c>
       <c r="BG81" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -16277,7 +16277,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G82" t="n">
         <v>1.91</v>
@@ -16286,7 +16286,7 @@
         <v>4.6</v>
       </c>
       <c r="I82" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J82" t="n">
         <v>3.65</v>
@@ -16301,7 +16301,7 @@
         <v>1.05</v>
       </c>
       <c r="N82" t="n">
-        <v>1.9</v>
+        <v>1.02</v>
       </c>
       <c r="O82" t="n">
         <v>1.29</v>
@@ -16313,7 +16313,7 @@
         <v>1.9</v>
       </c>
       <c r="R82" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S82" t="n">
         <v>2.88</v>
@@ -16349,7 +16349,7 @@
         <v>10.5</v>
       </c>
       <c r="AD82" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE82" t="n">
         <v>1000</v>
@@ -16361,7 +16361,7 @@
         <v>12.5</v>
       </c>
       <c r="AH82" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI82" t="n">
         <v>1000</v>
@@ -16385,62 +16385,62 @@
         <v>1000</v>
       </c>
       <c r="AP82" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ82" t="n">
         <v>12.5</v>
       </c>
       <c r="AR82" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AS82" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW82" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT82" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU82" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV82" t="n">
+      <c r="AX82" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC82" t="n">
         <v>14</v>
       </c>
-      <c r="AW82" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX82" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY82" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ82" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA82" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB82" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC82" t="n">
-        <v>17</v>
-      </c>
       <c r="BD82" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BE82" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF82" t="n">
         <v>9</v>
       </c>
       <c r="BG82" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -16474,13 +16474,13 @@
         <v>7.4</v>
       </c>
       <c r="G83" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="H83" t="n">
         <v>1.42</v>
       </c>
       <c r="I83" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="J83" t="n">
         <v>5.3</v>
@@ -16501,16 +16501,16 @@
         <v>1.16</v>
       </c>
       <c r="P83" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q83" t="n">
         <v>1.48</v>
       </c>
       <c r="R83" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S83" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="T83" t="n">
         <v>1.71</v>
@@ -16519,10 +16519,10 @@
         <v>2.24</v>
       </c>
       <c r="V83" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="W83" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X83" t="n">
         <v>34</v>
@@ -16555,7 +16555,7 @@
         <v>32</v>
       </c>
       <c r="AH83" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI83" t="n">
         <v>29</v>
@@ -16579,19 +16579,19 @@
         <v>4.7</v>
       </c>
       <c r="AP83" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ83" t="n">
         <v>11</v>
       </c>
       <c r="AR83" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS83" t="n">
         <v>11.5</v>
       </c>
       <c r="AT83" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU83" t="n">
         <v>11</v>
@@ -16612,19 +16612,19 @@
         <v>17.5</v>
       </c>
       <c r="BA83" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB83" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC83" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD83" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BD83" t="n">
-        <v>8</v>
-      </c>
       <c r="BE83" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF83" t="n">
         <v>8.199999999999999</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -16680,10 +16680,10 @@
         <v>3.6</v>
       </c>
       <c r="K84" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L84" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M84" t="n">
         <v>1.08</v>
@@ -16695,16 +16695,16 @@
         <v>1.37</v>
       </c>
       <c r="P84" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R84" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S84" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T84" t="n">
         <v>1.92</v>
@@ -16719,7 +16719,7 @@
         <v>1.25</v>
       </c>
       <c r="X84" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y84" t="n">
         <v>9.6</v>
@@ -16794,7 +16794,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW84" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AX84" t="n">
         <v>4.9</v>
@@ -16812,23 +16812,23 @@
         <v>5.2</v>
       </c>
       <c r="BC84" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BD84" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE84" t="n">
         <v>5.2</v>
       </c>
       <c r="BF84" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG84" t="n">
         <v>13</v>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -16880,10 +16880,10 @@
         <v>1.01</v>
       </c>
       <c r="M85" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N85" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O85" t="n">
         <v>1.2</v>
@@ -16892,7 +16892,7 @@
         <v>2.48</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R85" t="n">
         <v>1.58</v>
@@ -16904,7 +16904,7 @@
         <v>1.64</v>
       </c>
       <c r="U85" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V85" t="n">
         <v>1.26</v>
@@ -16928,7 +16928,7 @@
         <v>14.5</v>
       </c>
       <c r="AC85" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD85" t="n">
         <v>22</v>
@@ -16973,10 +16973,10 @@
         <v>20</v>
       </c>
       <c r="AR85" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS85" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT85" t="n">
         <v>10.5</v>
@@ -16988,7 +16988,7 @@
         <v>16.5</v>
       </c>
       <c r="AW85" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX85" t="n">
         <v>11.5</v>
@@ -17012,17 +17012,17 @@
         <v>4.9</v>
       </c>
       <c r="BE85" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF85" t="n">
         <v>7</v>
       </c>
       <c r="BG85" t="n">
-        <v>34</v>
+        <v>5.2</v>
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G88" t="n">
         <v>2.36</v>
@@ -17450,7 +17450,7 @@
         <v>2.94</v>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J88" t="n">
         <v>4.2</v>
@@ -17468,7 +17468,7 @@
         <v>7</v>
       </c>
       <c r="O88" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P88" t="n">
         <v>3</v>
@@ -17486,7 +17486,7 @@
         <v>1.48</v>
       </c>
       <c r="U88" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="V88" t="n">
         <v>1.5</v>
@@ -17522,7 +17522,7 @@
         <v>20</v>
       </c>
       <c r="AG88" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH88" t="n">
         <v>14.5</v>
@@ -17561,7 +17561,7 @@
         <v>25</v>
       </c>
       <c r="AT88" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU88" t="n">
         <v>9.6</v>
@@ -17585,7 +17585,7 @@
         <v>26</v>
       </c>
       <c r="BB88" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC88" t="n">
         <v>18.5</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -17641,13 +17641,13 @@
         <v>1.49</v>
       </c>
       <c r="H89" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I89" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J89" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K89" t="n">
         <v>5.6</v>
@@ -17689,7 +17689,7 @@
         <v>3</v>
       </c>
       <c r="X89" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Y89" t="n">
         <v>1000</v>
@@ -17764,7 +17764,7 @@
         <v>23</v>
       </c>
       <c r="AW89" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AX89" t="n">
         <v>9.800000000000001</v>
@@ -17785,10 +17785,10 @@
         <v>12.5</v>
       </c>
       <c r="BD89" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BE89" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BF89" t="n">
         <v>4.5</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
@@ -17832,19 +17832,19 @@
         <v>1.49</v>
       </c>
       <c r="G90" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="H90" t="n">
         <v>6.6</v>
       </c>
       <c r="I90" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J90" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K90" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L90" t="n">
         <v>1.29</v>
@@ -17853,7 +17853,7 @@
         <v>1.03</v>
       </c>
       <c r="N90" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O90" t="n">
         <v>1.19</v>
@@ -17862,7 +17862,7 @@
         <v>2.62</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R90" t="n">
         <v>1.63</v>
@@ -17871,7 +17871,7 @@
         <v>2.5</v>
       </c>
       <c r="T90" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U90" t="n">
         <v>2.22</v>
@@ -17880,7 +17880,7 @@
         <v>1.16</v>
       </c>
       <c r="W90" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="X90" t="n">
         <v>26</v>
@@ -17898,13 +17898,13 @@
         <v>11.5</v>
       </c>
       <c r="AC90" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD90" t="n">
         <v>26</v>
       </c>
       <c r="AE90" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF90" t="n">
         <v>10.5</v>
@@ -17919,7 +17919,7 @@
         <v>75</v>
       </c>
       <c r="AJ90" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK90" t="n">
         <v>14</v>
@@ -17943,13 +17943,13 @@
         <v>25</v>
       </c>
       <c r="AR90" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS90" t="n">
         <v>46</v>
       </c>
       <c r="AT90" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU90" t="n">
         <v>10.5</v>
@@ -17982,7 +17982,7 @@
         <v>24</v>
       </c>
       <c r="BE90" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BF90" t="n">
         <v>5.5</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-21 22:33:50</t>
+          <t>2026-04-22 00:49:35</t>
         </is>
       </c>
     </row>
